--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Potential Defects'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$I$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$I$23</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Test Cases'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$S$83</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$S$84</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="794">
   <si>
     <t xml:space="preserve">DemoBlaze – Test Case Suite (Login &amp; Cart)</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2 (20-Oct-2026)</t>
+    <t xml:space="preserve">1.3 (20-Oct-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Execution environment</t>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t xml:space="preserve">Automation decision recorded: 32 cases automated in the Playwright framework (6 as known-defect tests), with spec file per case; remaining cases marked Backlog or Manual with the reason.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First full automated run on the live site found a new critical defect (PD-22: guests landing on a product page share one cart); added CRT-049. LGN-022 updated: DemoBlaze's mobile menu never collapses.</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -799,20 +805,19 @@
     <t xml:space="preserve">LGN-022</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify login works at mobile width through the collapsed menu</t>
+    <t xml:space="preserve">Verify login works at mobile width</t>
   </si>
   <si>
     <t xml:space="preserve">Account {VALID_USER} exists; user is logged out. Browser viewport is 375 x 812 (mobile emulation).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
-2. Tap the menu toggle (☰) in the navbar.
-3. Tap 'Log in'.
-4. Enter {VALID_USER} and {VALID_PASSWORD} and tap 'Log in'.
-5. Tap the menu toggle again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The menu expands and shows 'Log in'. After login, the expanded menu shows 'Welcome {VALID_USER}' and 'Log out'.</t>
+2. Check the menu toggle (☰) is shown in the navbar.
+3. Tap 'Log in' (expand the menu first if it is collapsed).
+4. Enter {VALID_USER} and {VALID_PASSWORD} and tap 'Log in'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mobile menu toggle is shown and 'Log in' is reachable. After login, the menu shows 'Welcome {VALID_USER}' and 'Log out'.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-023</t>
@@ -2118,6 +2123,32 @@
     <t xml:space="preserve">tests/api/product.api.spec.ts</t>
   </si>
   <si>
+    <t xml:space="preserve">CRT-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify a guest who opens a product page directly gets a private cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged out; browser has no DemoBlaze cookies (new session).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to {BASE_URL}/prod.html?idp_=2 directly (do not open Home first).
+2. Click 'Add to cart' and accept the alert.
+3. Click 'Cart'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cart contains only the one 'Nokia lumia 1520' just added (the guest has a private cart keyed by a unique guest id).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated run: a guest who opened the product page directly saw 121-134 items in the cart, added by other guests. /addtocart was sent with an empty guest id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromium, Firefox, WebKit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
@@ -2499,6 +2530,22 @@
   </si>
   <si>
     <t xml:space="preserve">Order accepted; the Name overflows the confirmation dialog horizontally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guests who open a product page directly share one cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a new private browser window.
+2. Go to https://www.demoblaze.com/prod.html?idp_=2 directly.
+3. Click 'Add to cart'.
+4. Click 'Cart'.
+5. Check DevTools &gt; Network &gt; POST /addtocart: 'cookie' is empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each guest has a private cart keyed by a unique guest id, whichever page they land on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only the Home page creates the guest id cookie ('user'). A guest who lands on a product page first (search result, shared link) sends an empty id, so all such guests read and write the same cart: our test saw 121-134 items from other people. Privacy issue: one guest can see, and buy, another guest's items. Reproduced 20-Oct-2026 by the automated run on Chromium, Firefox and WebKit.</t>
   </si>
   <si>
     <t xml:space="preserve">Note: DemoBlaze has no published requirements. 'Expected' follows common e-commerce practice, so 'Potential defect – requirement to confirm' items should be agreed with the product owner before being raised as bugs. 'Reproduced?' = observed when the related test was run on 19-Oct-2026.</t>
@@ -3324,7 +3371,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3442,31 +3489,31 @@
         <v>20</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A11,'Test Cases'!$F$2:$F$83,"Positive")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Positive")</f>
         <v>11</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A11,'Test Cases'!$F$2:$F$83,"Negative")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Negative")</f>
         <v>15</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A11,'Test Cases'!$F$2:$F$83,"Edge")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Edge")</f>
         <v>7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A11,'Test Cases'!$F$2:$F$83,"Boundary")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Boundary")</f>
         <v>1</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$83,$A11)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$84,$A11)</f>
         <v>34</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A11,'Test Cases'!$M$2:$M$83,"Automated*")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$M$2:$M$84,"Automated*")</f>
         <v>15</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A11,'Test Cases'!$O$2:$O$83,"&lt;&gt;Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
         <v>6</v>
       </c>
     </row>
@@ -3475,32 +3522,32 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A12,'Test Cases'!$F$2:$F$83,"Positive")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Positive")</f>
         <v>22</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A12,'Test Cases'!$F$2:$F$83,"Negative")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Negative")</f>
         <v>15</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A12,'Test Cases'!$F$2:$F$83,"Edge")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Edge")</f>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A12,'Test Cases'!$F$2:$F$83,"Boundary")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Boundary")</f>
         <v>4</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$83,$A12)</f>
-        <v>48</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$84,$A12)</f>
+        <v>49</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A12,'Test Cases'!$M$2:$M$83,"Automated*")</f>
-        <v>17</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$M$2:$M$84,"Automated*")</f>
+        <v>18</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A12,'Test Cases'!$O$2:$O$83,"&lt;&gt;Not Run")</f>
-        <v>34</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
+        <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3517,7 +3564,7 @@
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">SUM(D11:D12)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">SUM(E11:E12)</f>
@@ -3525,15 +3572,15 @@
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">SUM(F11:F12)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">SUM(G11:G12)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">SUM(H11:H12)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3569,23 +3616,23 @@
         <v>20</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A17,'Test Cases'!$E$2:$E$83,"Functional")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Functional")</f>
         <v>19</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A17,'Test Cases'!$E$2:$E$83,"Security")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Security")</f>
         <v>9</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A17,'Test Cases'!$E$2:$E$83,"API")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"API")</f>
         <v>3</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A17,'Test Cases'!$E$2:$E$83,"Usability")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Usability")</f>
         <v>3</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A17,'Test Cases'!$E$2:$E$83,"Performance")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Performance")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
@@ -3598,28 +3645,28 @@
         <v>21</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A18,'Test Cases'!$E$2:$E$83,"Functional")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Functional")</f>
         <v>36</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A18,'Test Cases'!$E$2:$E$83,"Security")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Security")</f>
+        <v>6</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A18,'Test Cases'!$E$2:$E$83,"API")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"API")</f>
         <v>3</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A18,'Test Cases'!$E$2:$E$83,"Usability")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Usability")</f>
         <v>3</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$83,$A18,'Test Cases'!$E$2:$E$83,"Performance")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Performance")</f>
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
         <f aca="false">SUM(B18:F18)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3632,7 +3679,7 @@
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">SUM(C17:C18)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">SUM(D17:D18)</f>
@@ -3648,7 +3695,7 @@
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">SUM(G17:G18)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3678,19 +3725,19 @@
         <v>34</v>
       </c>
       <c r="B23" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$83,$A23)</f>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A23)</f>
         <v>20</v>
       </c>
       <c r="C23" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A23,'Test Cases'!$G$2:$G$83,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P1")</f>
         <v>9</v>
       </c>
       <c r="D23" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A23,'Test Cases'!$G$2:$G$83,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P2")</f>
         <v>10</v>
       </c>
       <c r="E23" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A23,'Test Cases'!$G$2:$G$83,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P3")</f>
         <v>1</v>
       </c>
       <c r="G23" s="9" t="s">
@@ -3702,24 +3749,24 @@
         <v>36</v>
       </c>
       <c r="B24" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$83,$A24)</f>
-        <v>20</v>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A24)</f>
+        <v>21</v>
       </c>
       <c r="C24" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A24,'Test Cases'!$G$2:$G$83,"P1")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P1")</f>
+        <v>4</v>
       </c>
       <c r="D24" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A24,'Test Cases'!$G$2:$G$83,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P2")</f>
         <v>7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A24,'Test Cases'!$G$2:$G$83,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P3")</f>
         <v>10</v>
       </c>
       <c r="G24" s="10" t="n">
         <f aca="false">IFERROR(B23/(B23+B24),0)</f>
-        <v>0.5</v>
+        <v>0.487804878048781</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3727,19 +3774,19 @@
         <v>37</v>
       </c>
       <c r="B25" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$83,$A25)</f>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A25,'Test Cases'!$G$2:$G$83,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A25,'Test Cases'!$G$2:$G$84,"P1")</f>
         <v>0</v>
       </c>
       <c r="D25" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A25,'Test Cases'!$G$2:$G$83,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A25,'Test Cases'!$G$2:$G$84,"P2")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A25,'Test Cases'!$G$2:$G$83,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A25,'Test Cases'!$G$2:$G$84,"P3")</f>
         <v>0</v>
       </c>
     </row>
@@ -3748,19 +3795,19 @@
         <v>38</v>
       </c>
       <c r="B26" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$83,$A26)</f>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A26)</f>
         <v>42</v>
       </c>
       <c r="C26" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A26,'Test Cases'!$G$2:$G$83,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P1")</f>
         <v>6</v>
       </c>
       <c r="D26" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A26,'Test Cases'!$G$2:$G$83,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P2")</f>
         <v>19</v>
       </c>
       <c r="E26" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$83,$A26,'Test Cases'!$G$2:$G$83,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P3")</f>
         <v>17</v>
       </c>
     </row>
@@ -3770,11 +3817,11 @@
       </c>
       <c r="B27" s="8" t="n">
         <f aca="false">SUM(B23:B26)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" s="8" t="n">
         <f aca="false">SUM(C23:C26)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" s="8" t="n">
         <f aca="false">SUM(D23:D26)</f>
@@ -3806,7 +3853,7 @@
         <v>18</v>
       </c>
       <c r="B31" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$83,$A31)</f>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A31)</f>
         <v>26</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -3823,8 +3870,8 @@
         <v>43</v>
       </c>
       <c r="B32" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$83,$A32)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A32)</f>
+        <v>7</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>44</v>
@@ -3840,7 +3887,7 @@
         <v>45</v>
       </c>
       <c r="B33" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$83,$A33)</f>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A33)</f>
         <v>25</v>
       </c>
       <c r="C33" s="11" t="s">
@@ -3857,7 +3904,7 @@
         <v>47</v>
       </c>
       <c r="B34" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$83,$A34)</f>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A34)</f>
         <v>25</v>
       </c>
       <c r="C34" s="11" t="s">
@@ -3890,7 +3937,7 @@
         <v>51</v>
       </c>
       <c r="B38" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$83,$A38)</f>
+        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$84,$A38)</f>
         <v>5</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -3907,7 +3954,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$83,$A39)</f>
+        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$84,$A39)</f>
         <v>35</v>
       </c>
       <c r="C39" s="11" t="s">
@@ -3924,8 +3971,8 @@
         <v>55</v>
       </c>
       <c r="B40" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$83,$A40)</f>
-        <v>42</v>
+        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$84,$A40)</f>
+        <v>43</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>56</v>
@@ -3957,12 +4004,12 @@
         <v>61</v>
       </c>
       <c r="B44" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$22,$A44)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A44)</f>
+        <v>8</v>
       </c>
       <c r="C44" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$22,$A44,'Potential Defects'!$I$2:$I$22,"Reproduced")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A44,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3970,11 +4017,11 @@
         <v>62</v>
       </c>
       <c r="B45" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$22,$A45)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A45)</f>
         <v>6</v>
       </c>
       <c r="C45" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$22,$A45,'Potential Defects'!$I$2:$I$22,"Reproduced")</f>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A45,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
         <v>6</v>
       </c>
     </row>
@@ -3983,11 +4030,11 @@
         <v>63</v>
       </c>
       <c r="B46" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$22,$A46)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A46)</f>
         <v>4</v>
       </c>
       <c r="C46" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$22,$A46,'Potential Defects'!$I$2:$I$22,"Reproduced")</f>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A46,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
         <v>3</v>
       </c>
     </row>
@@ -3996,11 +4043,11 @@
         <v>64</v>
       </c>
       <c r="B47" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$22,$A47)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A47)</f>
         <v>4</v>
       </c>
       <c r="C47" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$22,$A47,'Potential Defects'!$I$2:$I$22,"Reproduced")</f>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A47,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
         <v>2</v>
       </c>
     </row>
@@ -4010,11 +4057,11 @@
       </c>
       <c r="B48" s="8" t="n">
         <f aca="false">SUM(B44:B47)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C48" s="8" t="n">
         <f aca="false">SUM(C44:C47)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4192,8 +4239,24 @@
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
     </row>
+    <row r="65" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -4216,6 +4279,7 @@
     <mergeCell ref="C62:H62"/>
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="C64:H64"/>
+    <mergeCell ref="C65:H65"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4232,7 +4296,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -4258,19 +4322,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>78</v>
@@ -4279,54 +4343,54 @@
         <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -4341,16 +4405,16 @@
         <v>53</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>18</v>
@@ -4363,21 +4427,21 @@
       <c r="Q2" s="12"/>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>23</v>
@@ -4392,16 +4456,16 @@
         <v>53</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -4414,12 +4478,12 @@
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -4428,7 +4492,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>23</v>
@@ -4443,16 +4507,16 @@
         <v>53</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>45</v>
@@ -4465,12 +4529,12 @@
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -4479,7 +4543,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>23</v>
@@ -4494,22 +4558,22 @@
         <v>51</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>34</v>
@@ -4518,16 +4582,16 @@
         <v>86</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
@@ -4536,7 +4600,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>23</v>
@@ -4551,16 +4615,16 @@
         <v>53</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>45</v>
@@ -4573,12 +4637,12 @@
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
@@ -4587,7 +4651,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>23</v>
@@ -4602,16 +4666,16 @@
         <v>53</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
@@ -4624,12 +4688,12 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>20</v>
@@ -4638,7 +4702,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>23</v>
@@ -4653,16 +4717,16 @@
         <v>53</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>18</v>
@@ -4675,12 +4739,12 @@
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>20</v>
@@ -4689,7 +4753,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>23</v>
@@ -4704,16 +4768,16 @@
         <v>53</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
@@ -4726,12 +4790,12 @@
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
       <c r="S9" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>20</v>
@@ -4740,7 +4804,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>23</v>
@@ -4755,16 +4819,16 @@
         <v>53</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>18</v>
@@ -4777,12 +4841,12 @@
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>20</v>
@@ -4791,7 +4855,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>23</v>
@@ -4806,16 +4870,16 @@
         <v>53</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
@@ -4828,12 +4892,12 @@
       <c r="Q11" s="14"/>
       <c r="R11" s="14"/>
       <c r="S11" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>20</v>
@@ -4842,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
@@ -4857,16 +4921,16 @@
         <v>55</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>47</v>
@@ -4878,15 +4942,15 @@
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
       <c r="R12" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>20</v>
@@ -4895,7 +4959,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>23</v>
@@ -4910,16 +4974,16 @@
         <v>55</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>47</v>
@@ -4932,12 +4996,12 @@
       <c r="Q13" s="14"/>
       <c r="R13" s="14"/>
       <c r="S13" s="15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>20</v>
@@ -4946,7 +5010,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>23</v>
@@ -4961,16 +5025,16 @@
         <v>55</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>47</v>
@@ -4983,12 +5047,12 @@
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>20</v>
@@ -4997,7 +5061,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>24</v>
@@ -5012,16 +5076,16 @@
         <v>55</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>45</v>
@@ -5034,12 +5098,12 @@
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
       <c r="S15" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>20</v>
@@ -5048,7 +5112,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>23</v>
@@ -5063,16 +5127,16 @@
         <v>55</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>45</v>
@@ -5085,12 +5149,12 @@
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
       <c r="S16" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -5099,7 +5163,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>23</v>
@@ -5114,16 +5178,16 @@
         <v>55</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>47</v>
@@ -5136,12 +5200,12 @@
       <c r="Q17" s="14"/>
       <c r="R17" s="14"/>
       <c r="S17" s="15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>20</v>
@@ -5150,7 +5214,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
@@ -5165,16 +5229,16 @@
         <v>55</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>45</v>
@@ -5187,12 +5251,12 @@
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>20</v>
@@ -5201,7 +5265,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>24</v>
@@ -5216,16 +5280,16 @@
         <v>55</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>47</v>
@@ -5238,12 +5302,12 @@
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
       <c r="S19" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>20</v>
@@ -5252,7 +5316,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>23</v>
@@ -5267,16 +5331,16 @@
         <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>47</v>
@@ -5289,12 +5353,12 @@
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
       <c r="S20" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
@@ -5303,7 +5367,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -5318,16 +5382,16 @@
         <v>55</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>47</v>
@@ -5339,15 +5403,15 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5356,7 +5420,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>26</v>
@@ -5371,16 +5435,16 @@
         <v>55</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>47</v>
@@ -5392,15 +5456,15 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>20</v>
@@ -5409,7 +5473,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -5424,16 +5488,16 @@
         <v>51</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
@@ -5446,21 +5510,21 @@
       <c r="Q23" s="14"/>
       <c r="R23" s="14"/>
       <c r="S23" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>23</v>
@@ -5475,22 +5539,22 @@
         <v>53</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>34</v>
@@ -5499,25 +5563,25 @@
         <v>86</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -5532,22 +5596,22 @@
         <v>53</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>34</v>
@@ -5556,25 +5620,25 @@
         <v>86</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -5589,22 +5653,22 @@
         <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>38</v>
@@ -5613,21 +5677,21 @@
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>24</v>
@@ -5642,22 +5706,22 @@
         <v>55</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O27" s="14" t="s">
         <v>36</v>
@@ -5666,27 +5730,27 @@
         <v>86</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
@@ -5701,22 +5765,22 @@
         <v>55</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>36</v>
@@ -5725,27 +5789,27 @@
         <v>86</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>24</v>
@@ -5760,16 +5824,16 @@
         <v>55</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M29" s="15" t="s">
         <v>47</v>
@@ -5782,21 +5846,21 @@
       <c r="Q29" s="14"/>
       <c r="R29" s="14"/>
       <c r="S29" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>24</v>
@@ -5811,16 +5875,16 @@
         <v>55</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>47</v>
@@ -5832,24 +5896,24 @@
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
       <c r="R30" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>23</v>
@@ -5864,16 +5928,16 @@
         <v>53</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
@@ -5886,21 +5950,21 @@
       <c r="Q31" s="14"/>
       <c r="R31" s="14"/>
       <c r="S31" s="15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>24</v>
@@ -5915,16 +5979,16 @@
         <v>55</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M32" s="13" t="s">
         <v>45</v>
@@ -5937,12 +6001,12 @@
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
       <c r="S32" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>20</v>
@@ -5951,7 +6015,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
@@ -5966,16 +6030,16 @@
         <v>53</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>18</v>
@@ -5988,12 +6052,12 @@
       <c r="Q33" s="14"/>
       <c r="R33" s="14"/>
       <c r="S33" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>20</v>
@@ -6002,7 +6066,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>25</v>
@@ -6017,16 +6081,16 @@
         <v>53</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>18</v>
@@ -6039,21 +6103,21 @@
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>25</v>
@@ -6068,22 +6132,22 @@
         <v>55</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M35" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>36</v>
@@ -6092,27 +6156,27 @@
         <v>86</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S35" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>23</v>
@@ -6127,22 +6191,22 @@
         <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>34</v>
@@ -6151,25 +6215,25 @@
         <v>86</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>23</v>
@@ -6184,22 +6248,22 @@
         <v>55</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O37" s="14" t="s">
         <v>34</v>
@@ -6208,25 +6272,25 @@
         <v>86</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R37" s="14"/>
       <c r="S37" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>23</v>
@@ -6241,22 +6305,22 @@
         <v>55</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>36</v>
@@ -6265,27 +6329,27 @@
         <v>86</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>23</v>
@@ -6300,22 +6364,22 @@
         <v>55</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>36</v>
@@ -6324,27 +6388,27 @@
         <v>86</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>23</v>
@@ -6359,16 +6423,16 @@
         <v>53</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M40" s="13" t="s">
         <v>45</v>
@@ -6381,21 +6445,21 @@
       <c r="Q40" s="12"/>
       <c r="R40" s="12"/>
       <c r="S40" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>23</v>
@@ -6410,22 +6474,22 @@
         <v>51</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M41" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>34</v>
@@ -6434,27 +6498,27 @@
         <v>86</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>23</v>
@@ -6469,16 +6533,16 @@
         <v>53</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M42" s="13" t="s">
         <v>18</v>
@@ -6490,24 +6554,24 @@
       <c r="P42" s="12"/>
       <c r="Q42" s="12"/>
       <c r="R42" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>23</v>
@@ -6522,22 +6586,22 @@
         <v>53</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>34</v>
@@ -6546,25 +6610,25 @@
         <v>86</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R43" s="14"/>
       <c r="S43" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>23</v>
@@ -6579,22 +6643,22 @@
         <v>53</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M44" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O44" s="12" t="s">
         <v>34</v>
@@ -6603,25 +6667,25 @@
         <v>86</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>23</v>
@@ -6636,22 +6700,22 @@
         <v>55</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M45" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>36</v>
@@ -6660,27 +6724,27 @@
         <v>86</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R45" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>23</v>
@@ -6695,16 +6759,16 @@
         <v>55</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M46" s="13" t="s">
         <v>47</v>
@@ -6717,21 +6781,21 @@
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
       <c r="S46" s="13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -6746,22 +6810,22 @@
         <v>55</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>36</v>
@@ -6770,27 +6834,27 @@
         <v>86</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>23</v>
@@ -6805,22 +6869,22 @@
         <v>53</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>34</v>
@@ -6829,25 +6893,25 @@
         <v>86</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>23</v>
@@ -6862,16 +6926,16 @@
         <v>53</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M49" s="15" t="s">
         <v>45</v>
@@ -6884,21 +6948,21 @@
       <c r="Q49" s="14"/>
       <c r="R49" s="14"/>
       <c r="S49" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>23</v>
@@ -6913,22 +6977,22 @@
         <v>53</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M50" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>34</v>
@@ -6937,25 +7001,25 @@
         <v>86</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R50" s="12"/>
       <c r="S50" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>23</v>
@@ -6970,16 +7034,16 @@
         <v>53</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M51" s="15" t="s">
         <v>45</v>
@@ -6992,21 +7056,21 @@
       <c r="Q51" s="14"/>
       <c r="R51" s="14"/>
       <c r="S51" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
@@ -7021,22 +7085,22 @@
         <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M52" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>34</v>
@@ -7045,25 +7109,25 @@
         <v>86</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>26</v>
@@ -7078,16 +7142,16 @@
         <v>51</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M53" s="15" t="s">
         <v>45</v>
@@ -7100,21 +7164,21 @@
       <c r="Q53" s="14"/>
       <c r="R53" s="14"/>
       <c r="S53" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>27</v>
@@ -7129,16 +7193,16 @@
         <v>55</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M54" s="13" t="s">
         <v>18</v>
@@ -7151,21 +7215,21 @@
       <c r="Q54" s="12"/>
       <c r="R54" s="12"/>
       <c r="S54" s="13" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>23</v>
@@ -7180,16 +7244,16 @@
         <v>53</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M55" s="15" t="s">
         <v>45</v>
@@ -7202,21 +7266,21 @@
       <c r="Q55" s="14"/>
       <c r="R55" s="14"/>
       <c r="S55" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -7231,16 +7295,16 @@
         <v>53</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M56" s="13" t="s">
         <v>45</v>
@@ -7253,21 +7317,21 @@
       <c r="Q56" s="12"/>
       <c r="R56" s="12"/>
       <c r="S56" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>24</v>
@@ -7282,16 +7346,16 @@
         <v>55</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M57" s="15" t="s">
         <v>45</v>
@@ -7304,21 +7368,21 @@
       <c r="Q57" s="14"/>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>23</v>
@@ -7333,16 +7397,16 @@
         <v>55</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M58" s="13" t="s">
         <v>47</v>
@@ -7354,24 +7418,24 @@
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
       <c r="R58" s="12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="S58" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>23</v>
@@ -7386,22 +7450,22 @@
         <v>53</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M59" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O59" s="14" t="s">
         <v>34</v>
@@ -7410,25 +7474,25 @@
         <v>86</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>23</v>
@@ -7443,22 +7507,22 @@
         <v>51</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N60" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>34</v>
@@ -7467,27 +7531,27 @@
         <v>86</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>23</v>
@@ -7502,22 +7566,22 @@
         <v>53</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O61" s="14" t="s">
         <v>34</v>
@@ -7526,25 +7590,25 @@
         <v>86</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>23</v>
@@ -7559,22 +7623,22 @@
         <v>55</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M62" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>36</v>
@@ -7583,27 +7647,27 @@
         <v>86</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="S62" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>23</v>
@@ -7618,16 +7682,16 @@
         <v>53</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M63" s="15" t="s">
         <v>18</v>
@@ -7640,21 +7704,21 @@
       <c r="Q63" s="14"/>
       <c r="R63" s="14"/>
       <c r="S63" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>23</v>
@@ -7669,22 +7733,22 @@
         <v>55</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O64" s="12" t="s">
         <v>36</v>
@@ -7693,27 +7757,27 @@
         <v>86</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>23</v>
@@ -7728,22 +7792,22 @@
         <v>55</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O65" s="14" t="s">
         <v>36</v>
@@ -7752,27 +7816,27 @@
         <v>86</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="S65" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>23</v>
@@ -7787,22 +7851,22 @@
         <v>53</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M66" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O66" s="12" t="s">
         <v>34</v>
@@ -7811,27 +7875,27 @@
         <v>86</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>23</v>
@@ -7846,22 +7910,22 @@
         <v>53</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M67" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N67" s="15" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O67" s="14" t="s">
         <v>34</v>
@@ -7870,25 +7934,25 @@
         <v>86</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="15" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>23</v>
@@ -7903,22 +7967,22 @@
         <v>53</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N68" s="13" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>34</v>
@@ -7927,25 +7991,25 @@
         <v>86</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>23</v>
@@ -7960,22 +8024,22 @@
         <v>53</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O69" s="14" t="s">
         <v>34</v>
@@ -7984,25 +8048,25 @@
         <v>86</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="15" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>23</v>
@@ -8017,22 +8081,22 @@
         <v>55</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="13" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>36</v>
@@ -8041,27 +8105,27 @@
         <v>86</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R70" s="12" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>23</v>
@@ -8076,22 +8140,22 @@
         <v>55</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>36</v>
@@ -8100,27 +8164,27 @@
         <v>86</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R71" s="14" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>23</v>
@@ -8135,22 +8199,22 @@
         <v>55</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>36</v>
@@ -8159,27 +8223,27 @@
         <v>86</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R72" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>23</v>
@@ -8194,22 +8258,22 @@
         <v>55</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M73" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="15" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>36</v>
@@ -8218,27 +8282,27 @@
         <v>86</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R73" s="14" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>23</v>
@@ -8253,22 +8317,22 @@
         <v>55</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O74" s="12" t="s">
         <v>36</v>
@@ -8277,27 +8341,27 @@
         <v>86</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R74" s="12" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>23</v>
@@ -8312,22 +8376,22 @@
         <v>55</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M75" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="15" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>36</v>
@@ -8336,27 +8400,27 @@
         <v>86</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R75" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>26</v>
@@ -8371,22 +8435,22 @@
         <v>55</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="13" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>36</v>
@@ -8395,27 +8459,27 @@
         <v>86</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R76" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="S76" s="13" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>24</v>
@@ -8430,22 +8494,22 @@
         <v>55</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="15" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>34</v>
@@ -8454,25 +8518,25 @@
         <v>86</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="15" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>23</v>
@@ -8487,16 +8551,16 @@
         <v>55</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M78" s="13" t="s">
         <v>47</v>
@@ -8509,21 +8573,21 @@
       <c r="Q78" s="12"/>
       <c r="R78" s="12"/>
       <c r="S78" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>24</v>
@@ -8538,22 +8602,22 @@
         <v>55</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M79" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="15" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>36</v>
@@ -8562,27 +8626,27 @@
         <v>86</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>24</v>
@@ -8597,22 +8661,22 @@
         <v>55</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M80" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O80" s="12" t="s">
         <v>36</v>
@@ -8621,27 +8685,27 @@
         <v>86</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R80" s="12" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="S80" s="13" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>25</v>
@@ -8656,22 +8720,22 @@
         <v>53</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M81" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>34</v>
@@ -8680,25 +8744,25 @@
         <v>86</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="15" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>25</v>
@@ -8713,16 +8777,16 @@
         <v>53</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>18</v>
@@ -8735,21 +8799,21 @@
       <c r="Q82" s="12"/>
       <c r="R82" s="12"/>
       <c r="S82" s="13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>25</v>
@@ -8764,22 +8828,22 @@
         <v>55</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M83" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="15" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>36</v>
@@ -8788,18 +8852,77 @@
         <v>86</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S83" s="15" t="s">
-        <v>601</v>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="L84" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="M84" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="N84" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="O84" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P84" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q84" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="R84" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="S84" s="13" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S83"/>
-  <conditionalFormatting sqref="O2:O83">
+  <autoFilter ref="A1:S84"/>
+  <conditionalFormatting sqref="O2:O84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$O2="Pass"</formula>
     </cfRule>
@@ -8810,33 +8933,33 @@
       <formula>$O2="Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G83">
+  <conditionalFormatting sqref="G2:G84">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$G2="P1"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E84" type="list">
       <formula1>"Functional,Security,API,Usability,Performance"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F84" type="list">
       <formula1>"Positive,Negative,Edge,Boundary"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G84" type="list">
       <formula1>"P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H84" type="list">
       <formula1>"Challenge brief,Observed behaviour,Assumed (common practice)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O84" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M84" type="list">
       <formula1>"Automated,Automated (known defect),Backlog,Manual"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8857,7 +8980,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -8873,57 +8996,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>60</v>
@@ -8931,28 +9054,28 @@
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>60</v>
@@ -8960,28 +9083,28 @@
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>60</v>
@@ -8989,28 +9112,28 @@
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>60</v>
@@ -9018,28 +9141,28 @@
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>60</v>
@@ -9047,86 +9170,86 @@
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>60</v>
@@ -9134,86 +9257,86 @@
     </row>
     <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>60</v>
@@ -9221,28 +9344,28 @@
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>60</v>
@@ -9250,28 +9373,28 @@
     </row>
     <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>60</v>
@@ -9279,57 +9402,57 @@
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>60</v>
@@ -9337,28 +9460,28 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>60</v>
@@ -9366,28 +9489,28 @@
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>60</v>
@@ -9395,28 +9518,28 @@
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>60</v>
@@ -9424,28 +9547,28 @@
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>60</v>
@@ -9453,28 +9576,28 @@
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>60</v>
@@ -9482,52 +9605,81 @@
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>714</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
+    <row r="23" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>728</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I23"/>
   <mergeCells count="1">
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A25:I25"/>
   </mergeCells>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$I2="Reproduced"</formula>
     </cfRule>
@@ -9536,11 +9688,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I22" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I23" type="list">
       <formula1>"Reproduced,To reproduce,Intermittent,Not reproducible"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C22" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C23" type="list">
       <formula1>"Defect,Potential defect – requirement to confirm,Security observation,UX / improvement suggestion"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9571,175 +9723,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>734</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>736</v>
+        <v>750</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>739</v>
+        <v>753</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>740</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>742</v>
+        <v>756</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>744</v>
+        <v>758</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>745</v>
+        <v>759</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>58</v>
@@ -9747,182 +9899,182 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>360</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>820</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>650</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>800</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>320</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>700</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="B34" s="20" t="n">
         <f aca="false">B21+B22</f>
         <v>1180</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
       <c r="B35" s="20" t="n">
         <f aca="false">B21*2</f>
         <v>720</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="B36" s="20" t="n">
         <f aca="false">B21*2+B22</f>
         <v>1540</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="B37" s="20" t="n">
         <f aca="false">B23*3</f>
         <v>1950</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="B38" s="20" t="n">
         <f aca="false">SUM(B21:B29)+B21</f>
         <v>6380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="814">
   <si>
     <t xml:space="preserve">DemoBlaze – Test Case Suite (Login &amp; Cart)</t>
   </si>
@@ -55,13 +55,13 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3 (20-Oct-2026)</t>
+    <t xml:space="preserve">1.4 (20-Oct-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Execution environment</t>
   </si>
   <si>
-    <t xml:space="preserve">Chromium – desktop, 19-Oct-2026. Demo automation runs on Chromium, Firefox and WebKit plus a mobile viewport.</t>
+    <t xml:space="preserve">Manual: Chromium – desktop, 19-Oct-2026. Automated: Chromium, Firefox, WebKit, Pixel 7 emulation and API, 20-Oct-2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Coverage by module and technique</t>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t xml:space="preserve">First full automated run on the live site found a new critical defect (PD-22: guests landing on a product page share one cart); added CRT-049. LGN-022 updated: DemoBlaze's mobile menu never collapses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test cases aligned with the automation scripts (steps, data, preconditions, expected results); automated results (88/88 on 20-Oct-2026) recorded per test case.</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -381,6 +387,12 @@
     <t xml:space="preserve">Alert 'Sign up successful.' is shown and the modal closes. Login with the new credentials shows 'Welcome qa_&lt;timestamp&gt;'.</t>
   </si>
   <si>
+    <t xml:space="preserve">'Sign up successful.' shown; the new account logged in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: Chromium, Firefox, WebKit</t>
+  </si>
+  <si>
     <t xml:space="preserve">tests/ui/auth/signup.spec.ts</t>
   </si>
   <si>
@@ -438,16 +450,17 @@
   </si>
   <si>
     <t xml:space="preserve">Username: {VALID_USER}
-Password: {VALID_PASSWORD}</t>
+Password: {VALID_PASSWORD}
+(Automation: throwaway account per worker by default; USER_STRATEGY=env uses {VALID_USER})</t>
   </si>
   <si>
     <t xml:space="preserve">Modal closes. Navbar shows 'Welcome {VALID_USER}' and 'Log out'; 'Log in' and 'Sign up' are hidden.</t>
   </si>
   <si>
-    <t xml:space="preserve">Logged in as qa_sy_01; navbar showed 'Welcome qa_sy_01' and 'Log out'; 'Log in' and 'Sign up' hidden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromium – desktop</t>
+    <t xml:space="preserve">'Welcome &lt;user&gt;' shown; Log in / Sign up hidden. (Also passed manually on 19-Oct with qa_sy_01.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: Chromium, Firefox, WebKit, Pixel 7</t>
   </si>
   <si>
     <t xml:space="preserve">tests/ui/auth/login.spec.ts</t>
@@ -468,6 +481,10 @@
 4. Click 'Log in'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Username: {VALID_USER}
+Password: {VALID_PASSWORD}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Page reloads on cart.html, shows 'Welcome {VALID_USER}' and lists {VALID_USER}'s cart item.</t>
   </si>
   <si>
@@ -490,6 +507,9 @@
     <t xml:space="preserve">Alert 'Wrong password.' is shown. Login modal stays open and the user remains logged out.</t>
   </si>
   <si>
+    <t xml:space="preserve">'Wrong password.' shown; modal stayed open; user stayed logged out.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-007</t>
   </si>
   <si>
@@ -509,6 +529,9 @@
     <t xml:space="preserve">Alert 'User does not exist.' is shown. User remains logged out.</t>
   </si>
   <si>
+    <t xml:space="preserve">'User does not exist.' shown; user stayed logged out.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-008</t>
   </si>
   <si>
@@ -528,6 +551,9 @@
     <t xml:space="preserve">Alert 'Please fill out Username and Password.' is shown. No POST /login request is sent (Network tab).</t>
   </si>
   <si>
+    <t xml:space="preserve">'Please fill out Username and Password.' shown; no /login request sent.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-009</t>
   </si>
   <si>
@@ -544,7 +570,7 @@
 Password: Test@1234</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Please fill out Username and Password.' is shown. User remains logged out.</t>
+    <t xml:space="preserve">Alert 'Please fill out Username and Password.' is shown. No POST /login request is sent. User remains logged out.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-010</t>
@@ -808,7 +834,7 @@
     <t xml:space="preserve">Verify login works at mobile width</t>
   </si>
   <si>
-    <t xml:space="preserve">Account {VALID_USER} exists; user is logged out. Browser viewport is 375 x 812 (mobile emulation).</t>
+    <t xml:space="preserve">Account {VALID_USER} exists; user is logged out. Mobile emulation: Pixel 7 (412 x 915).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
@@ -820,6 +846,12 @@
     <t xml:space="preserve">The mobile menu toggle is shown and 'Log in' is reachable. After login, the menu shows 'Welcome {VALID_USER}' and 'Log out'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Menu toggle shown; logged in from the mobile menu; 'Welcome' and 'Log out' shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: Pixel 7 (mobile Chromium)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-023</t>
   </si>
   <si>
@@ -839,7 +871,7 @@
     <t xml:space="preserve">User stays logged in; navbar still shows 'Welcome {VALID_USER}'.</t>
   </si>
   <si>
-    <t xml:space="preserve">After refresh the navbar still showed 'Welcome qa_sy_01'.</t>
+    <t xml:space="preserve">Still 'Welcome &lt;user&gt;' after refresh.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/ui/auth/session.spec.ts</t>
@@ -863,6 +895,9 @@
     <t xml:space="preserve">'Welcome qa_sy_01' and 'Log out' shown on Home, product and Cart pages.</t>
   </si>
   <si>
+    <t xml:space="preserve">Chromium – desktop</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-025</t>
   </si>
   <si>
@@ -899,7 +934,7 @@
     <t xml:space="preserve">The token is random and opaque; decoding it does not reveal the username or any predictable value.</t>
   </si>
   <si>
-    <t xml:space="preserve">'cWFfc3lfMDExNzkzMDEx' decodes to 'qa_sy_011793011' (username + number).</t>
+    <t xml:space="preserve">Fails as expected (PD-18): token decodes to username + number.</t>
   </si>
   <si>
     <t xml:space="preserve">PD-18</t>
@@ -921,7 +956,7 @@
     <t xml:space="preserve">'tokenp_' has Secure and HttpOnly ticked, and document.cookie does not return it.</t>
   </si>
   <si>
-    <t xml:space="preserve">document.cookie returned 'tokenp_', so the cookie is not HttpOnly (it is set by JavaScript).</t>
+    <t xml:space="preserve">Fails as expected (PD-08): tokenp_ is set without Secure/HttpOnly.</t>
   </si>
   <si>
     <t xml:space="preserve">PD-08</t>
@@ -982,6 +1017,9 @@
     <t xml:space="preserve">User is taken to the Home page. Navbar shows 'Log in' and 'Sign up'; 'Welcome' and 'Log out' are hidden. Cookie 'tokenp_' is removed.</t>
   </si>
   <si>
+    <t xml:space="preserve">Returned to Home with logged-out navbar; tokenp_ cookie removed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-031</t>
   </si>
   <si>
@@ -1015,6 +1053,12 @@
     <t xml:space="preserve">HTTP 200. Response body starts with 'Auth_token: ' followed by a non-empty token.</t>
   </si>
   <si>
+    <t xml:space="preserve">HTTP 200; body 'Auth_token: &lt;token&gt;'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: API</t>
+  </si>
+  <si>
     <t xml:space="preserve">tests/api/auth.api.spec.ts</t>
   </si>
   <si>
@@ -1028,6 +1072,9 @@
   </si>
   <si>
     <t xml:space="preserve">Response body is {"errorMessage": "Wrong password."}; no 'Auth_token' is returned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body {"errorMessage": "Wrong password."}; no token.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-034</t>
@@ -1046,7 +1093,7 @@
     <t xml:space="preserve">HTTP 401 Unauthorized.</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 with body {"errorMessage":"Bad parameter, token malformed."}.</t>
+    <t xml:space="preserve">Fails as expected (PD-19): HTTP 200 + errorMessage instead of 401.</t>
   </si>
   <si>
     <t xml:space="preserve">PD-19</t>
@@ -1176,19 +1223,18 @@
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
 2. Click 'Samsung galaxy s6'.
-3. Note the cart Total (Cart page).
-4. Click 'Add to cart'.
-5. Accept the alert.
-6. Click 'Cart'.</t>
+3. Click 'Add to cart'.
+4. Accept the alert.
+5. Click 'Cart'.</t>
   </si>
   <si>
     <t xml:space="preserve">Product: Samsung galaxy s6 ($360)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Product added.' is shown. Cart has a new 'Samsung galaxy s6' row at 360 and the Total increases by 360.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alert 'Product added.'; each add created a new 'Samsung galaxy s6' row at 360; Total rose by 360 per add (to 1900).</t>
+    <t xml:space="preserve">Alert 'Product added.' is shown. Cart has one 'Samsung galaxy s6' row at 360; Total is 360.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Product added.'; one Samsung galaxy s6 row at 360; Total 360.</t>
   </si>
   <si>
     <t xml:space="preserve">PD-06</t>
@@ -1201,6 +1247,9 @@
   </si>
   <si>
     <t xml:space="preserve">Verify a guest can add a product to the cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged out; the journey starts on the Home page (where DemoBlaze creates the guest id).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
@@ -1213,7 +1262,10 @@
     <t xml:space="preserve">Product: Nokia lumia 1520 ($820)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Product added.' is shown (same text as for a logged-in user). Cart has a 'Nokia lumia 1520' row at 820.</t>
+    <t xml:space="preserve">An alert confirms the product was added. Cart has one 'Nokia lumia 1520' row at 820; Total is 820. (Guest alert wording differs from the logged-in text – tracked as PD-06, not part of this check.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item reached the guest's own cart (1 row, 820). Alert wording not asserted (PD-06).</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-008</t>
@@ -1234,7 +1286,7 @@
     <t xml:space="preserve">Both products are listed with their prices; Total equals the sum of the rows (1180).</t>
   </si>
   <si>
-    <t xml:space="preserve">'Nokia lumia 1520' (820) and 'Samsung galaxy s6' (360) listed; Total equalled the sum of the rows.</t>
+    <t xml:space="preserve">Both rows listed with their prices; Total 1180.</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-009</t>
@@ -1344,7 +1396,7 @@
     <t xml:space="preserve">The 'Samsung galaxy s6' row is removed, other rows remain, and the Total decreases by 360.</t>
   </si>
   <si>
-    <t xml:space="preserve">'Samsung galaxy s6' row removed, other rows kept; Total 1900 -&gt; 1540.</t>
+    <t xml:space="preserve">Samsung row removed, Nokia kept; Total 1180 -&gt; 820.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/ui/cart/cart-management.spec.ts</t>
@@ -1451,12 +1503,17 @@
     <t xml:space="preserve">Logged in as {VALID_USER}; cart has 5 items; broadband connection.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Go to {BASE_URL}.
-2. Click 'Cart' and start timing.
-3. Stop timing when all rows and the Total are displayed.</t>
+    <t xml:space="preserve">1. Go to {BASE_URL}/cart.html and start timing.
+2. Stop timing when all rows and the Total are displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">All rows and the Total are displayed within 3 seconds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cart ready in 2957 ms with 5 items (budget 3000 ms); DOMContentLoaded 580 ms, load 1033 ms. Only 43 ms headroom: the cart calls /view once per item, so load time grows with cart size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: Chromium (perf)</t>
   </si>
   <si>
     <t xml:space="preserve">tests/perf/cart-page.perf.spec.ts</t>
@@ -1565,7 +1622,7 @@
     <t xml:space="preserve">Modal 'Place order' shows 'Total: 1180', fields Name, Country, City, Credit card, Month, Year, and 'Close' and 'Purchase' buttons.</t>
   </si>
   <si>
-    <t xml:space="preserve">Modal showed 'Total: 1180' and all 6 fields with 'Close' and 'Purchase'.</t>
+    <t xml:space="preserve">Modal showed 'Total: 1180', all 6 fields, Close and Purchase.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/ui/checkout/place-order.spec.ts</t>
@@ -1575,14 +1632,48 @@
   </si>
   <si>
     <t xml:space="preserve">Verify a logged-in user can place an order with valid details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to {BASE_URL}.
+2. Open 'Samsung galaxy s6', click 'Add to cart' and accept the alert.
+3. Click 'Home', open 'Nokia lumia 1520', click 'Add to cart' and accept the alert.
+4. Click 'Cart' and check both rows and Total 1180.
+5. Click 'Place Order' and check the modal shows 'Total: 1180'.
+6. Fill all fields with the test data.
+7. Click 'Purchase'.
+8. Click 'OK'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: Samsung galaxy s6, Nokia lumia 1520
+Name: Wong Test
+Country: Malaysia
+City: Kuala Lumpur
+Card: 4111111111111111
+Month: 10
+Year: 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Thank you for your purchase!' shows an Id, 'Amount: 1180 USD', the card number and the name entered. 'OK' returns to the Home page. (Date is checked in CRT-027.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full UI journey: cart Total 1180; modal 'Total: 1180'; receipt 'Amount: 1180 USD', card and name as entered; OK returned to Home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the cart is empty after a successful order</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
 2. Click 'Cart' in the navbar.
 3. Click 'Place Order'.
-4. Fill all fields with the test data.
-5. Click 'Purchase'.
-6. Click 'OK'.</t>
+4. Fill all fields with the test data and click 'Purchase'.
+5. Click 'OK'.
+6. Click 'Cart'.</t>
   </si>
   <si>
     <t xml:space="preserve">Name: Wong Test
@@ -1593,104 +1684,84 @@
 Year: 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">'Thank you for your purchase!' shows an Id, 'Amount: 1180 USD', the card number and the name entered. 'OK' returns to the Home page. (Date is checked in CRT-027.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmation: Id 7999627, 'Amount: 1180 USD', card and name as entered; 'OK' returned to index.html.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRT-026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify the cart is empty after a successful order</t>
+    <t xml:space="preserve">The cart table has no rows, and the server-side cart (/viewcart) is empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cart empty on the server and in the UI after purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the confirmation shows today's date</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
 2. Click 'Cart' in the navbar.
 3. Click 'Place Order'.
-4. Fill Name and Credit card and click 'Purchase'.
-5. Click 'OK'.
-6. Click 'Cart'.</t>
+4. Fill all fields with the test data and click 'Purchase'.
+5. Read the 'Date' line on the confirmation.</t>
   </si>
   <si>
     <t xml:space="preserve">Name: Wong Test
-Card: 4111111111111111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cart table has no rows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart had no rows after the purchase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRT-027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify the confirmation shows today's date</t>
+Country: Malaysia
+City: Kuala Lumpur
+Card: 4111111111111111
+Month: 10
+Year: 2027
+Expected date: today (D/M/YYYY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Date' equals today's date, including the correct month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fails as expected (PD-02): confirmation date shows the previous month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify a guest can place an order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged out; the journey starts on the Home page; guest cart is empty.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
-2. Click 'Cart' in the navbar.
-3. Click 'Place Order'.
-4. Fill Name and Credit card and click 'Purchase'.
-5. Read the 'Date' line on the confirmation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name: Wong Test
-Card: 4111111111111111
-Expected date: today (D/M/YYYY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Date' equals today's date, including the correct month.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchased on 19 Oct 2026; confirmation showed 'Date: 19/9/2026'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRT-028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify a guest can place an order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged out; guest cart has Nokia lumia 1520.</t>
+2. Open 'Nokia lumia 1520', click 'Add to cart' and accept the alert.
+3. Click 'Cart', then 'Place Order'.
+4. Fill all fields with the test data.
+5. Click 'Purchase'.
+6. Click 'OK'.
+7. Click 'Cart'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation shows 'Amount: 820 USD'. Afterwards the guest cart has no rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt 'Amount: 820 USD'; guest cart empty afterwards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT-029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify an order cannot be placed with an empty cart</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
 2. Click 'Cart' in the navbar.
 3. Click 'Place Order'.
 4. Fill all fields with the test data.
-5. Click 'Purchase'.
-6. Click 'OK'.
-7. Click 'Cart'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmation shows 'Amount: 820 USD'. Afterwards the guest cart has no rows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRT-029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify an order cannot be placed with an empty cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to {BASE_URL}.
-2. Click 'Cart' in the navbar.
-3. Click 'Place Order'.
-4. Fill Name and Credit card.
 5. Click 'Purchase'.</t>
   </si>
   <si>
     <t xml:space="preserve">No purchase confirmation is shown; the user is told the cart is empty.</t>
   </si>
   <si>
-    <t xml:space="preserve">Order confirmed with 'Amount: 0 USD'.</t>
+    <t xml:space="preserve">Fails as expected (PD-01): confirmation shown for an empty cart.</t>
   </si>
   <si>
     <t xml:space="preserve">PD-01</t>
@@ -1762,7 +1833,7 @@
     <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.' is shown. Modal stays open; no order is placed; cart is unchanged.</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.'; modal stayed open; no order.</t>
+    <t xml:space="preserve">Alert shown; modal stayed open; no order; cart unchanged.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/ui/checkout/order-validation.spec.ts</t>
@@ -1785,12 +1856,6 @@
 Card: (empty)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.' is shown; no order is placed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.'; no order.</t>
-  </si>
-  <si>
     <t xml:space="preserve">CRT-034</t>
   </si>
   <si>
@@ -1940,6 +2005,9 @@
 Card: '   ' (3 spaces)</t>
   </si>
   <si>
+    <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.' is shown; no order is placed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Order placed; confirmation showed blank Name and Card Number.</t>
   </si>
   <si>
@@ -2011,6 +2079,10 @@
 5. Double-click 'Purchase'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Name: Wong Test
+Card: 4111111111111111</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exactly one confirmation (one order Id) is shown.</t>
   </si>
   <si>
@@ -2079,7 +2151,7 @@
     <t xml:space="preserve">Both calls return HTTP 200. /viewcart 'Items' contains an entry with prod_id 1 and the UUID sent.</t>
   </si>
   <si>
-    <t xml:space="preserve">/addtocart returned HTTP 200 (empty body); /viewcart listed the new prod_id.</t>
+    <t xml:space="preserve">Both calls HTTP 200; /viewcart lists the new item id with prod_id 1.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/api/cart.api.spec.ts</t>
@@ -2101,6 +2173,9 @@
     <t xml:space="preserve">The deleted id is no longer in the /viewcart 'Items'.</t>
   </si>
   <si>
+    <t xml:space="preserve">HTTP 200; deleted id no longer returned by /viewcart.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-048</t>
   </si>
   <si>
@@ -2117,7 +2192,7 @@
     <t xml:space="preserve">HTTP 404 Not Found.</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 with body {"errorMessage":"Not found."}.</t>
+    <t xml:space="preserve">Fails as expected (PD-19): HTTP 200 + 'Not found.' instead of 404.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/api/product.api.spec.ts</t>
@@ -2140,10 +2215,7 @@
     <t xml:space="preserve">The cart contains only the one 'Nokia lumia 1520' just added (the guest has a private cart keyed by a unique guest id).</t>
   </si>
   <si>
-    <t xml:space="preserve">Automated run: a guest who opened the product page directly saw 121-134 items in the cart, added by other guests. /addtocart was sent with an empty guest id.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromium, Firefox, WebKit</t>
+    <t xml:space="preserve">Fails as expected (PD-22): /addtocart sent with an empty guest id; the shared cart held 121-134 items from other guests.</t>
   </si>
   <si>
     <t xml:space="preserve">PD-22</t>
@@ -3371,7 +3443,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3514,7 +3586,7 @@
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3547,7 +3619,7 @@
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3580,7 +3652,7 @@
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">SUM(H11:H12)</f>
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3726,19 +3798,19 @@
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A23)</f>
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P1")</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P2")</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P3")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>35</v>
@@ -3766,7 +3838,7 @@
       </c>
       <c r="G24" s="10" t="n">
         <f aca="false">IFERROR(B23/(B23+B24),0)</f>
-        <v>0.487804878048781</v>
+        <v>0.618181818181818</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3796,19 +3868,19 @@
       </c>
       <c r="B26" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A26)</f>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P1")</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P2")</f>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P3")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4255,8 +4327,24 @@
       <c r="G65" s="11"/>
       <c r="H65" s="11"/>
     </row>
+    <row r="66" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -4280,6 +4368,7 @@
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="C64:H64"/>
     <mergeCell ref="C65:H65"/>
+    <mergeCell ref="C66:H66"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4322,19 +4411,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>78</v>
@@ -4343,54 +4432,54 @@
         <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -4405,43 +4494,49 @@
         <v>53</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="13"/>
+      <c r="N2" s="13" t="s">
+        <v>117</v>
+      </c>
       <c r="O2" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>23</v>
@@ -4456,16 +4551,16 @@
         <v>53</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>45</v>
@@ -4478,12 +4573,12 @@
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -4492,7 +4587,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>23</v>
@@ -4507,16 +4602,16 @@
         <v>53</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>45</v>
@@ -4529,12 +4624,12 @@
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -4543,7 +4638,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>23</v>
@@ -4558,40 +4653,40 @@
         <v>51</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
@@ -4600,7 +4695,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>23</v>
@@ -4615,16 +4710,16 @@
         <v>53</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>45</v>
@@ -4637,12 +4732,12 @@
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
@@ -4651,7 +4746,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>23</v>
@@ -4666,34 +4761,40 @@
         <v>53</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N7" s="15"/>
+      <c r="N7" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="O7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>20</v>
@@ -4702,7 +4803,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>23</v>
@@ -4717,34 +4818,40 @@
         <v>53</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="13"/>
+      <c r="N8" s="13" t="s">
+        <v>157</v>
+      </c>
       <c r="O8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="R8" s="12"/>
       <c r="S8" s="13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>20</v>
@@ -4753,7 +4860,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>23</v>
@@ -4768,34 +4875,40 @@
         <v>53</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="15"/>
+      <c r="N9" s="15" t="s">
+        <v>163</v>
+      </c>
       <c r="O9" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="R9" s="14"/>
       <c r="S9" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>20</v>
@@ -4804,7 +4917,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>23</v>
@@ -4819,34 +4932,40 @@
         <v>53</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="13"/>
+      <c r="N10" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="O10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="R10" s="12"/>
       <c r="S10" s="13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>20</v>
@@ -4855,7 +4974,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>23</v>
@@ -4870,34 +4989,40 @@
         <v>53</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N11" s="15"/>
+      <c r="N11" s="15" t="s">
+        <v>163</v>
+      </c>
       <c r="O11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="R11" s="14"/>
       <c r="S11" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>20</v>
@@ -4906,7 +5031,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
@@ -4921,16 +5046,16 @@
         <v>55</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>47</v>
@@ -4942,15 +5067,15 @@
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
       <c r="R12" s="12" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>20</v>
@@ -4959,7 +5084,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>23</v>
@@ -4974,16 +5099,16 @@
         <v>55</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>47</v>
@@ -4996,12 +5121,12 @@
       <c r="Q13" s="14"/>
       <c r="R13" s="14"/>
       <c r="S13" s="15" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>20</v>
@@ -5010,7 +5135,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>23</v>
@@ -5025,16 +5150,16 @@
         <v>55</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>47</v>
@@ -5047,12 +5172,12 @@
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="13" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>20</v>
@@ -5061,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>24</v>
@@ -5076,16 +5201,16 @@
         <v>55</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>45</v>
@@ -5098,12 +5223,12 @@
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
       <c r="S15" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>20</v>
@@ -5112,7 +5237,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>23</v>
@@ -5127,16 +5252,16 @@
         <v>55</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>45</v>
@@ -5149,12 +5274,12 @@
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
       <c r="S16" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -5163,7 +5288,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>23</v>
@@ -5178,16 +5303,16 @@
         <v>55</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>47</v>
@@ -5200,12 +5325,12 @@
       <c r="Q17" s="14"/>
       <c r="R17" s="14"/>
       <c r="S17" s="15" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>20</v>
@@ -5214,7 +5339,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
@@ -5229,16 +5354,16 @@
         <v>55</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>45</v>
@@ -5251,12 +5376,12 @@
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>20</v>
@@ -5265,7 +5390,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>24</v>
@@ -5280,16 +5405,16 @@
         <v>55</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>47</v>
@@ -5302,12 +5427,12 @@
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
       <c r="S19" s="15" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>20</v>
@@ -5316,7 +5441,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>23</v>
@@ -5331,16 +5456,16 @@
         <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>47</v>
@@ -5353,12 +5478,12 @@
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
       <c r="S20" s="13" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
@@ -5367,7 +5492,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -5382,16 +5507,16 @@
         <v>55</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>47</v>
@@ -5403,15 +5528,15 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="14" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5420,7 +5545,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>26</v>
@@ -5435,16 +5560,16 @@
         <v>55</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>47</v>
@@ -5456,15 +5581,15 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>20</v>
@@ -5473,7 +5598,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -5488,43 +5613,49 @@
         <v>51</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N23" s="15"/>
+      <c r="N23" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="O23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>241</v>
+      </c>
       <c r="R23" s="14"/>
       <c r="S23" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>23</v>
@@ -5539,49 +5670,49 @@
         <v>53</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>34</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -5596,22 +5727,22 @@
         <v>53</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>34</v>
@@ -5620,25 +5751,25 @@
         <v>86</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -5653,22 +5784,22 @@
         <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>38</v>
@@ -5677,21 +5808,21 @@
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>24</v>
@@ -5706,51 +5837,51 @@
         <v>55</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="O27" s="14" t="s">
         <v>36</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
@@ -5765,51 +5896,51 @@
         <v>55</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>36</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>24</v>
@@ -5824,16 +5955,16 @@
         <v>55</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="M29" s="15" t="s">
         <v>47</v>
@@ -5846,21 +5977,21 @@
       <c r="Q29" s="14"/>
       <c r="R29" s="14"/>
       <c r="S29" s="15" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>24</v>
@@ -5875,16 +6006,16 @@
         <v>55</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>47</v>
@@ -5896,24 +6027,24 @@
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
       <c r="R30" s="12" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>23</v>
@@ -5928,43 +6059,49 @@
         <v>53</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N31" s="15"/>
+      <c r="N31" s="15" t="s">
+        <v>292</v>
+      </c>
       <c r="O31" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P31" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q31" s="14" t="s">
+        <v>138</v>
+      </c>
       <c r="R31" s="14"/>
       <c r="S31" s="15" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>24</v>
@@ -5979,16 +6116,16 @@
         <v>55</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="M32" s="13" t="s">
         <v>45</v>
@@ -6001,12 +6138,12 @@
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
       <c r="S32" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>20</v>
@@ -6015,7 +6152,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
@@ -6030,34 +6167,40 @@
         <v>53</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N33" s="15"/>
+      <c r="N33" s="15" t="s">
+        <v>303</v>
+      </c>
       <c r="O33" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P33" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q33" s="14" t="s">
+        <v>304</v>
+      </c>
       <c r="R33" s="14"/>
       <c r="S33" s="15" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>20</v>
@@ -6066,7 +6209,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>25</v>
@@ -6081,43 +6224,49 @@
         <v>53</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N34" s="13"/>
+      <c r="N34" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="O34" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>304</v>
+      </c>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>25</v>
@@ -6132,51 +6281,51 @@
         <v>55</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="M35" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>36</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="S35" s="15" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>23</v>
@@ -6191,22 +6340,22 @@
         <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>34</v>
@@ -6215,25 +6364,25 @@
         <v>86</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>23</v>
@@ -6248,22 +6397,22 @@
         <v>55</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="M37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="O37" s="14" t="s">
         <v>34</v>
@@ -6272,25 +6421,25 @@
         <v>86</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R37" s="14"/>
       <c r="S37" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>23</v>
@@ -6305,22 +6454,22 @@
         <v>55</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>36</v>
@@ -6329,27 +6478,27 @@
         <v>86</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>23</v>
@@ -6364,22 +6513,22 @@
         <v>55</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>36</v>
@@ -6388,27 +6537,27 @@
         <v>86</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>23</v>
@@ -6423,16 +6572,16 @@
         <v>53</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="M40" s="13" t="s">
         <v>45</v>
@@ -6445,21 +6594,21 @@
       <c r="Q40" s="12"/>
       <c r="R40" s="12"/>
       <c r="S40" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>23</v>
@@ -6474,51 +6623,51 @@
         <v>51</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="M41" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>23</v>
@@ -6533,45 +6682,51 @@
         <v>53</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>111</v>
+        <v>362</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="M42" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N42" s="13"/>
+      <c r="N42" s="13" t="s">
+        <v>366</v>
+      </c>
       <c r="O42" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P42" s="12"/>
-      <c r="Q42" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="R42" s="12" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>23</v>
@@ -6586,49 +6741,49 @@
         <v>53</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="M43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R43" s="14"/>
       <c r="S43" s="15" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>23</v>
@@ -6643,22 +6798,22 @@
         <v>53</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="M44" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="O44" s="12" t="s">
         <v>34</v>
@@ -6667,25 +6822,25 @@
         <v>86</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>23</v>
@@ -6700,22 +6855,22 @@
         <v>55</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="M45" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>36</v>
@@ -6724,27 +6879,27 @@
         <v>86</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R45" s="14" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>23</v>
@@ -6759,16 +6914,16 @@
         <v>55</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="M46" s="13" t="s">
         <v>47</v>
@@ -6781,21 +6936,21 @@
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
       <c r="S46" s="13" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -6810,22 +6965,22 @@
         <v>55</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="M47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>36</v>
@@ -6834,27 +6989,27 @@
         <v>86</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>23</v>
@@ -6869,49 +7024,49 @@
         <v>53</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="M48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>34</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>23</v>
@@ -6926,16 +7081,16 @@
         <v>53</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="M49" s="15" t="s">
         <v>45</v>
@@ -6948,21 +7103,21 @@
       <c r="Q49" s="14"/>
       <c r="R49" s="14"/>
       <c r="S49" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>23</v>
@@ -6977,22 +7132,22 @@
         <v>53</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="M50" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>34</v>
@@ -7001,25 +7156,25 @@
         <v>86</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R50" s="12"/>
       <c r="S50" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>23</v>
@@ -7034,16 +7189,16 @@
         <v>53</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="M51" s="15" t="s">
         <v>45</v>
@@ -7056,21 +7211,21 @@
       <c r="Q51" s="14"/>
       <c r="R51" s="14"/>
       <c r="S51" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
@@ -7085,22 +7240,22 @@
         <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="M52" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>34</v>
@@ -7109,25 +7264,25 @@
         <v>86</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>26</v>
@@ -7142,16 +7297,16 @@
         <v>51</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="M53" s="15" t="s">
         <v>45</v>
@@ -7164,21 +7319,21 @@
       <c r="Q53" s="14"/>
       <c r="R53" s="14"/>
       <c r="S53" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>27</v>
@@ -7193,43 +7348,49 @@
         <v>55</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="M54" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N54" s="13"/>
+      <c r="N54" s="13" t="s">
+        <v>439</v>
+      </c>
       <c r="O54" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P54" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q54" s="12" t="s">
+        <v>440</v>
+      </c>
       <c r="R54" s="12"/>
       <c r="S54" s="13" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>23</v>
@@ -7244,16 +7405,16 @@
         <v>53</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="M55" s="15" t="s">
         <v>45</v>
@@ -7266,21 +7427,21 @@
       <c r="Q55" s="14"/>
       <c r="R55" s="14"/>
       <c r="S55" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -7295,16 +7456,16 @@
         <v>53</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="M56" s="13" t="s">
         <v>45</v>
@@ -7317,21 +7478,21 @@
       <c r="Q56" s="12"/>
       <c r="R56" s="12"/>
       <c r="S56" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>24</v>
@@ -7346,16 +7507,16 @@
         <v>55</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="M57" s="15" t="s">
         <v>45</v>
@@ -7368,21 +7529,21 @@
       <c r="Q57" s="14"/>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>23</v>
@@ -7397,16 +7558,16 @@
         <v>55</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="M58" s="13" t="s">
         <v>47</v>
@@ -7418,24 +7579,24 @@
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
       <c r="R58" s="12" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="S58" s="13" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>23</v>
@@ -7450,49 +7611,49 @@
         <v>53</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="M59" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="O59" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>23</v>
@@ -7507,51 +7668,51 @@
         <v>51</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>450</v>
+        <v>327</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="M60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N60" s="13" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>34</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>23</v>
@@ -7566,49 +7727,49 @@
         <v>53</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="O61" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>23</v>
@@ -7623,51 +7784,51 @@
         <v>55</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="M62" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="13" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>36</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="S62" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>23</v>
@@ -7682,43 +7843,49 @@
         <v>53</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="M63" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N63" s="15"/>
+      <c r="N63" s="15" t="s">
+        <v>499</v>
+      </c>
       <c r="O63" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P63" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q63" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="R63" s="14"/>
       <c r="S63" s="15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>23</v>
@@ -7733,51 +7900,51 @@
         <v>55</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="O64" s="12" t="s">
         <v>36</v>
       </c>
       <c r="P64" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>23</v>
@@ -7792,22 +7959,22 @@
         <v>55</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="M65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="O65" s="14" t="s">
         <v>36</v>
@@ -7816,27 +7983,27 @@
         <v>86</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="S65" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>23</v>
@@ -7851,22 +8018,22 @@
         <v>53</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="M66" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="13" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="O66" s="12" t="s">
         <v>34</v>
@@ -7875,27 +8042,27 @@
         <v>86</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>23</v>
@@ -7910,49 +8077,49 @@
         <v>53</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="M67" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N67" s="15" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="O67" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="15" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>23</v>
@@ -7967,49 +8134,49 @@
         <v>53</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="M68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N68" s="13" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>34</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>23</v>
@@ -8024,49 +8191,49 @@
         <v>53</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="O69" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="15" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>23</v>
@@ -8081,22 +8248,22 @@
         <v>55</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="13" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>36</v>
@@ -8105,27 +8272,27 @@
         <v>86</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R70" s="12" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>23</v>
@@ -8140,22 +8307,22 @@
         <v>55</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>36</v>
@@ -8164,27 +8331,27 @@
         <v>86</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R71" s="14" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>23</v>
@@ -8199,22 +8366,22 @@
         <v>55</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>36</v>
@@ -8223,27 +8390,27 @@
         <v>86</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R72" s="12" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>23</v>
@@ -8258,22 +8425,22 @@
         <v>55</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="M73" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="15" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>36</v>
@@ -8282,27 +8449,27 @@
         <v>86</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R73" s="14" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>23</v>
@@ -8317,22 +8484,22 @@
         <v>55</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="O74" s="12" t="s">
         <v>36</v>
@@ -8341,27 +8508,27 @@
         <v>86</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R74" s="12" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>23</v>
@@ -8376,22 +8543,22 @@
         <v>55</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="M75" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="15" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>36</v>
@@ -8400,27 +8567,27 @@
         <v>86</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R75" s="14" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>26</v>
@@ -8435,22 +8602,22 @@
         <v>55</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="13" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>36</v>
@@ -8459,27 +8626,27 @@
         <v>86</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R76" s="12" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="S76" s="13" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>24</v>
@@ -8494,22 +8661,22 @@
         <v>55</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="15" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>34</v>
@@ -8518,25 +8685,25 @@
         <v>86</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="15" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>23</v>
@@ -8551,16 +8718,16 @@
         <v>55</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>465</v>
+        <v>589</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="M78" s="13" t="s">
         <v>47</v>
@@ -8573,21 +8740,21 @@
       <c r="Q78" s="12"/>
       <c r="R78" s="12"/>
       <c r="S78" s="13" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>24</v>
@@ -8602,22 +8769,22 @@
         <v>55</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="M79" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="15" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>36</v>
@@ -8626,27 +8793,27 @@
         <v>86</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>24</v>
@@ -8661,22 +8828,22 @@
         <v>55</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>465</v>
+        <v>589</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="M80" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="O80" s="12" t="s">
         <v>36</v>
@@ -8685,27 +8852,27 @@
         <v>86</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="R80" s="12" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="S80" s="13" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>25</v>
@@ -8720,49 +8887,49 @@
         <v>53</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="M81" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="15" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>25</v>
@@ -8777,43 +8944,49 @@
         <v>53</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N82" s="13"/>
+      <c r="N82" s="13" t="s">
+        <v>617</v>
+      </c>
       <c r="O82" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P82" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q82" s="12" t="s">
+        <v>304</v>
+      </c>
       <c r="R82" s="12"/>
       <c r="S82" s="13" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>25</v>
@@ -8828,51 +9001,51 @@
         <v>55</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="M83" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="15" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>36</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="S83" s="15" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>24</v>
@@ -8887,22 +9060,22 @@
         <v>55</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="M84" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N84" s="13" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="O84" s="12" t="s">
         <v>36</v>
@@ -8911,13 +9084,13 @@
         <v>89</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>610</v>
+        <v>118</v>
       </c>
       <c r="R84" s="12" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="S84" s="13" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -8996,57 +9169,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>60</v>
@@ -9054,28 +9227,28 @@
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>60</v>
@@ -9083,28 +9256,28 @@
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>60</v>
@@ -9112,28 +9285,28 @@
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>60</v>
@@ -9141,28 +9314,28 @@
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>60</v>
@@ -9170,86 +9343,86 @@
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>60</v>
@@ -9257,86 +9430,86 @@
     </row>
     <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>60</v>
@@ -9344,28 +9517,28 @@
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>677</v>
+        <v>697</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>681</v>
+        <v>701</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>60</v>
@@ -9373,28 +9546,28 @@
     </row>
     <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>60</v>
@@ -9402,57 +9575,57 @@
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>60</v>
@@ -9460,28 +9633,28 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>60</v>
@@ -9489,28 +9662,28 @@
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>60</v>
@@ -9518,28 +9691,28 @@
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>60</v>
@@ -9547,28 +9720,28 @@
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>60</v>
@@ -9576,28 +9749,28 @@
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>60</v>
@@ -9605,28 +9778,28 @@
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>60</v>
@@ -9634,28 +9807,28 @@
     </row>
     <row r="23" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>60</v>
@@ -9663,7 +9836,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -9723,175 +9896,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>58</v>
@@ -9899,182 +10072,182 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>360</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>774</v>
+        <v>794</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>820</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>650</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>800</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>320</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>779</v>
+        <v>799</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>700</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>782</v>
+        <v>802</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>784</v>
+        <v>804</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>788</v>
+        <v>808</v>
       </c>
       <c r="B34" s="20" t="n">
         <f aca="false">B21+B22</f>
         <v>1180</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>790</v>
+        <v>810</v>
       </c>
       <c r="B35" s="20" t="n">
         <f aca="false">B21*2</f>
         <v>720</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>791</v>
+        <v>811</v>
       </c>
       <c r="B36" s="20" t="n">
         <f aca="false">B21*2+B22</f>
         <v>1540</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="B37" s="20" t="n">
         <f aca="false">B23*3</f>
         <v>1950</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="B38" s="20" t="n">
         <f aca="false">SUM(B21:B29)+B21</f>
         <v>6380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Potential Defects'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$I$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$I$28</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Test Cases'!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$S$84</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="860">
   <si>
     <t xml:space="preserve">DemoBlaze – Test Case Suite (Login &amp; Cart)</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4 (20-Oct-2026)</t>
+    <t xml:space="preserve">1.5 (20-Oct-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Execution environment</t>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t xml:space="preserve">Test cases aligned with the automation scripts (steps, data, preconditions, expected results); automated results (88/88 on 20-Oct-2026) recorded per test case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 more cases automated (60 in total; only CRT-011 stays manual among the previously not-run cases). Full run of 167 tests passed, 17 cases failing as expected; 5 new potential defects (PD-23 to PD-27).</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -418,7 +424,7 @@
     <t xml:space="preserve">Alert 'This user already exist.' is shown. Login with {VALID_PASSWORD} still works (existing account unchanged).</t>
   </si>
   <si>
-    <t xml:space="preserve">Automatable – lower priority for the demo; next sprint</t>
+    <t xml:space="preserve">'This user already exist.' shown; the existing account's password still works.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-003</t>
@@ -435,6 +441,12 @@
   </si>
   <si>
     <t xml:space="preserve">Modal 'Log in' opens with Username and Password fields and 'Close' and 'Log in' buttons. Password input is masked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal 'Log in' with Username, masked Password, Close and Log in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/ui/auth/login.spec.ts</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-004</t>
@@ -463,9 +475,6 @@
     <t xml:space="preserve">Automated: Chromium, Firefox, WebKit, Pixel 7</t>
   </si>
   <si>
-    <t xml:space="preserve">tests/ui/auth/login.spec.ts</t>
-  </si>
-  <si>
     <t xml:space="preserve">LGN-005</t>
   </si>
   <si>
@@ -488,6 +497,9 @@
     <t xml:space="preserve">Page reloads on cart.html, shows 'Welcome {VALID_USER}' and lists {VALID_USER}'s cart item.</t>
   </si>
   <si>
+    <t xml:space="preserve">Page reloaded on cart.html with 'Welcome &lt;user&gt;' and the user's cart item listed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-006</t>
   </si>
   <si>
@@ -608,10 +620,10 @@
     <t xml:space="preserve">Alert 'Please fill out Username and Password.' is shown. No POST /login request is sent.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-05): spaces-only input was sent to the server instead of being blocked.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PD-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected result is an assumed requirement – confirm with PO before automating</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-012</t>
@@ -633,7 +645,10 @@
     <t xml:space="preserve">Login succeeds and the navbar shows 'Welcome {VALID_USER}' (no spaces).</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumed requirement – confirm with PO before automating</t>
+    <t xml:space="preserve">Fails as expected (PD-26): ' &lt;username&gt; ' with spaces gave 'User does not exist.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-26</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-013</t>
@@ -655,6 +670,12 @@
     <t xml:space="preserve">Login succeeds and the navbar shows 'Welcome {VALID_USER}'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-27): username in upper case gave 'User does not exist.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-014</t>
   </si>
   <si>
@@ -672,6 +693,9 @@
   </si>
   <si>
     <t xml:space="preserve">Alert 'Wrong password.' is shown. User remains logged out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password with inverted case gave 'Wrong password.'</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-015</t>
@@ -709,6 +733,34 @@
     <t xml:space="preserve">Sign up succeeds and login shows 'Welcome qa_uni_&lt;timestamp&gt;'.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Signed up and logged in with password 'Pässwörd_#$%_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">密码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-016</t>
   </si>
   <si>
@@ -721,14 +773,14 @@
 4. Click 'Log in'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Username: 'a' x 300
+    <t xml:space="preserve">Username: unique 300-character value (qa_long_&lt;timestamp&gt; padded with 'a')
 Password: Test@1234</t>
   </si>
   <si>
     <t xml:space="preserve">Alert 'User does not exist.' is shown. No JavaScript error in the Console; the page stays usable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Needs human judgement of console errors and page usability</t>
+    <t xml:space="preserve">Unique 300-character username: 'User does not exist.', no JavaScript errors. Note: the username 'a' x 300 is already registered by someone, so sign-up accepts 300-character usernames.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-017</t>
@@ -747,13 +799,22 @@
 Password: ' OR '1'='1</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'User does not exist.' is shown. User remains logged out; no server error.</t>
+    <t xml:space="preserve">Login is rejected with an error alert and the user remains logged out (no bypass, no server error).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Injection string rejected with a normal login error; user stayed logged out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/security/login-security.spec.ts</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-018</t>
   </si>
   <si>
     <t xml:space="preserve">Verify repeated failed logins trigger a lockout or rate limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A dedicated test account exists (automation uses a throwaway account, so a lockout affects no one else); user is logged out.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
@@ -764,7 +825,10 @@
     <t xml:space="preserve">After the configured threshold (e.g. 5 attempts, to confirm with PO), further attempts are blocked with a lockout, CAPTCHA or rate-limit message.</t>
   </si>
   <si>
-    <t xml:space="preserve">Destructive: would lock shared accounts on a public site; belongs in a security test plan</t>
+    <t xml:space="preserve">Fails as expected (PD-25): the 10th consecutive wrong password still returned 'Wrong password.' – no lockout or rate limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-25</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-019</t>
@@ -781,7 +845,10 @@
     <t xml:space="preserve">User is logged in ('Welcome {VALID_USER}'). Only one POST /login request is sent; no error alert.</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing race (double-click) – non-deterministic, would be flaky</t>
+    <t xml:space="preserve">Fails as expected (PD-23): double-click sent two POST /login requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-23</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-020</t>
@@ -798,10 +865,10 @@
     <t xml:space="preserve">Login is submitted and the navbar shows 'Welcome {VALID_USER}'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-10): Enter in the Password field did not submit the form.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PD-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyboard UX, assumed requirement – manual exploratory check</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-021</t>
@@ -822,10 +889,10 @@
     <t xml:space="preserve">Modal closes and the user remains logged out. When reopened, Username and Password are empty.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-11): reopened Login modal still contained the typed values.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PD-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UX, assumed requirement – manual exploratory check</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-022</t>
@@ -898,6 +965,9 @@
     <t xml:space="preserve">Chromium – desktop</t>
   </si>
   <si>
+    <t xml:space="preserve">Automatable – lower priority for the demo; next sprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGN-025</t>
   </si>
   <si>
@@ -915,10 +985,7 @@
     <t xml:space="preserve">An error tells the user the session is invalid, and the navbar shows 'Log in' and 'Sign up' (logged-out state).</t>
   </si>
   <si>
-    <t xml:space="preserve">Partial: only checked at API level (/check with an invalid token returned 'Bad parameter, token malformed.'). UI steps not yet run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevTools cookie tampering – manual security check (automatable later)</t>
+    <t xml:space="preserve">Alert 'Bad parameter, token malformed.'; navbar returned to the logged-out state.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-026</t>
@@ -977,7 +1044,7 @@
     <t xml:space="preserve">The request URL starts with https:// (https://api.demoblaze.com/login).</t>
   </si>
   <si>
-    <t xml:space="preserve">Transport-security inspection – better covered by a DAST/proxy tool</t>
+    <t xml:space="preserve">POST https://api.demoblaze.com/login (HTTPS).</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-029</t>
@@ -995,10 +1062,10 @@
     <t xml:space="preserve">The request body does not contain the password in plain text or a reversible encoding such as Base64.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-07): request body contains the password Base64-encoded.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PD-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request-body inspection – better covered by a DAST/proxy tool</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-030</t>
@@ -1033,6 +1100,9 @@
   </si>
   <si>
     <t xml:space="preserve">After refresh the navbar shows 'Log in' and 'Sign up'; no 'Welcome {VALID_USER}'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back + refresh after logout showed the logged-out navbar.</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-032</t>
@@ -1212,6 +1282,12 @@
     <t xml:space="preserve">Cart has one 'Sony vaio i5' row at 790; Total is 790.</t>
   </si>
   <si>
+    <t xml:space="preserve">Laptops filter showed only laptops; Sony vaio i5 added; cart 1 row at 790.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/ui/cart/add-to-cart.spec.ts</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-006</t>
   </si>
   <si>
@@ -1240,9 +1316,6 @@
     <t xml:space="preserve">PD-06</t>
   </si>
   <si>
-    <t xml:space="preserve">tests/ui/cart/add-to-cart.spec.ts</t>
-  </si>
-  <si>
     <t xml:space="preserve">CRT-007</t>
   </si>
   <si>
@@ -1351,7 +1424,7 @@
     <t xml:space="preserve">Cart has 3 'Nexus 6' rows; Total is 1950. No error alerts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing race (rapid clicks) – non-deterministic, would be flaky</t>
+    <t xml:space="preserve">Result depends on the intermittent lost-items defect (PD-14), so an automated test would pass or fail at random</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-012</t>
@@ -1417,6 +1490,9 @@
   </si>
   <si>
     <t xml:space="preserve">No rows remain in the cart table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both items deleted one by one; cart table empty.</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-015</t>
@@ -1457,6 +1533,9 @@
     <t xml:space="preserve">Cart lists 10 rows; Total equals the sum of the 10 prices (6380).</t>
   </si>
   <si>
+    <t xml:space="preserve">10 rows listed; Total 6380.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-017</t>
   </si>
   <si>
@@ -1494,6 +1573,9 @@
     <t xml:space="preserve">Rows, Total and 'Place Order' are visible without horizontal scrolling; all modal fields and buttons can be used.</t>
   </si>
   <si>
+    <t xml:space="preserve">No horizontal scrolling; rows, Total and Place Order visible; modal fields usable; Purchase and Close in view.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-019</t>
   </si>
   <si>
@@ -1510,7 +1592,7 @@
     <t xml:space="preserve">All rows and the Total are displayed within 3 seconds.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart ready in 2957 ms with 5 items (budget 3000 ms); DOMContentLoaded 580 ms, load 1033 ms. Only 43 ms headroom: the cart calls /view once per item, so load time grows with cart size.</t>
+    <t xml:space="preserve">Cart ready in 2803 ms with 5 items (budget 3000 ms) in the latest run; 2957 ms the run before. Little headroom: the cart calls /view once per item, so load time grows with cart size.</t>
   </si>
   <si>
     <t xml:space="preserve">Automated: Chromium (perf)</t>
@@ -1540,6 +1622,12 @@
     <t xml:space="preserve">The 'Samsung galaxy s6' row is still in the cart.</t>
   </si>
   <si>
+    <t xml:space="preserve">Item still in the cart after logging out and back in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests/ui/cart/cart-persistence.spec.ts</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-021</t>
   </si>
   <si>
@@ -1554,13 +1642,16 @@
     <t xml:space="preserve">None of {VALID_USER}'s items are shown in the guest cart.</t>
   </si>
   <si>
+    <t xml:space="preserve">Guest cart after logout was empty.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-022</t>
   </si>
   <si>
     <t xml:space="preserve">Verify a user cannot see another user's cart items</t>
   </si>
   <si>
-    <t xml:space="preserve">{VALID_USER}'s cart has Samsung galaxy s6. {USER_B}'s cart is empty. User is logged out.</t>
+    <t xml:space="preserve">{VALID_USER}'s cart has Samsung galaxy s6. A second account {USER_B} exists with an empty cart (automation creates it). User is logged out.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Go to {BASE_URL}.
@@ -1573,6 +1664,9 @@
   </si>
   <si>
     <t xml:space="preserve">{USER_B}'s cart is empty; no items from {VALID_USER} are shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second user's cart was empty; user A's item not visible.</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-023</t>
@@ -1596,10 +1690,10 @@
     <t xml:space="preserve">The 'HTC One M9' row added as a guest is in {VALID_USER}'s cart.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-09): item added as a guest was not in the cart after login.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PD-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumed requirement (cart merge) – confirm with PO</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-024</t>
@@ -2086,6 +2180,12 @@
     <t xml:space="preserve">Exactly one confirmation (one order Id) is shown.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fails as expected (PD-24): double-click sent two order submissions (POST /deletecart twice).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRT-044</t>
   </si>
   <si>
@@ -2336,7 +2436,7 @@
     <t xml:space="preserve">Treated as empty and rejected client-side.</t>
   </si>
   <si>
-    <t xml:space="preserve">Input is not trimmed, so the check passes (login request is sent; purchase succeeds). Reproduced on Place Order (spaces-only Name/Card accepted). Login side still to check.</t>
+    <t xml:space="preserve">Input is not trimmed, so the check passes (login request is sent; purchase succeeds). Reproduced on Place Order (spaces-only Name/Card accepted). Login side still to check. Login side (LGN-011) reproduced by the automated run on 20-Oct-2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Inconsistent 'Product added' alert text</t>
@@ -2376,7 +2476,7 @@
     <t xml:space="preserve">Password protected by HTTPS only and never stored/sent in a reversible encoding.</t>
   </si>
   <si>
-    <t xml:space="preserve">Password is only Base64-encoded in the JSON body; anyone who sees the body can decode it.</t>
+    <t xml:space="preserve">Password is only Base64-encoded in the JSON body; anyone who sees the body can decode it. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
     <t xml:space="preserve">Auth cookie lacks Secure/HttpOnly flags</t>
@@ -2407,7 +2507,7 @@
     <t xml:space="preserve">Guest items merged into user cart.</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest and user carts are separate; guest items are not shown.</t>
+    <t xml:space="preserve">Guest and user carts are separate; guest items are not shown. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
     <t xml:space="preserve">Enter key does not submit the Login form</t>
@@ -2424,7 +2524,7 @@
     <t xml:space="preserve">Login submitted.</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected: nothing happens (form has no submit button). Confirm by execution.</t>
+    <t xml:space="preserve">Expected: nothing happens (form has no submit button). Confirm by execution. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
     <t xml:space="preserve">Modal fields keep previous values after closing</t>
@@ -2442,7 +2542,7 @@
     <t xml:space="preserve">Fields cleared.</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected: previous values remain. Confirm by execution. Reproduced on Place Order modal (Name kept after Close).</t>
+    <t xml:space="preserve">Expected: previous values remain. Confirm by execution. Reproduced on Place Order modal (Name kept after Close). Login modal (LGN-021) reproduced by the automated run on 20-Oct-2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Order ID generated client-side and not persisted</t>
@@ -2618,6 +2718,82 @@
   </si>
   <si>
     <t xml:space="preserve">Only the Home page creates the guest id cookie ('user'). A guest who lands on a product page first (search result, shared link) sends an empty id, so all such guests read and write the same cart: our test saw 121-134 items from other people. Privacy issue: one guest can see, and buy, another guest's items. Reproduced 20-Oct-2026 by the automated run on Chromium, Firefox and WebKit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double-clicking 'Log in' sends two login requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Log in and enter valid credentials.
+2. Open DevTools &gt; Network.
+3. Double-click 'Log in'.
+4. Count POST /login requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One login request per submit (button disabled while the request is in flight).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A double-click calls logIn() twice and sends two POST /login requests. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double-clicking 'Purchase' submits the order twice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add an item to the cart and open Place Order.
+2. Fill Name and Credit card.
+3. Open DevTools &gt; Network.
+4. Double-click 'Purchase'.
+5. Count POST /deletecart requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One order per submit (Purchase disabled after the first click).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A double-click runs purchaseOrder() twice: two order submissions (POST /deletecart twice) and the confirmation is regenerated. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No lockout or rate limit after repeated failed logins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High (Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Use a test account.
+2. Enter a wrong password and click 'Log in' 10 times in a row.
+3. Check the message on the last attempts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After a small number of failed attempts, further attempts are blocked or delayed (lockout, CAPTCHA or rate limit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 consecutive wrong passwords all returned 'Wrong password.'; nothing slows down or blocks guessing, so passwords can be brute-forced. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login does not trim spaces around the username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Log in.
+2. Enter a valid username with a space before and after it, and the correct password.
+3. Click 'Log in'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leading/trailing spaces are ignored, as most sites do.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">' &lt;username&gt; ' with surrounding spaces returns 'User does not exist.' Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login treats the username as case-sensitive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Log in.
+2. Enter a valid username in UPPER CASE and the correct password.
+3. Click 'Log in'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username matching is case-insensitive (to confirm with the product owner).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The username in upper case returns 'User does not exist.' Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
     <t xml:space="preserve">Note: DemoBlaze has no published requirements. 'Expected' follows common e-commerce practice, so 'Potential defect – requirement to confirm' items should be agreed with the product owner before being raised as bugs. 'Reproduced?' = observed when the related test was run on 19-Oct-2026.</t>
@@ -3443,7 +3619,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3582,11 +3758,11 @@
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$M$2:$M$84,"Automated*")</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3615,11 +3791,11 @@
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$M$2:$M$84,"Automated*")</f>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3648,11 +3824,11 @@
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">SUM(G11:G12)</f>
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">SUM(H11:H12)</f>
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3798,19 +3974,19 @@
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A23)</f>
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P1")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P2")</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P3")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>35</v>
@@ -3822,7 +3998,7 @@
       </c>
       <c r="B24" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A24)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P1")</f>
@@ -3830,15 +4006,15 @@
       </c>
       <c r="D24" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P2")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P3")</f>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G24" s="10" t="n">
         <f aca="false">IFERROR(B23/(B23+B24),0)</f>
-        <v>0.618181818181818</v>
+        <v>0.621951219512195</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3868,19 +4044,19 @@
       </c>
       <c r="B26" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A26)</f>
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P1")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P2")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P3")</f>
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3926,7 +4102,7 @@
       </c>
       <c r="B31" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A31)</f>
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>42</v>
@@ -3943,7 +4119,7 @@
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A32)</f>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>44</v>
@@ -3960,7 +4136,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A33)</f>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>46</v>
@@ -3977,7 +4153,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A34)</f>
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>48</v>
@@ -4076,12 +4252,12 @@
         <v>61</v>
       </c>
       <c r="B44" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A44)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A44)</f>
+        <v>10</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A44,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
         <v>8</v>
-      </c>
-      <c r="C44" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A44,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
-        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4089,12 +4265,12 @@
         <v>62</v>
       </c>
       <c r="B45" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A45)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A45)</f>
+        <v>8</v>
       </c>
       <c r="C45" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A45,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
-        <v>6</v>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A45,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4102,12 +4278,12 @@
         <v>63</v>
       </c>
       <c r="B46" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A46)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A46)</f>
+        <v>5</v>
       </c>
       <c r="C46" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A46,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A46,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4115,12 +4291,12 @@
         <v>64</v>
       </c>
       <c r="B47" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$23,$A47)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A47)</f>
         <v>4</v>
       </c>
       <c r="C47" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$23,$A47,'Potential Defects'!$I$2:$I$23,"Reproduced")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A47,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,11 +4305,11 @@
       </c>
       <c r="B48" s="8" t="n">
         <f aca="false">SUM(B44:B47)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C48" s="8" t="n">
         <f aca="false">SUM(C44:C47)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4343,8 +4519,24 @@
       <c r="G66" s="11"/>
       <c r="H66" s="11"/>
     </row>
+    <row r="67" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -4369,6 +4561,7 @@
     <mergeCell ref="C64:H64"/>
     <mergeCell ref="C65:H65"/>
     <mergeCell ref="C66:H66"/>
+    <mergeCell ref="C67:H67"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4411,19 +4604,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>78</v>
@@ -4432,54 +4625,54 @@
         <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -4494,22 +4687,22 @@
         <v>53</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O2" s="12" t="s">
         <v>34</v>
@@ -4518,25 +4711,25 @@
         <v>89</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>23</v>
@@ -4551,34 +4744,40 @@
         <v>53</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="O3" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R3" s="14"/>
       <c r="S3" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -4587,7 +4786,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>23</v>
@@ -4602,34 +4801,40 @@
         <v>53</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>134</v>
+      </c>
       <c r="O4" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R4" s="12"/>
       <c r="S4" s="13" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -4638,7 +4843,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>23</v>
@@ -4653,22 +4858,22 @@
         <v>51</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>34</v>
@@ -4677,16 +4882,16 @@
         <v>89</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
@@ -4695,7 +4900,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>23</v>
@@ -4710,34 +4915,40 @@
         <v>53</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>149</v>
+      </c>
       <c r="O6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R6" s="12"/>
       <c r="S6" s="13" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
@@ -4746,7 +4957,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>23</v>
@@ -4761,22 +4972,22 @@
         <v>53</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O7" s="14" t="s">
         <v>34</v>
@@ -4785,16 +4996,16 @@
         <v>89</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>20</v>
@@ -4803,7 +5014,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>23</v>
@@ -4818,22 +5029,22 @@
         <v>53</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>34</v>
@@ -4842,16 +5053,16 @@
         <v>89</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>20</v>
@@ -4860,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>23</v>
@@ -4875,22 +5086,22 @@
         <v>53</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O9" s="14" t="s">
         <v>34</v>
@@ -4899,16 +5110,16 @@
         <v>89</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>20</v>
@@ -4917,7 +5128,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>23</v>
@@ -4932,22 +5143,22 @@
         <v>53</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>34</v>
@@ -4956,16 +5167,16 @@
         <v>89</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>20</v>
@@ -4974,7 +5185,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>23</v>
@@ -4989,22 +5200,22 @@
         <v>53</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>172</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>168</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O11" s="14" t="s">
         <v>34</v>
@@ -5013,16 +5224,16 @@
         <v>89</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R11" s="14"/>
       <c r="S11" s="15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>20</v>
@@ -5031,7 +5242,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
@@ -5046,36 +5257,42 @@
         <v>55</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>182</v>
+      </c>
       <c r="O12" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R12" s="12" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>20</v>
@@ -5084,7 +5301,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>23</v>
@@ -5099,34 +5316,42 @@
         <v>55</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>189</v>
+      </c>
       <c r="O13" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>190</v>
+      </c>
       <c r="S13" s="15" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>20</v>
@@ -5135,7 +5360,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>23</v>
@@ -5150,34 +5375,42 @@
         <v>55</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>196</v>
+      </c>
       <c r="O14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>197</v>
+      </c>
       <c r="S14" s="13" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>20</v>
@@ -5186,7 +5419,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>24</v>
@@ -5201,34 +5434,40 @@
         <v>55</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N15" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>203</v>
+      </c>
       <c r="O15" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R15" s="14"/>
       <c r="S15" s="15" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>20</v>
@@ -5237,7 +5476,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>23</v>
@@ -5252,34 +5491,40 @@
         <v>55</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N16" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>209</v>
+      </c>
       <c r="O16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R16" s="12"/>
       <c r="S16" s="13" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -5288,7 +5533,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>23</v>
@@ -5303,34 +5548,40 @@
         <v>55</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N17" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>215</v>
+      </c>
       <c r="O17" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R17" s="14"/>
       <c r="S17" s="15" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>20</v>
@@ -5339,7 +5590,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
@@ -5354,34 +5605,40 @@
         <v>55</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N18" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>221</v>
+      </c>
       <c r="O18" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R18" s="12"/>
       <c r="S18" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>20</v>
@@ -5390,7 +5647,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>24</v>
@@ -5405,34 +5662,42 @@
         <v>55</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>228</v>
+      </c>
       <c r="O19" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>229</v>
+      </c>
       <c r="S19" s="15" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>20</v>
@@ -5441,7 +5706,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>23</v>
@@ -5456,34 +5721,42 @@
         <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N20" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>234</v>
+      </c>
       <c r="O20" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>235</v>
+      </c>
       <c r="S20" s="13" t="s">
-        <v>221</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
@@ -5492,7 +5765,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -5507,36 +5780,42 @@
         <v>55</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N21" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="O21" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q21" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R21" s="14" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5545,7 +5824,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>26</v>
@@ -5560,36 +5839,42 @@
         <v>55</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>247</v>
+      </c>
       <c r="O22" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q22" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R22" s="12" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>234</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>20</v>
@@ -5598,7 +5883,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -5613,22 +5898,22 @@
         <v>51</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>34</v>
@@ -5637,25 +5922,25 @@
         <v>89</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="R23" s="14"/>
       <c r="S23" s="15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>23</v>
@@ -5670,22 +5955,22 @@
         <v>53</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>34</v>
@@ -5694,25 +5979,25 @@
         <v>89</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -5727,22 +6012,22 @@
         <v>53</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>34</v>
@@ -5751,25 +6036,25 @@
         <v>86</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="15" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -5784,45 +6069,49 @@
         <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>24</v>
@@ -5837,22 +6126,22 @@
         <v>55</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="O27" s="14" t="s">
         <v>36</v>
@@ -5861,27 +6150,27 @@
         <v>89</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
@@ -5896,22 +6185,22 @@
         <v>55</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>36</v>
@@ -5920,27 +6209,27 @@
         <v>89</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>24</v>
@@ -5955,43 +6244,49 @@
         <v>55</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="M29" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N29" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>294</v>
+      </c>
       <c r="O29" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q29" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R29" s="14"/>
       <c r="S29" s="15" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>24</v>
@@ -6006,45 +6301,51 @@
         <v>55</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N30" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>299</v>
+      </c>
       <c r="O30" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q30" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R30" s="12" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>286</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>23</v>
@@ -6059,22 +6360,22 @@
         <v>53</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="O31" s="14" t="s">
         <v>34</v>
@@ -6083,25 +6384,25 @@
         <v>89</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="R31" s="14"/>
       <c r="S31" s="15" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>24</v>
@@ -6116,34 +6417,40 @@
         <v>55</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N32" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>311</v>
+      </c>
       <c r="O32" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q32" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R32" s="12"/>
       <c r="S32" s="13" t="s">
-        <v>126</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>20</v>
@@ -6152,7 +6459,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
@@ -6167,22 +6474,22 @@
         <v>53</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="O33" s="14" t="s">
         <v>34</v>
@@ -6191,16 +6498,16 @@
         <v>89</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="R33" s="14"/>
       <c r="S33" s="15" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>20</v>
@@ -6209,7 +6516,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>25</v>
@@ -6224,22 +6531,22 @@
         <v>53</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="O34" s="12" t="s">
         <v>34</v>
@@ -6248,25 +6555,25 @@
         <v>89</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>25</v>
@@ -6281,22 +6588,22 @@
         <v>55</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="M35" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>36</v>
@@ -6305,27 +6612,27 @@
         <v>89</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="S35" s="15" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>23</v>
@@ -6340,22 +6647,22 @@
         <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>34</v>
@@ -6364,25 +6671,25 @@
         <v>86</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>23</v>
@@ -6397,22 +6704,22 @@
         <v>55</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="M37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="O37" s="14" t="s">
         <v>34</v>
@@ -6421,25 +6728,25 @@
         <v>86</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R37" s="14"/>
       <c r="S37" s="15" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>23</v>
@@ -6454,22 +6761,22 @@
         <v>55</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>36</v>
@@ -6478,27 +6785,27 @@
         <v>86</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>23</v>
@@ -6513,22 +6820,22 @@
         <v>55</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>36</v>
@@ -6537,27 +6844,27 @@
         <v>86</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>23</v>
@@ -6572,43 +6879,49 @@
         <v>53</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N40" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>366</v>
+      </c>
       <c r="O40" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R40" s="12"/>
       <c r="S40" s="13" t="s">
-        <v>126</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>23</v>
@@ -6623,22 +6936,22 @@
         <v>51</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="M41" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>34</v>
@@ -6647,27 +6960,27 @@
         <v>89</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>23</v>
@@ -6682,22 +6995,22 @@
         <v>53</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="M42" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>34</v>
@@ -6706,27 +7019,27 @@
         <v>89</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R42" s="12" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>23</v>
@@ -6741,22 +7054,22 @@
         <v>53</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="M43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>34</v>
@@ -6765,25 +7078,25 @@
         <v>89</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R43" s="14"/>
       <c r="S43" s="15" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>23</v>
@@ -6798,22 +7111,22 @@
         <v>53</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="M44" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="O44" s="12" t="s">
         <v>34</v>
@@ -6822,25 +7135,25 @@
         <v>86</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>23</v>
@@ -6855,22 +7168,22 @@
         <v>55</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M45" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>36</v>
@@ -6879,27 +7192,27 @@
         <v>86</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R45" s="14" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>23</v>
@@ -6914,16 +7227,16 @@
         <v>55</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="M46" s="13" t="s">
         <v>47</v>
@@ -6936,21 +7249,21 @@
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
       <c r="S46" s="13" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -6965,22 +7278,22 @@
         <v>55</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="M47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>36</v>
@@ -6989,27 +7302,27 @@
         <v>86</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>23</v>
@@ -7024,22 +7337,22 @@
         <v>53</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="M48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>34</v>
@@ -7048,25 +7361,25 @@
         <v>89</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>23</v>
@@ -7081,43 +7394,49 @@
         <v>53</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="M49" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N49" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N49" s="15" t="s">
+        <v>428</v>
+      </c>
       <c r="O49" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P49" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q49" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R49" s="14"/>
       <c r="S49" s="15" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>23</v>
@@ -7132,22 +7451,22 @@
         <v>53</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="M50" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>34</v>
@@ -7156,25 +7475,25 @@
         <v>86</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R50" s="12"/>
       <c r="S50" s="13" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>23</v>
@@ -7189,43 +7508,49 @@
         <v>53</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="M51" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N51" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N51" s="15" t="s">
+        <v>440</v>
+      </c>
       <c r="O51" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q51" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R51" s="14"/>
       <c r="S51" s="15" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
@@ -7240,22 +7565,22 @@
         <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="M52" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>34</v>
@@ -7264,25 +7589,25 @@
         <v>86</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="13" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>26</v>
@@ -7297,43 +7622,49 @@
         <v>51</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="M53" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N53" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>452</v>
+      </c>
       <c r="O53" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q53" s="14" t="s">
+        <v>255</v>
+      </c>
       <c r="R53" s="14"/>
       <c r="S53" s="15" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>27</v>
@@ -7348,22 +7679,22 @@
         <v>55</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="M54" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>34</v>
@@ -7372,25 +7703,25 @@
         <v>89</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="13" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>23</v>
@@ -7405,43 +7736,49 @@
         <v>53</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="M55" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N55" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N55" s="15" t="s">
+        <v>467</v>
+      </c>
       <c r="O55" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P55" s="14"/>
-      <c r="Q55" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q55" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R55" s="14"/>
       <c r="S55" s="15" t="s">
-        <v>126</v>
+        <v>468</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -7456,43 +7793,49 @@
         <v>53</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N56" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N56" s="13" t="s">
+        <v>473</v>
+      </c>
       <c r="O56" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P56" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q56" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R56" s="12"/>
       <c r="S56" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>24</v>
@@ -7507,43 +7850,49 @@
         <v>55</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="M57" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N57" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="N57" s="15" t="s">
+        <v>480</v>
+      </c>
       <c r="O57" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="P57" s="14"/>
-      <c r="Q57" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="P57" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q57" s="14" t="s">
+        <v>120</v>
+      </c>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
-        <v>126</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>23</v>
@@ -7558,45 +7907,51 @@
         <v>55</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="M58" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N58" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N58" s="13" t="s">
+        <v>487</v>
+      </c>
       <c r="O58" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P58" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q58" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="R58" s="12" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="S58" s="13" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>23</v>
@@ -7611,22 +7966,22 @@
         <v>53</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="M59" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="O59" s="14" t="s">
         <v>34</v>
@@ -7635,25 +7990,25 @@
         <v>89</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>23</v>
@@ -7668,22 +8023,22 @@
         <v>51</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="M60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N60" s="13" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>34</v>
@@ -7692,27 +8047,27 @@
         <v>89</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>482</v>
+        <v>505</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>23</v>
@@ -7727,22 +8082,22 @@
         <v>53</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="O61" s="14" t="s">
         <v>34</v>
@@ -7751,25 +8106,25 @@
         <v>89</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>23</v>
@@ -7784,22 +8139,22 @@
         <v>55</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="M62" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="13" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>36</v>
@@ -7808,27 +8163,27 @@
         <v>89</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="S62" s="13" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>23</v>
@@ -7843,22 +8198,22 @@
         <v>53</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>496</v>
+        <v>519</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="M63" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N63" s="15" t="s">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="O63" s="14" t="s">
         <v>34</v>
@@ -7867,25 +8222,25 @@
         <v>89</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="15" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>23</v>
@@ -7900,22 +8255,22 @@
         <v>55</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="O64" s="12" t="s">
         <v>36</v>
@@ -7924,27 +8279,27 @@
         <v>89</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>23</v>
@@ -7959,22 +8314,22 @@
         <v>55</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>509</v>
+        <v>532</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="M65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="O65" s="14" t="s">
         <v>36</v>
@@ -7983,27 +8338,27 @@
         <v>86</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>512</v>
+        <v>535</v>
       </c>
       <c r="S65" s="15" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>23</v>
@@ -8018,22 +8373,22 @@
         <v>53</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="M66" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="13" t="s">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="O66" s="12" t="s">
         <v>34</v>
@@ -8042,27 +8397,27 @@
         <v>86</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>23</v>
@@ -8077,22 +8432,22 @@
         <v>53</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="M67" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N67" s="15" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="O67" s="14" t="s">
         <v>34</v>
@@ -8101,25 +8456,25 @@
         <v>89</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="15" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>23</v>
@@ -8134,22 +8489,22 @@
         <v>53</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="M68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N68" s="13" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>34</v>
@@ -8158,25 +8513,25 @@
         <v>89</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>530</v>
+        <v>553</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>531</v>
+        <v>554</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>23</v>
@@ -8191,22 +8546,22 @@
         <v>53</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>533</v>
+        <v>556</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="O69" s="14" t="s">
         <v>34</v>
@@ -8215,25 +8570,25 @@
         <v>89</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="15" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>23</v>
@@ -8248,22 +8603,22 @@
         <v>55</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>537</v>
+        <v>560</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="13" t="s">
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>36</v>
@@ -8272,27 +8627,27 @@
         <v>86</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R70" s="12" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>542</v>
+        <v>565</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>23</v>
@@ -8307,22 +8662,22 @@
         <v>55</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>547</v>
+        <v>570</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>36</v>
@@ -8331,27 +8686,27 @@
         <v>86</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R71" s="14" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>23</v>
@@ -8366,22 +8721,22 @@
         <v>55</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>36</v>
@@ -8390,27 +8745,27 @@
         <v>86</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R72" s="12" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>553</v>
+        <v>576</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>23</v>
@@ -8425,22 +8780,22 @@
         <v>55</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="M73" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="15" t="s">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>36</v>
@@ -8449,27 +8804,27 @@
         <v>86</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R73" s="14" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>23</v>
@@ -8484,22 +8839,22 @@
         <v>55</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="O74" s="12" t="s">
         <v>36</v>
@@ -8508,27 +8863,27 @@
         <v>86</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R74" s="12" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>566</v>
+        <v>589</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>23</v>
@@ -8543,22 +8898,22 @@
         <v>55</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="M75" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="15" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>36</v>
@@ -8567,27 +8922,27 @@
         <v>86</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R75" s="14" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>26</v>
@@ -8602,22 +8957,22 @@
         <v>55</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="13" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>36</v>
@@ -8626,27 +8981,27 @@
         <v>86</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R76" s="12" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="S76" s="13" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>24</v>
@@ -8661,22 +9016,22 @@
         <v>55</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="15" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>34</v>
@@ -8685,25 +9040,25 @@
         <v>86</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="15" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>23</v>
@@ -8718,43 +9073,51 @@
         <v>55</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="M78" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N78" s="13"/>
+        <v>43</v>
+      </c>
+      <c r="N78" s="13" t="s">
+        <v>614</v>
+      </c>
       <c r="O78" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P78" s="12"/>
-      <c r="Q78" s="12"/>
-      <c r="R78" s="12"/>
+        <v>36</v>
+      </c>
+      <c r="P78" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q78" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R78" s="12" t="s">
+        <v>615</v>
+      </c>
       <c r="S78" s="13" t="s">
-        <v>221</v>
+        <v>496</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>24</v>
@@ -8769,22 +9132,22 @@
         <v>55</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="M79" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="15" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>36</v>
@@ -8793,27 +9156,27 @@
         <v>86</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>24</v>
@@ -8828,22 +9191,22 @@
         <v>55</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="M80" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="O80" s="12" t="s">
         <v>36</v>
@@ -8852,27 +9215,27 @@
         <v>86</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="R80" s="12" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="S80" s="13" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>25</v>
@@ -8887,22 +9250,22 @@
         <v>53</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="M81" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>34</v>
@@ -8911,25 +9274,25 @@
         <v>89</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="15" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>25</v>
@@ -8944,22 +9307,22 @@
         <v>53</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N82" s="13" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="O82" s="12" t="s">
         <v>34</v>
@@ -8968,25 +9331,25 @@
         <v>89</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="R82" s="12"/>
       <c r="S82" s="13" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>25</v>
@@ -9001,22 +9364,22 @@
         <v>55</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="M83" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="15" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>36</v>
@@ -9025,27 +9388,27 @@
         <v>89</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="S83" s="15" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>24</v>
@@ -9060,22 +9423,22 @@
         <v>55</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="M84" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N84" s="13" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="O84" s="12" t="s">
         <v>36</v>
@@ -9084,13 +9447,13 @@
         <v>89</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R84" s="12" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="S84" s="13" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -9153,7 +9516,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -9169,57 +9532,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>60</v>
@@ -9227,28 +9590,28 @@
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>60</v>
@@ -9256,28 +9619,28 @@
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>60</v>
@@ -9285,57 +9648,57 @@
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>60</v>
@@ -9343,86 +9706,86 @@
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>672</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>60</v>
@@ -9430,86 +9793,86 @@
     </row>
     <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>672</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>694</v>
+        <v>719</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>60</v>
@@ -9517,28 +9880,28 @@
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>697</v>
+        <v>722</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>60</v>
@@ -9546,28 +9909,28 @@
     </row>
     <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>704</v>
+        <v>729</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>706</v>
+        <v>731</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>60</v>
@@ -9575,57 +9938,57 @@
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>711</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>713</v>
+        <v>738</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>715</v>
+        <v>740</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>60</v>
@@ -9633,28 +9996,28 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>719</v>
+        <v>744</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>60</v>
@@ -9662,28 +10025,28 @@
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>720</v>
+        <v>745</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>60</v>
@@ -9691,28 +10054,28 @@
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>60</v>
@@ -9720,28 +10083,28 @@
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>733</v>
+        <v>758</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>60</v>
@@ -9749,28 +10112,28 @@
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>512</v>
+        <v>535</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>738</v>
+        <v>763</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>739</v>
+        <v>764</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>60</v>
@@ -9778,28 +10141,28 @@
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>741</v>
+        <v>766</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>742</v>
+        <v>767</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>60</v>
@@ -9807,52 +10170,197 @@
     </row>
     <row r="23" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>744</v>
+        <v>769</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>748</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
+    <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>773</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>774</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>775</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>776</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>680</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>779</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>780</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>783</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>784</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>785</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>786</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>787</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>788</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>790</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>791</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>792</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>793</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I28"/>
   <mergeCells count="1">
-    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I28">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$I2="Reproduced"</formula>
     </cfRule>
@@ -9861,11 +10369,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I23" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I28" type="list">
       <formula1>"Reproduced,To reproduce,Intermittent,Not reproducible"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C23" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C28" type="list">
       <formula1>"Defect,Potential defect – requirement to confirm,Security observation,UX / improvement suggestion"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9896,175 +10404,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>749</v>
+        <v>795</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>752</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>753</v>
+        <v>799</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>754</v>
+        <v>800</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>756</v>
+        <v>802</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>757</v>
+        <v>803</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>759</v>
+        <v>805</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>762</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>763</v>
+        <v>809</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>764</v>
+        <v>810</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>765</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>767</v>
+        <v>813</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>762</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>768</v>
+        <v>814</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>770</v>
+        <v>816</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>771</v>
+        <v>817</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>773</v>
+        <v>819</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>774</v>
+        <v>820</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>775</v>
+        <v>821</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>776</v>
+        <v>822</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>777</v>
+        <v>823</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>779</v>
+        <v>825</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>777</v>
+        <v>823</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>780</v>
+        <v>826</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>781</v>
+        <v>827</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>782</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>783</v>
+        <v>829</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>785</v>
+        <v>831</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>787</v>
+        <v>833</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>788</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>789</v>
+        <v>835</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>790</v>
+        <v>836</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>58</v>
@@ -10072,182 +10580,182 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>792</v>
+        <v>838</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>360</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>794</v>
+        <v>840</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>820</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>795</v>
+        <v>841</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>650</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>796</v>
+        <v>842</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>800</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>797</v>
+        <v>843</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>798</v>
+        <v>844</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>320</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>799</v>
+        <v>845</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>700</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>800</v>
+        <v>846</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>801</v>
+        <v>847</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>802</v>
+        <v>848</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>801</v>
+        <v>847</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>803</v>
+        <v>849</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>804</v>
+        <v>850</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>805</v>
+        <v>851</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>806</v>
+        <v>852</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>807</v>
+        <v>853</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>808</v>
+        <v>854</v>
       </c>
       <c r="B34" s="20" t="n">
         <f aca="false">B21+B22</f>
         <v>1180</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>809</v>
+        <v>855</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>810</v>
+        <v>856</v>
       </c>
       <c r="B35" s="20" t="n">
         <f aca="false">B21*2</f>
         <v>720</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>811</v>
+        <v>857</v>
       </c>
       <c r="B36" s="20" t="n">
         <f aca="false">B21*2+B22</f>
         <v>1540</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>812</v>
+        <v>858</v>
       </c>
       <c r="B37" s="20" t="n">
         <f aca="false">B23*3</f>
         <v>1950</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>813</v>
+        <v>859</v>
       </c>
       <c r="B38" s="20" t="n">
         <f aca="false">SUM(B21:B29)+B21</f>
         <v>6380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Potential Defects'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$I$28</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$J$28</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Test Cases'!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$S$84</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="880">
   <si>
     <t xml:space="preserve">DemoBlaze – Test Case Suite (Login &amp; Cart)</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5 (20-Oct-2026)</t>
+    <t xml:space="preserve">1.6 (20-Oct-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Execution environment</t>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t xml:space="preserve">27 more cases automated (60 in total; only CRT-011 stays manual among the previously not-run cases). Full run of 167 tests passed, 17 cases failing as expected; 5 new potential defects (PD-23 to PD-27).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated runs now keep evidence for every known defect (screenshot + video, or API log) in reports/evidence/; new 'Automated evidence' column in Potential Defects. Firefox start-up race fixed at source (no retry).</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -2345,6 +2351,9 @@
     <t xml:space="preserve">Reproduced?</t>
   </si>
   <si>
+    <t xml:space="preserve">Automated evidence (latest run)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Order can be placed with an empty cart</t>
   </si>
   <si>
@@ -2361,6 +2370,10 @@
   </si>
   <si>
     <t xml:space="preserve">Purchase confirmation shown with 'Amount: 0 USD'. Reproduced 19-Oct-2026: 'Amount: 0 USD'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/evidence/PD-01_CRT-029_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
     <t xml:space="preserve">Wrong month on purchase confirmation date</t>
@@ -2379,6 +2392,10 @@
     <t xml:space="preserve">Month is one behind, e.g. 19/9/2026 (month is 0-based in the code). Reproduced 19-Oct-2026: purchase on 19 Oct showed 'Date: 19/9/2026'.</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-02_CRT-027_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">No credit card number validation</t>
   </si>
   <si>
@@ -2397,6 +2414,9 @@
     <t xml:space="preserve">Any non-empty value is accepted. Reproduced: 'abcd-efgh!@#' and '123' both accepted.</t>
   </si>
   <si>
+    <t xml:space="preserve">Manual run – see Actual (observed)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Country, City, Month, Year are not validated or required</t>
   </si>
   <si>
@@ -2439,6 +2459,10 @@
     <t xml:space="preserve">Input is not trimmed, so the check passes (login request is sent; purchase succeeds). Reproduced on Place Order (spaces-only Name/Card accepted). Login side still to check. Login side (LGN-011) reproduced by the automated run on 20-Oct-2026.</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-05_LGN-011_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Inconsistent 'Product added' alert text</t>
   </si>
   <si>
@@ -2479,6 +2503,10 @@
     <t xml:space="preserve">Password is only Base64-encoded in the JSON body; anyone who sees the body can decode it. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-07_LGN-029_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auth cookie lacks Secure/HttpOnly flags</t>
   </si>
   <si>
@@ -2496,6 +2524,10 @@
     <t xml:space="preserve">Cookie is set by JavaScript (document.cookie), so it cannot be HttpOnly and is readable by scripts. Reproduced 19-Oct-2026: tokenp_ is readable from document.cookie, so it is not HttpOnly.</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-08_LGN-027_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Guest cart items are not carried over after login</t>
   </si>
   <si>
@@ -2510,6 +2542,10 @@
     <t xml:space="preserve">Guest and user carts are separate; guest items are not shown. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-09_CRT-023_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enter key does not submit the Login form</t>
   </si>
   <si>
@@ -2525,6 +2561,10 @@
   </si>
   <si>
     <t xml:space="preserve">Expected: nothing happens (form has no submit button). Confirm by execution. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/evidence/PD-10_LGN-020_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
     <t xml:space="preserve">Modal fields keep previous values after closing</t>
@@ -2545,6 +2585,10 @@
     <t xml:space="preserve">Expected: previous values remain. Confirm by execution. Reproduced on Place Order modal (Name kept after Close). Login modal (LGN-021) reproduced by the automated run on 20-Oct-2026.</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-11_LGN-021_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Order ID generated client-side and not persisted</t>
   </si>
   <si>
@@ -2655,6 +2699,10 @@
     <t xml:space="preserve">'cWFfc3lfMDExNzkzMDEx' decodes to 'qa_sy_011793011' (username + number). A token for another user could potentially be built without their password (not attempted).</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-18_LGN-026_&lt;browser&gt;.txt (API log)
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">API returns HTTP 200 for error responses</t>
   </si>
   <si>
@@ -2673,6 +2721,10 @@
   </si>
   <si>
     <t xml:space="preserve">HTTP 200 with {"errorMessage": ...} in the body.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/evidence/PD-19_LGN-034_api.txt (API log)
+reports/evidence/PD-19_CRT-048_api.txt (API log)</t>
   </si>
   <si>
     <t xml:space="preserve">Order amount uses a stale client-side total</t>
@@ -2720,6 +2772,10 @@
     <t xml:space="preserve">Only the Home page creates the guest id cookie ('user'). A guest who lands on a product page first (search result, shared link) sends an empty id, so all such guests read and write the same cart: our test saw 121-134 items from other people. Privacy issue: one guest can see, and buy, another guest's items. Reproduced 20-Oct-2026 by the automated run on Chromium, Firefox and WebKit.</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-22_CRT-049_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Double-clicking 'Log in' sends two login requests</t>
   </si>
   <si>
@@ -2733,6 +2789,10 @@
   </si>
   <si>
     <t xml:space="preserve">A double-click calls logIn() twice and sends two POST /login requests. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/evidence/PD-23_LGN-019_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
     <t xml:space="preserve">Double-clicking 'Purchase' submits the order twice</t>
@@ -2751,6 +2811,10 @@
     <t xml:space="preserve">A double-click runs purchaseOrder() twice: two order submissions (POST /deletecart twice) and the confirmation is regenerated. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-24_CRT-043_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">No lockout or rate limit after repeated failed logins</t>
   </si>
   <si>
@@ -2768,6 +2832,10 @@
     <t xml:space="preserve">10 consecutive wrong passwords all returned 'Wrong password.'; nothing slows down or blocks guessing, so passwords can be brute-forced. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-25_LGN-018_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Login does not trim spaces around the username</t>
   </si>
   <si>
@@ -2782,6 +2850,10 @@
     <t xml:space="preserve">' &lt;username&gt; ' with surrounding spaces returns 'User does not exist.' Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
+    <t xml:space="preserve">reports/evidence/PD-26_LGN-012_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Login treats the username as case-sensitive</t>
   </si>
   <si>
@@ -2794,6 +2866,10 @@
   </si>
   <si>
     <t xml:space="preserve">The username in upper case returns 'User does not exist.' Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/evidence/PD-27_LGN-013_&lt;browser&gt;.png + .webm
+(&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
     <t xml:space="preserve">Note: DemoBlaze has no published requirements. 'Expected' follows common e-commerce practice, so 'Potential defect – requirement to confirm' items should be agreed with the product owner before being raised as bugs. 'Reproduced?' = observed when the related test was run on 19-Oct-2026.</t>
@@ -3619,7 +3695,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -4535,8 +4611,24 @@
       <c r="G67" s="11"/>
       <c r="H67" s="11"/>
     </row>
+    <row r="68" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -4562,6 +4654,7 @@
     <mergeCell ref="C65:H65"/>
     <mergeCell ref="C66:H66"/>
     <mergeCell ref="C67:H67"/>
+    <mergeCell ref="C68:H68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4604,19 +4697,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>78</v>
@@ -4625,54 +4718,54 @@
         <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -4687,22 +4780,22 @@
         <v>53</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O2" s="12" t="s">
         <v>34</v>
@@ -4711,25 +4804,25 @@
         <v>89</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>23</v>
@@ -4744,22 +4837,22 @@
         <v>53</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O3" s="14" t="s">
         <v>34</v>
@@ -4768,16 +4861,16 @@
         <v>89</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -4786,7 +4879,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>23</v>
@@ -4801,22 +4894,22 @@
         <v>53</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>34</v>
@@ -4825,16 +4918,16 @@
         <v>89</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R4" s="12"/>
       <c r="S4" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -4843,7 +4936,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>23</v>
@@ -4858,22 +4951,22 @@
         <v>51</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>34</v>
@@ -4882,16 +4975,16 @@
         <v>89</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
@@ -4900,7 +4993,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>23</v>
@@ -4915,22 +5008,22 @@
         <v>53</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>34</v>
@@ -4939,16 +5032,16 @@
         <v>89</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
@@ -4957,7 +5050,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>23</v>
@@ -4972,22 +5065,22 @@
         <v>53</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O7" s="14" t="s">
         <v>34</v>
@@ -4996,16 +5089,16 @@
         <v>89</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>20</v>
@@ -5014,7 +5107,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>23</v>
@@ -5029,22 +5122,22 @@
         <v>53</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>34</v>
@@ -5053,16 +5146,16 @@
         <v>89</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>20</v>
@@ -5071,7 +5164,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>23</v>
@@ -5086,22 +5179,22 @@
         <v>53</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O9" s="14" t="s">
         <v>34</v>
@@ -5110,16 +5203,16 @@
         <v>89</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>20</v>
@@ -5128,7 +5221,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>23</v>
@@ -5143,22 +5236,22 @@
         <v>53</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>34</v>
@@ -5167,16 +5260,16 @@
         <v>89</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>20</v>
@@ -5185,7 +5278,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>23</v>
@@ -5200,22 +5293,22 @@
         <v>53</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O11" s="14" t="s">
         <v>34</v>
@@ -5224,16 +5317,16 @@
         <v>89</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R11" s="14"/>
       <c r="S11" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>20</v>
@@ -5242,7 +5335,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
@@ -5257,22 +5350,22 @@
         <v>55</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>36</v>
@@ -5281,18 +5374,18 @@
         <v>89</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>20</v>
@@ -5301,7 +5394,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>23</v>
@@ -5316,22 +5409,22 @@
         <v>55</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O13" s="14" t="s">
         <v>36</v>
@@ -5340,18 +5433,18 @@
         <v>89</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S13" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>20</v>
@@ -5360,7 +5453,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>23</v>
@@ -5375,22 +5468,22 @@
         <v>55</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>36</v>
@@ -5399,18 +5492,18 @@
         <v>89</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>20</v>
@@ -5419,7 +5512,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>24</v>
@@ -5434,22 +5527,22 @@
         <v>55</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O15" s="14" t="s">
         <v>34</v>
@@ -5458,16 +5551,16 @@
         <v>89</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R15" s="14"/>
       <c r="S15" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>20</v>
@@ -5476,7 +5569,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>23</v>
@@ -5491,22 +5584,22 @@
         <v>55</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>34</v>
@@ -5515,16 +5608,16 @@
         <v>89</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -5533,7 +5626,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>23</v>
@@ -5548,22 +5641,22 @@
         <v>55</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O17" s="14" t="s">
         <v>34</v>
@@ -5572,16 +5665,16 @@
         <v>89</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R17" s="14"/>
       <c r="S17" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>20</v>
@@ -5590,7 +5683,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
@@ -5605,22 +5698,22 @@
         <v>55</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>34</v>
@@ -5629,16 +5722,16 @@
         <v>89</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>20</v>
@@ -5647,7 +5740,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>24</v>
@@ -5662,22 +5755,22 @@
         <v>55</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O19" s="14" t="s">
         <v>36</v>
@@ -5686,18 +5779,18 @@
         <v>89</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R19" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="S19" s="15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>20</v>
@@ -5706,7 +5799,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>23</v>
@@ -5721,22 +5814,22 @@
         <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>36</v>
@@ -5745,18 +5838,18 @@
         <v>89</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
@@ -5765,7 +5858,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -5780,22 +5873,22 @@
         <v>55</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="14" t="s">
         <v>36</v>
@@ -5804,18 +5897,18 @@
         <v>89</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R21" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5824,7 +5917,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>26</v>
@@ -5839,22 +5932,22 @@
         <v>55</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" s="12" t="s">
         <v>36</v>
@@ -5863,18 +5956,18 @@
         <v>89</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>20</v>
@@ -5883,7 +5976,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -5898,22 +5991,22 @@
         <v>51</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>34</v>
@@ -5922,25 +6015,25 @@
         <v>89</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="R23" s="14"/>
       <c r="S23" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>23</v>
@@ -5955,22 +6048,22 @@
         <v>53</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>34</v>
@@ -5979,25 +6072,25 @@
         <v>89</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -6012,22 +6105,22 @@
         <v>53</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>34</v>
@@ -6036,25 +6129,25 @@
         <v>86</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -6069,22 +6162,22 @@
         <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>34</v>
@@ -6093,25 +6186,25 @@
         <v>89</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>24</v>
@@ -6126,22 +6219,22 @@
         <v>55</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O27" s="14" t="s">
         <v>36</v>
@@ -6150,27 +6243,27 @@
         <v>89</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
@@ -6185,22 +6278,22 @@
         <v>55</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>36</v>
@@ -6209,27 +6302,27 @@
         <v>89</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>24</v>
@@ -6244,22 +6337,22 @@
         <v>55</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M29" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O29" s="14" t="s">
         <v>34</v>
@@ -6268,25 +6361,25 @@
         <v>89</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R29" s="14"/>
       <c r="S29" s="15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>24</v>
@@ -6301,22 +6394,22 @@
         <v>55</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O30" s="12" t="s">
         <v>36</v>
@@ -6325,27 +6418,27 @@
         <v>89</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>23</v>
@@ -6360,22 +6453,22 @@
         <v>53</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O31" s="14" t="s">
         <v>34</v>
@@ -6384,25 +6477,25 @@
         <v>89</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R31" s="14"/>
       <c r="S31" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>24</v>
@@ -6417,22 +6510,22 @@
         <v>55</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M32" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O32" s="12" t="s">
         <v>34</v>
@@ -6441,16 +6534,16 @@
         <v>89</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R32" s="12"/>
       <c r="S32" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>20</v>
@@ -6459,7 +6552,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
@@ -6474,22 +6567,22 @@
         <v>53</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O33" s="14" t="s">
         <v>34</v>
@@ -6498,16 +6591,16 @@
         <v>89</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R33" s="14"/>
       <c r="S33" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>20</v>
@@ -6516,7 +6609,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>25</v>
@@ -6531,22 +6624,22 @@
         <v>53</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O34" s="12" t="s">
         <v>34</v>
@@ -6555,25 +6648,25 @@
         <v>89</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>25</v>
@@ -6588,22 +6681,22 @@
         <v>55</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M35" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>36</v>
@@ -6612,27 +6705,27 @@
         <v>89</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S35" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>23</v>
@@ -6647,22 +6740,22 @@
         <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>34</v>
@@ -6671,25 +6764,25 @@
         <v>86</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>23</v>
@@ -6704,22 +6797,22 @@
         <v>55</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O37" s="14" t="s">
         <v>34</v>
@@ -6728,25 +6821,25 @@
         <v>86</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R37" s="14"/>
       <c r="S37" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>23</v>
@@ -6761,22 +6854,22 @@
         <v>55</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>36</v>
@@ -6785,27 +6878,27 @@
         <v>86</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>23</v>
@@ -6820,22 +6913,22 @@
         <v>55</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>36</v>
@@ -6844,27 +6937,27 @@
         <v>86</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>23</v>
@@ -6879,22 +6972,22 @@
         <v>53</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M40" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O40" s="12" t="s">
         <v>34</v>
@@ -6903,25 +6996,25 @@
         <v>89</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R40" s="12"/>
       <c r="S40" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>23</v>
@@ -6936,22 +7029,22 @@
         <v>51</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M41" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>34</v>
@@ -6960,27 +7053,27 @@
         <v>89</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>23</v>
@@ -6995,22 +7088,22 @@
         <v>53</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M42" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>34</v>
@@ -7019,27 +7112,27 @@
         <v>89</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R42" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>23</v>
@@ -7054,22 +7147,22 @@
         <v>53</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>34</v>
@@ -7078,25 +7171,25 @@
         <v>89</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R43" s="14"/>
       <c r="S43" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>23</v>
@@ -7111,22 +7204,22 @@
         <v>53</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M44" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O44" s="12" t="s">
         <v>34</v>
@@ -7135,25 +7228,25 @@
         <v>86</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>23</v>
@@ -7168,22 +7261,22 @@
         <v>55</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M45" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>36</v>
@@ -7192,27 +7285,27 @@
         <v>86</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R45" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>23</v>
@@ -7227,16 +7320,16 @@
         <v>55</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M46" s="13" t="s">
         <v>47</v>
@@ -7249,21 +7342,21 @@
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
       <c r="S46" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -7278,22 +7371,22 @@
         <v>55</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>36</v>
@@ -7302,27 +7395,27 @@
         <v>86</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>23</v>
@@ -7337,22 +7430,22 @@
         <v>53</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>34</v>
@@ -7361,25 +7454,25 @@
         <v>89</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>23</v>
@@ -7394,22 +7487,22 @@
         <v>53</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M49" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>34</v>
@@ -7418,25 +7511,25 @@
         <v>89</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>23</v>
@@ -7451,22 +7544,22 @@
         <v>53</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M50" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>34</v>
@@ -7475,25 +7568,25 @@
         <v>86</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R50" s="12"/>
       <c r="S50" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>23</v>
@@ -7508,22 +7601,22 @@
         <v>53</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M51" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N51" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O51" s="14" t="s">
         <v>34</v>
@@ -7532,25 +7625,25 @@
         <v>89</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
@@ -7565,22 +7658,22 @@
         <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M52" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>34</v>
@@ -7589,25 +7682,25 @@
         <v>86</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>26</v>
@@ -7622,22 +7715,22 @@
         <v>51</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M53" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N53" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O53" s="14" t="s">
         <v>34</v>
@@ -7646,25 +7739,25 @@
         <v>89</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="R53" s="14"/>
       <c r="S53" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>27</v>
@@ -7679,22 +7772,22 @@
         <v>55</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M54" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>34</v>
@@ -7703,25 +7796,25 @@
         <v>89</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>23</v>
@@ -7736,22 +7829,22 @@
         <v>53</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M55" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N55" s="15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O55" s="14" t="s">
         <v>34</v>
@@ -7760,25 +7853,25 @@
         <v>89</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R55" s="14"/>
       <c r="S55" s="15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -7793,22 +7886,22 @@
         <v>53</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M56" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N56" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O56" s="12" t="s">
         <v>34</v>
@@ -7817,25 +7910,25 @@
         <v>89</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R56" s="12"/>
       <c r="S56" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>24</v>
@@ -7850,22 +7943,22 @@
         <v>55</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M57" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N57" s="15" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O57" s="14" t="s">
         <v>34</v>
@@ -7874,25 +7967,25 @@
         <v>89</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>23</v>
@@ -7907,22 +8000,22 @@
         <v>55</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M58" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N58" s="13" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O58" s="12" t="s">
         <v>36</v>
@@ -7931,27 +8024,27 @@
         <v>89</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R58" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="S58" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>23</v>
@@ -7966,22 +8059,22 @@
         <v>53</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M59" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O59" s="14" t="s">
         <v>34</v>
@@ -7990,25 +8083,25 @@
         <v>89</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>23</v>
@@ -8023,22 +8116,22 @@
         <v>51</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N60" s="13" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>34</v>
@@ -8047,27 +8140,27 @@
         <v>89</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>23</v>
@@ -8082,22 +8175,22 @@
         <v>53</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O61" s="14" t="s">
         <v>34</v>
@@ -8106,25 +8199,25 @@
         <v>89</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>23</v>
@@ -8139,22 +8232,22 @@
         <v>55</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M62" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>36</v>
@@ -8163,27 +8256,27 @@
         <v>89</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="S62" s="13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>23</v>
@@ -8198,22 +8291,22 @@
         <v>53</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M63" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N63" s="15" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O63" s="14" t="s">
         <v>34</v>
@@ -8222,25 +8315,25 @@
         <v>89</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="15" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>23</v>
@@ -8255,22 +8348,22 @@
         <v>55</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O64" s="12" t="s">
         <v>36</v>
@@ -8279,27 +8372,27 @@
         <v>89</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>23</v>
@@ -8314,22 +8407,22 @@
         <v>55</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O65" s="14" t="s">
         <v>36</v>
@@ -8338,27 +8431,27 @@
         <v>86</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="S65" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>23</v>
@@ -8373,22 +8466,22 @@
         <v>53</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M66" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="13" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O66" s="12" t="s">
         <v>34</v>
@@ -8397,27 +8490,27 @@
         <v>86</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>23</v>
@@ -8432,22 +8525,22 @@
         <v>53</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M67" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N67" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O67" s="14" t="s">
         <v>34</v>
@@ -8456,25 +8549,25 @@
         <v>89</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>23</v>
@@ -8489,22 +8582,22 @@
         <v>53</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N68" s="13" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>34</v>
@@ -8513,25 +8606,25 @@
         <v>89</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>23</v>
@@ -8546,22 +8639,22 @@
         <v>53</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O69" s="14" t="s">
         <v>34</v>
@@ -8570,25 +8663,25 @@
         <v>89</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>23</v>
@@ -8603,22 +8696,22 @@
         <v>55</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="13" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>36</v>
@@ -8627,27 +8720,27 @@
         <v>86</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R70" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>23</v>
@@ -8662,22 +8755,22 @@
         <v>55</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>36</v>
@@ -8686,27 +8779,27 @@
         <v>86</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R71" s="14" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>23</v>
@@ -8721,22 +8814,22 @@
         <v>55</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>36</v>
@@ -8745,27 +8838,27 @@
         <v>86</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R72" s="12" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>23</v>
@@ -8780,22 +8873,22 @@
         <v>55</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M73" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="15" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>36</v>
@@ -8804,27 +8897,27 @@
         <v>86</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R73" s="14" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>23</v>
@@ -8839,22 +8932,22 @@
         <v>55</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O74" s="12" t="s">
         <v>36</v>
@@ -8863,27 +8956,27 @@
         <v>86</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R74" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>23</v>
@@ -8898,22 +8991,22 @@
         <v>55</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M75" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="15" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>36</v>
@@ -8922,27 +9015,27 @@
         <v>86</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R75" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>26</v>
@@ -8957,22 +9050,22 @@
         <v>55</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="13" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>36</v>
@@ -8981,27 +9074,27 @@
         <v>86</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R76" s="12" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="S76" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>24</v>
@@ -9016,22 +9109,22 @@
         <v>55</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="15" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>34</v>
@@ -9040,25 +9133,25 @@
         <v>86</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="15" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>23</v>
@@ -9073,22 +9166,22 @@
         <v>55</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M78" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N78" s="13" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="O78" s="12" t="s">
         <v>36</v>
@@ -9097,27 +9190,27 @@
         <v>89</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R78" s="12" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="S78" s="13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>24</v>
@@ -9132,22 +9225,22 @@
         <v>55</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M79" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="15" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>36</v>
@@ -9156,27 +9249,27 @@
         <v>86</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>24</v>
@@ -9191,22 +9284,22 @@
         <v>55</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="M80" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="O80" s="12" t="s">
         <v>36</v>
@@ -9215,27 +9308,27 @@
         <v>86</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R80" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="S80" s="13" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>25</v>
@@ -9250,22 +9343,22 @@
         <v>53</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M81" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>34</v>
@@ -9274,25 +9367,25 @@
         <v>89</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="15" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>25</v>
@@ -9307,22 +9400,22 @@
         <v>53</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N82" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="O82" s="12" t="s">
         <v>34</v>
@@ -9331,25 +9424,25 @@
         <v>89</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R82" s="12"/>
       <c r="S82" s="13" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>25</v>
@@ -9364,22 +9457,22 @@
         <v>55</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M83" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="15" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>36</v>
@@ -9388,27 +9481,27 @@
         <v>89</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S83" s="15" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>24</v>
@@ -9423,22 +9516,22 @@
         <v>55</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M84" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N84" s="13" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O84" s="12" t="s">
         <v>36</v>
@@ -9447,13 +9540,13 @@
         <v>89</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R84" s="12" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="S84" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -9516,7 +9609,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -9528,823 +9621,908 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>664</v>
+        <v>666</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J2" s="13" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J3" s="15" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J4" s="13" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J5" s="15" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J6" s="13" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>697</v>
+        <v>704</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J8" s="13" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J9" s="15" t="s">
+        <v>716</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J10" s="13" t="s">
+        <v>721</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J11" s="15" t="s">
+        <v>727</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J12" s="13" t="s">
+        <v>733</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J13" s="15" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J14" s="13" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>736</v>
+        <v>748</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J16" s="13" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J17" s="15" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J18" s="13" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J19" s="15" t="s">
+        <v>767</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>755</v>
+        <v>768</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>756</v>
+        <v>769</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>759</v>
+        <v>772</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>760</v>
+        <v>773</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J20" s="13" t="s">
+        <v>774</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J21" s="15" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J22" s="13" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J23" s="15" t="s">
+        <v>787</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J24" s="13" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J25" s="15" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>782</v>
+        <v>799</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>784</v>
+        <v>801</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>785</v>
+        <v>802</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J26" s="13" t="s">
+        <v>803</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>789</v>
+        <v>807</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>60</v>
       </c>
+      <c r="J27" s="15" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>790</v>
+        <v>809</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>792</v>
+        <v>811</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>793</v>
+        <v>812</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>60</v>
       </c>
+      <c r="J28" s="13" t="s">
+        <v>813</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -10354,11 +10532,12 @@
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
       <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:J28"/>
   <mergeCells count="1">
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A30:J30"/>
   </mergeCells>
   <conditionalFormatting sqref="I2:I28">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
@@ -10404,175 +10583,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>796</v>
+        <v>816</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>58</v>
@@ -10580,182 +10759,182 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>360</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>820</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>650</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>800</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>320</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>700</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="B34" s="20" t="n">
         <f aca="false">B21+B22</f>
         <v>1180</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="B35" s="20" t="n">
         <f aca="false">B21*2</f>
         <v>720</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B36" s="20" t="n">
         <f aca="false">B21*2+B22</f>
         <v>1540</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="B37" s="20" t="n">
         <f aca="false">B23*3</f>
         <v>1950</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="B38" s="20" t="n">
         <f aca="false">SUM(B21:B29)+B21</f>
         <v>6380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Potential Defects'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$J$28</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Potential Defects'!$A$1:$J$29</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Test Cases'!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$S$84</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$S$85</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="896">
   <si>
     <t xml:space="preserve">DemoBlaze – Test Case Suite (Login &amp; Cart)</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6 (20-Oct-2026)</t>
+    <t xml:space="preserve">1.7 (20-Oct-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Execution environment</t>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t xml:space="preserve">Automated runs now keep evidence for every known defect (screenshot + video, or API log) in reports/evidence/; new 'Automated evidence' column in Potential Defects. Firefox start-up race fixed at source (no retry).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root causes of the latest run's 5 failures: new defect PD-28 (bought items stay in the cart when OK is pressed quickly), covered by CRT-050; LGN-005 starts on Home to avoid the shared guest cart; the performance check runs on its own and uses the median of 3 cold loads.</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -490,10 +496,11 @@
     <t xml:space="preserve">Account {VALID_USER} exists; user is logged out. {VALID_USER}'s cart has 1 item.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Go to {BASE_URL}/cart.html.
-2. Click 'Log in'.
-3. Enter {VALID_USER} and {VALID_PASSWORD}.
-4. Click 'Log in'.</t>
+    <t xml:space="preserve">1. Go to {BASE_URL}.
+2. Click 'Cart' in the navbar.
+3. Click 'Log in'.
+4. Enter {VALID_USER} and {VALID_PASSWORD}.
+5. Click 'Log in'.</t>
   </si>
   <si>
     <t xml:space="preserve">Username: {VALID_USER}
@@ -503,7 +510,7 @@
     <t xml:space="preserve">Page reloads on cart.html, shows 'Welcome {VALID_USER}' and lists {VALID_USER}'s cart item.</t>
   </si>
   <si>
-    <t xml:space="preserve">Page reloaded on cart.html with 'Welcome &lt;user&gt;' and the user's cart item listed.</t>
+    <t xml:space="preserve">Page reloaded on cart.html with 'Welcome &lt;user&gt;' and the user's cart item listed. (The journey starts on Home: opening cart.html directly as a guest loads the shared guest cart (PD-22), hundreds of items, which once slowed the API enough to time the test out.)</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-006</t>
@@ -1598,7 +1605,7 @@
     <t xml:space="preserve">All rows and the Total are displayed within 3 seconds.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart ready in 2803 ms with 5 items (budget 3000 ms) in the latest run; 2957 ms the run before. Little headroom: the cart calls /view once per item, so load time grows with cart size.</t>
+    <t xml:space="preserve">Cart ready in 2803 ms with 5 items (budget 3000 ms); 2957 ms the run before. A full-suite run measured 3415 ms, but there the page competed with ~160 parallel browser tests, so perf now runs on its own (npm run test:perf) and uses the median of 3 cold loads. Little headroom: the cart calls /view once per item, so load time grows with cart size.</t>
   </si>
   <si>
     <t xml:space="preserve">Automated: Chromium (perf)</t>
@@ -1787,7 +1794,7 @@
     <t xml:space="preserve">The cart table has no rows, and the server-side cart (/viewcart) is empty.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart empty on the server and in the UI after purchase.</t>
+    <t xml:space="preserve">Cart empty on the server and in the UI after purchase. One run failed on Chromium and Firefox because the script pressed OK before the site's cart-clear call had finished: logged as PD-28 (CRT-050). The script now waits for that call, as a user reading the receipt would.</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-027</t>
@@ -2327,6 +2334,35 @@
     <t xml:space="preserve">PD-22</t>
   </si>
   <si>
+    <t xml:space="preserve">CRT-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the cart is emptied when the order is confirmed straight away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged in as {VALID_USER}; cart has 1 item. Slow connection (DevTools &gt; Network &gt; 'Slow 3G'), so the cart-clear request takes a few seconds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to {BASE_URL}.
+2. Click 'Cart' in the navbar.
+3. Click 'Place Order'.
+4. Fill all fields with the test data and click 'Purchase'.
+5. Click 'OK' as soon as the confirmation appears.
+6. Turn throttling off and click 'Cart'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cart is empty, however quickly 'OK' is clicked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fails as expected (PD-28). First seen in the 20-Oct full run (CRT-026, Chromium and Firefox): OK was pressed about 1 s after Purchase, the move to Home cancelled POST /deletecart (no response), and the server cart still held the item 20 s later. The test reproduces it on demand by slowing that one request down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated: Chromium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
@@ -2870,6 +2906,28 @@
   <si>
     <t xml:space="preserve">reports/evidence/PD-27_LGN-013_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressing OK on the order confirmation too soon leaves the bought items in the cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and add an item to the cart.
+2. Open DevTools &gt; Network and set throttling to 'Slow 3G'.
+3. Place Order, fill Name and Credit card, click 'Purchase'.
+4. Click 'OK' as soon as the confirmation appears.
+5. Turn throttling off and open Cart: the item is still there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cart is emptied as part of placing the order, whatever the user does next.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purchaseOrder() sends POST /deletecart without waiting for it, and OK goes to Home straight away. If OK is pressed before that request finishes, the browser cancels it and the server cart keeps the purchased items (automated run: the item was still there 20 s later). The customer can then pay for the same items again. Found by the automated run on 20-Oct-2026 (Chromium, Firefox).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports/evidence/PD-28_CRT-050_chromium.png + .webm</t>
   </si>
   <si>
     <t xml:space="preserve">Note: DemoBlaze has no published requirements. 'Expected' follows common e-commerce practice, so 'Potential defect – requirement to confirm' items should be agreed with the product owner before being raised as bugs. 'Reproduced?' = observed when the related test was run on 19-Oct-2026.</t>
@@ -3695,7 +3753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3813,31 +3871,31 @@
         <v>20</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Positive")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A11,'Test Cases'!$F$2:$F$85,"Positive")</f>
         <v>11</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Negative")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A11,'Test Cases'!$F$2:$F$85,"Negative")</f>
         <v>15</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Edge")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A11,'Test Cases'!$F$2:$F$85,"Edge")</f>
         <v>7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$F$2:$F$84,"Boundary")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A11,'Test Cases'!$F$2:$F$85,"Boundary")</f>
         <v>1</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$84,$A11)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$85,$A11)</f>
         <v>34</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$M$2:$M$84,"Automated*")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A11,'Test Cases'!$M$2:$M$85,"Automated*")</f>
         <v>33</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A11,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A11,'Test Cases'!$O$2:$O$85,"&lt;&gt;Not Run")</f>
         <v>34</v>
       </c>
     </row>
@@ -3846,32 +3904,32 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Positive")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$F$2:$F$85,"Positive")</f>
         <v>22</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Negative")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$F$2:$F$85,"Negative")</f>
         <v>15</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Edge")</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$F$2:$F$85,"Edge")</f>
+        <v>9</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$F$2:$F$84,"Boundary")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$F$2:$F$85,"Boundary")</f>
         <v>4</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$84,$A12)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$85,$A12)</f>
+        <v>50</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$M$2:$M$85,"Automated*")</f>
+        <v>28</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$O$2:$O$85,"&lt;&gt;Not Run")</f>
         <v>49</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$M$2:$M$84,"Automated*")</f>
-        <v>27</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A12,'Test Cases'!$O$2:$O$84,"&lt;&gt;Not Run")</f>
-        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3888,7 +3946,7 @@
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">SUM(D11:D12)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">SUM(E11:E12)</f>
@@ -3896,15 +3954,15 @@
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">SUM(F11:F12)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">SUM(G11:G12)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">SUM(H11:H12)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3940,23 +3998,23 @@
         <v>20</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Functional")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A17,'Test Cases'!$E$2:$E$85,"Functional")</f>
         <v>19</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Security")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A17,'Test Cases'!$E$2:$E$85,"Security")</f>
         <v>9</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"API")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A17,'Test Cases'!$E$2:$E$85,"API")</f>
         <v>3</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Usability")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A17,'Test Cases'!$E$2:$E$85,"Usability")</f>
         <v>3</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A17,'Test Cases'!$E$2:$E$84,"Performance")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A17,'Test Cases'!$E$2:$E$85,"Performance")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
@@ -3969,28 +4027,28 @@
         <v>21</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Functional")</f>
-        <v>36</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A18,'Test Cases'!$E$2:$E$85,"Functional")</f>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Security")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A18,'Test Cases'!$E$2:$E$85,"Security")</f>
         <v>6</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"API")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A18,'Test Cases'!$E$2:$E$85,"API")</f>
         <v>3</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Usability")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A18,'Test Cases'!$E$2:$E$85,"Usability")</f>
         <v>3</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$84,$A18,'Test Cases'!$E$2:$E$84,"Performance")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A18,'Test Cases'!$E$2:$E$85,"Performance")</f>
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
         <f aca="false">SUM(B18:F18)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3999,7 +4057,7 @@
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">SUM(B17:B18)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">SUM(C17:C18)</f>
@@ -4019,7 +4077,7 @@
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">SUM(G17:G18)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4049,19 +4107,19 @@
         <v>34</v>
       </c>
       <c r="B23" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A23)</f>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$85,$A23)</f>
         <v>51</v>
       </c>
       <c r="C23" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A23,'Test Cases'!$G$2:$G$85,"P1")</f>
         <v>15</v>
       </c>
       <c r="D23" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A23,'Test Cases'!$G$2:$G$85,"P2")</f>
         <v>27</v>
       </c>
       <c r="E23" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A23,'Test Cases'!$G$2:$G$84,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A23,'Test Cases'!$G$2:$G$85,"P3")</f>
         <v>9</v>
       </c>
       <c r="G23" s="9" t="s">
@@ -4073,24 +4131,24 @@
         <v>36</v>
       </c>
       <c r="B24" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A24)</f>
-        <v>31</v>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$85,$A24)</f>
+        <v>32</v>
       </c>
       <c r="C24" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A24,'Test Cases'!$G$2:$G$85,"P1")</f>
         <v>4</v>
       </c>
       <c r="D24" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P2")</f>
-        <v>9</v>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A24,'Test Cases'!$G$2:$G$85,"P2")</f>
+        <v>10</v>
       </c>
       <c r="E24" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A24,'Test Cases'!$G$2:$G$84,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A24,'Test Cases'!$G$2:$G$85,"P3")</f>
         <v>18</v>
       </c>
       <c r="G24" s="10" t="n">
         <f aca="false">IFERROR(B23/(B23+B24),0)</f>
-        <v>0.621951219512195</v>
+        <v>0.614457831325301</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4098,19 +4156,19 @@
         <v>37</v>
       </c>
       <c r="B25" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A25)</f>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$85,$A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A25,'Test Cases'!$G$2:$G$84,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A25,'Test Cases'!$G$2:$G$85,"P1")</f>
         <v>0</v>
       </c>
       <c r="D25" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A25,'Test Cases'!$G$2:$G$84,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A25,'Test Cases'!$G$2:$G$85,"P2")</f>
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A25,'Test Cases'!$G$2:$G$84,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A25,'Test Cases'!$G$2:$G$85,"P3")</f>
         <v>0</v>
       </c>
     </row>
@@ -4119,19 +4177,19 @@
         <v>38</v>
       </c>
       <c r="B26" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$84,$A26)</f>
+        <f aca="false">COUNTIF('Test Cases'!$O$2:$O$85,$A26)</f>
         <v>1</v>
       </c>
       <c r="C26" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P1")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A26,'Test Cases'!$G$2:$G$85,"P1")</f>
         <v>0</v>
       </c>
       <c r="D26" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P2")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A26,'Test Cases'!$G$2:$G$85,"P2")</f>
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$84,$A26,'Test Cases'!$G$2:$G$84,"P3")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A26,'Test Cases'!$G$2:$G$85,"P3")</f>
         <v>1</v>
       </c>
     </row>
@@ -4141,7 +4199,7 @@
       </c>
       <c r="B27" s="8" t="n">
         <f aca="false">SUM(B23:B26)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" s="8" t="n">
         <f aca="false">SUM(C23:C26)</f>
@@ -4149,7 +4207,7 @@
       </c>
       <c r="D27" s="8" t="n">
         <f aca="false">SUM(D23:D26)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E27" s="8" t="n">
         <f aca="false">SUM(E23:E26)</f>
@@ -4177,7 +4235,7 @@
         <v>18</v>
       </c>
       <c r="B31" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A31)</f>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A31)</f>
         <v>43</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -4194,8 +4252,8 @@
         <v>43</v>
       </c>
       <c r="B32" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A32)</f>
-        <v>17</v>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A32)</f>
+        <v>18</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>44</v>
@@ -4211,7 +4269,7 @@
         <v>45</v>
       </c>
       <c r="B33" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A33)</f>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A33)</f>
         <v>11</v>
       </c>
       <c r="C33" s="11" t="s">
@@ -4228,7 +4286,7 @@
         <v>47</v>
       </c>
       <c r="B34" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$84,$A34)</f>
+        <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A34)</f>
         <v>12</v>
       </c>
       <c r="C34" s="11" t="s">
@@ -4261,7 +4319,7 @@
         <v>51</v>
       </c>
       <c r="B38" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$84,$A38)</f>
+        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$85,$A38)</f>
         <v>5</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -4278,8 +4336,8 @@
         <v>53</v>
       </c>
       <c r="B39" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$84,$A39)</f>
-        <v>35</v>
+        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$85,$A39)</f>
+        <v>36</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>54</v>
@@ -4295,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="B40" s="7" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$84,$A40)</f>
+        <f aca="false">COUNTIF('Test Cases'!$H$2:$H$85,$A40)</f>
         <v>43</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -4328,12 +4386,12 @@
         <v>61</v>
       </c>
       <c r="B44" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A44)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$29,$A44)</f>
+        <v>11</v>
       </c>
       <c r="C44" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A44,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$29,$A44,'Potential Defects'!$I$2:$I$29,"Reproduced")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4341,11 +4399,11 @@
         <v>62</v>
       </c>
       <c r="B45" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A45)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$29,$A45)</f>
         <v>8</v>
       </c>
       <c r="C45" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A45,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$29,$A45,'Potential Defects'!$I$2:$I$29,"Reproduced")</f>
         <v>8</v>
       </c>
     </row>
@@ -4354,11 +4412,11 @@
         <v>63</v>
       </c>
       <c r="B46" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A46)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$29,$A46)</f>
         <v>5</v>
       </c>
       <c r="C46" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A46,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$29,$A46,'Potential Defects'!$I$2:$I$29,"Reproduced")</f>
         <v>5</v>
       </c>
     </row>
@@ -4367,11 +4425,11 @@
         <v>64</v>
       </c>
       <c r="B47" s="7" t="n">
-        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$28,$A47)</f>
+        <f aca="false">COUNTIF('Potential Defects'!$C$2:$C$29,$A47)</f>
         <v>4</v>
       </c>
       <c r="C47" s="7" t="n">
-        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$28,$A47,'Potential Defects'!$I$2:$I$28,"Reproduced")</f>
+        <f aca="false">COUNTIFS('Potential Defects'!$C$2:$C$29,$A47,'Potential Defects'!$I$2:$I$29,"Reproduced")</f>
         <v>4</v>
       </c>
     </row>
@@ -4381,11 +4439,11 @@
       </c>
       <c r="B48" s="8" t="n">
         <f aca="false">SUM(B44:B47)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48" s="8" t="n">
         <f aca="false">SUM(C44:C47)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4627,8 +4685,24 @@
       <c r="G68" s="11"/>
       <c r="H68" s="11"/>
     </row>
+    <row r="69" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -4655,6 +4729,7 @@
     <mergeCell ref="C66:H66"/>
     <mergeCell ref="C67:H67"/>
     <mergeCell ref="C68:H68"/>
+    <mergeCell ref="C69:H69"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4671,7 +4746,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -4697,19 +4772,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>78</v>
@@ -4718,54 +4793,54 @@
         <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -4780,22 +4855,22 @@
         <v>53</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O2" s="12" t="s">
         <v>34</v>
@@ -4804,25 +4879,25 @@
         <v>89</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>23</v>
@@ -4837,22 +4912,22 @@
         <v>53</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O3" s="14" t="s">
         <v>34</v>
@@ -4861,16 +4936,16 @@
         <v>89</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -4879,7 +4954,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>23</v>
@@ -4894,22 +4969,22 @@
         <v>53</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>34</v>
@@ -4918,16 +4993,16 @@
         <v>89</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R4" s="12"/>
       <c r="S4" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -4936,7 +5011,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>23</v>
@@ -4951,22 +5026,22 @@
         <v>51</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>34</v>
@@ -4975,16 +5050,16 @@
         <v>89</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
@@ -4993,7 +5068,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>23</v>
@@ -5008,22 +5083,22 @@
         <v>53</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>34</v>
@@ -5032,16 +5107,16 @@
         <v>89</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
@@ -5050,7 +5125,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>23</v>
@@ -5065,22 +5140,22 @@
         <v>53</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O7" s="14" t="s">
         <v>34</v>
@@ -5089,16 +5164,16 @@
         <v>89</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>20</v>
@@ -5107,7 +5182,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>23</v>
@@ -5122,22 +5197,22 @@
         <v>53</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>34</v>
@@ -5146,16 +5221,16 @@
         <v>89</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>20</v>
@@ -5164,7 +5239,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>23</v>
@@ -5179,22 +5254,22 @@
         <v>53</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O9" s="14" t="s">
         <v>34</v>
@@ -5203,16 +5278,16 @@
         <v>89</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>20</v>
@@ -5221,7 +5296,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>23</v>
@@ -5236,22 +5311,22 @@
         <v>53</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>34</v>
@@ -5260,16 +5335,16 @@
         <v>89</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>20</v>
@@ -5278,7 +5353,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>23</v>
@@ -5293,22 +5368,22 @@
         <v>53</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O11" s="14" t="s">
         <v>34</v>
@@ -5317,16 +5392,16 @@
         <v>89</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R11" s="14"/>
       <c r="S11" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>20</v>
@@ -5335,7 +5410,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
@@ -5350,22 +5425,22 @@
         <v>55</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>36</v>
@@ -5374,18 +5449,18 @@
         <v>89</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>20</v>
@@ -5394,7 +5469,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>23</v>
@@ -5409,22 +5484,22 @@
         <v>55</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O13" s="14" t="s">
         <v>36</v>
@@ -5433,18 +5508,18 @@
         <v>89</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="S13" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>20</v>
@@ -5453,7 +5528,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>23</v>
@@ -5468,22 +5543,22 @@
         <v>55</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>36</v>
@@ -5492,18 +5567,18 @@
         <v>89</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>20</v>
@@ -5512,7 +5587,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>24</v>
@@ -5527,22 +5602,22 @@
         <v>55</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O15" s="14" t="s">
         <v>34</v>
@@ -5551,16 +5626,16 @@
         <v>89</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R15" s="14"/>
       <c r="S15" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>20</v>
@@ -5569,7 +5644,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>23</v>
@@ -5584,22 +5659,22 @@
         <v>55</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>34</v>
@@ -5608,16 +5683,16 @@
         <v>89</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -5626,7 +5701,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>23</v>
@@ -5641,22 +5716,22 @@
         <v>55</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O17" s="14" t="s">
         <v>34</v>
@@ -5665,16 +5740,16 @@
         <v>89</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R17" s="14"/>
       <c r="S17" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>20</v>
@@ -5683,7 +5758,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
@@ -5698,22 +5773,22 @@
         <v>55</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>34</v>
@@ -5722,16 +5797,16 @@
         <v>89</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>20</v>
@@ -5740,7 +5815,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>24</v>
@@ -5755,22 +5830,22 @@
         <v>55</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O19" s="14" t="s">
         <v>36</v>
@@ -5779,18 +5854,18 @@
         <v>89</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R19" s="14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S19" s="15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>20</v>
@@ -5799,7 +5874,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>23</v>
@@ -5814,22 +5889,22 @@
         <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>36</v>
@@ -5838,18 +5913,18 @@
         <v>89</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
@@ -5858,7 +5933,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -5873,22 +5948,22 @@
         <v>55</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O21" s="14" t="s">
         <v>36</v>
@@ -5897,18 +5972,18 @@
         <v>89</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R21" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5917,7 +5992,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>26</v>
@@ -5932,22 +6007,22 @@
         <v>55</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O22" s="12" t="s">
         <v>36</v>
@@ -5956,18 +6031,18 @@
         <v>89</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>20</v>
@@ -5976,7 +6051,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -5991,22 +6066,22 @@
         <v>51</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>34</v>
@@ -6015,25 +6090,25 @@
         <v>89</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R23" s="14"/>
       <c r="S23" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>23</v>
@@ -6048,22 +6123,22 @@
         <v>53</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>34</v>
@@ -6072,25 +6147,25 @@
         <v>89</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -6105,22 +6180,22 @@
         <v>53</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>34</v>
@@ -6129,25 +6204,25 @@
         <v>86</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -6162,22 +6237,22 @@
         <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>34</v>
@@ -6186,25 +6261,25 @@
         <v>89</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>24</v>
@@ -6219,22 +6294,22 @@
         <v>55</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" s="14" t="s">
         <v>36</v>
@@ -6243,27 +6318,27 @@
         <v>89</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
@@ -6278,22 +6353,22 @@
         <v>55</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>36</v>
@@ -6302,27 +6377,27 @@
         <v>89</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>24</v>
@@ -6337,22 +6412,22 @@
         <v>55</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M29" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O29" s="14" t="s">
         <v>34</v>
@@ -6361,25 +6436,25 @@
         <v>89</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R29" s="14"/>
       <c r="S29" s="15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>24</v>
@@ -6394,22 +6469,22 @@
         <v>55</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O30" s="12" t="s">
         <v>36</v>
@@ -6418,27 +6493,27 @@
         <v>89</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>23</v>
@@ -6453,22 +6528,22 @@
         <v>53</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O31" s="14" t="s">
         <v>34</v>
@@ -6477,25 +6552,25 @@
         <v>89</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R31" s="14"/>
       <c r="S31" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>24</v>
@@ -6510,22 +6585,22 @@
         <v>55</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M32" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O32" s="12" t="s">
         <v>34</v>
@@ -6534,16 +6609,16 @@
         <v>89</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R32" s="12"/>
       <c r="S32" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>20</v>
@@ -6552,7 +6627,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
@@ -6567,22 +6642,22 @@
         <v>53</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O33" s="14" t="s">
         <v>34</v>
@@ -6591,16 +6666,16 @@
         <v>89</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R33" s="14"/>
       <c r="S33" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>20</v>
@@ -6609,7 +6684,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>25</v>
@@ -6624,22 +6699,22 @@
         <v>53</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O34" s="12" t="s">
         <v>34</v>
@@ -6648,25 +6723,25 @@
         <v>89</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>25</v>
@@ -6681,22 +6756,22 @@
         <v>55</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M35" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>36</v>
@@ -6705,27 +6780,27 @@
         <v>89</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S35" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>23</v>
@@ -6740,22 +6815,22 @@
         <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>34</v>
@@ -6764,25 +6839,25 @@
         <v>86</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>23</v>
@@ -6797,22 +6872,22 @@
         <v>55</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O37" s="14" t="s">
         <v>34</v>
@@ -6821,25 +6896,25 @@
         <v>86</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R37" s="14"/>
       <c r="S37" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>23</v>
@@ -6854,22 +6929,22 @@
         <v>55</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>36</v>
@@ -6878,27 +6953,27 @@
         <v>86</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>23</v>
@@ -6913,22 +6988,22 @@
         <v>55</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>36</v>
@@ -6937,27 +7012,27 @@
         <v>86</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>23</v>
@@ -6972,22 +7047,22 @@
         <v>53</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M40" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O40" s="12" t="s">
         <v>34</v>
@@ -6996,25 +7071,25 @@
         <v>89</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R40" s="12"/>
       <c r="S40" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>23</v>
@@ -7029,22 +7104,22 @@
         <v>51</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M41" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>34</v>
@@ -7053,27 +7128,27 @@
         <v>89</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>23</v>
@@ -7088,22 +7163,22 @@
         <v>53</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M42" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>34</v>
@@ -7112,27 +7187,27 @@
         <v>89</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R42" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>23</v>
@@ -7147,22 +7222,22 @@
         <v>53</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>34</v>
@@ -7171,25 +7246,25 @@
         <v>89</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R43" s="14"/>
       <c r="S43" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>23</v>
@@ -7204,22 +7279,22 @@
         <v>53</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M44" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O44" s="12" t="s">
         <v>34</v>
@@ -7228,25 +7303,25 @@
         <v>86</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>23</v>
@@ -7261,22 +7336,22 @@
         <v>55</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M45" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>36</v>
@@ -7285,27 +7360,27 @@
         <v>86</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R45" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>23</v>
@@ -7320,16 +7395,16 @@
         <v>55</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M46" s="13" t="s">
         <v>47</v>
@@ -7342,21 +7417,21 @@
       <c r="Q46" s="12"/>
       <c r="R46" s="12"/>
       <c r="S46" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -7371,22 +7446,22 @@
         <v>55</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>36</v>
@@ -7395,27 +7470,27 @@
         <v>86</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>23</v>
@@ -7430,22 +7505,22 @@
         <v>53</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>34</v>
@@ -7454,25 +7529,25 @@
         <v>89</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>23</v>
@@ -7487,22 +7562,22 @@
         <v>53</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M49" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>34</v>
@@ -7511,25 +7586,25 @@
         <v>89</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="15" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>23</v>
@@ -7544,22 +7619,22 @@
         <v>53</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M50" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>34</v>
@@ -7568,25 +7643,25 @@
         <v>86</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R50" s="12"/>
       <c r="S50" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>23</v>
@@ -7601,22 +7676,22 @@
         <v>53</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M51" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N51" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O51" s="14" t="s">
         <v>34</v>
@@ -7625,25 +7700,25 @@
         <v>89</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="15" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
@@ -7658,22 +7733,22 @@
         <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M52" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>34</v>
@@ -7682,25 +7757,25 @@
         <v>86</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>26</v>
@@ -7715,22 +7790,22 @@
         <v>51</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M53" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N53" s="15" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O53" s="14" t="s">
         <v>34</v>
@@ -7739,25 +7814,25 @@
         <v>89</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R53" s="14"/>
       <c r="S53" s="15" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>27</v>
@@ -7772,22 +7847,22 @@
         <v>55</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M54" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>34</v>
@@ -7796,25 +7871,25 @@
         <v>89</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>23</v>
@@ -7829,22 +7904,22 @@
         <v>53</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M55" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N55" s="15" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O55" s="14" t="s">
         <v>34</v>
@@ -7853,25 +7928,25 @@
         <v>89</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R55" s="14"/>
       <c r="S55" s="15" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -7886,22 +7961,22 @@
         <v>53</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M56" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N56" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O56" s="12" t="s">
         <v>34</v>
@@ -7910,25 +7985,25 @@
         <v>89</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R56" s="12"/>
       <c r="S56" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>24</v>
@@ -7943,22 +8018,22 @@
         <v>55</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M57" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N57" s="15" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O57" s="14" t="s">
         <v>34</v>
@@ -7967,25 +8042,25 @@
         <v>89</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>23</v>
@@ -8000,22 +8075,22 @@
         <v>55</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M58" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N58" s="13" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O58" s="12" t="s">
         <v>36</v>
@@ -8024,27 +8099,27 @@
         <v>89</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R58" s="12" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="S58" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>23</v>
@@ -8059,22 +8134,22 @@
         <v>53</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M59" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O59" s="14" t="s">
         <v>34</v>
@@ -8083,25 +8158,25 @@
         <v>89</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>23</v>
@@ -8116,22 +8191,22 @@
         <v>51</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N60" s="13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>34</v>
@@ -8140,27 +8215,27 @@
         <v>89</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>23</v>
@@ -8175,22 +8250,22 @@
         <v>53</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O61" s="14" t="s">
         <v>34</v>
@@ -8199,25 +8274,25 @@
         <v>89</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>23</v>
@@ -8232,22 +8307,22 @@
         <v>55</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M62" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="13" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>36</v>
@@ -8256,27 +8331,27 @@
         <v>89</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="S62" s="13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>23</v>
@@ -8291,22 +8366,22 @@
         <v>53</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M63" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N63" s="15" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O63" s="14" t="s">
         <v>34</v>
@@ -8315,25 +8390,25 @@
         <v>89</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="15" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>23</v>
@@ -8348,22 +8423,22 @@
         <v>55</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O64" s="12" t="s">
         <v>36</v>
@@ -8372,27 +8447,27 @@
         <v>89</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>23</v>
@@ -8407,22 +8482,22 @@
         <v>55</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O65" s="14" t="s">
         <v>36</v>
@@ -8431,27 +8506,27 @@
         <v>86</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="S65" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>23</v>
@@ -8466,22 +8541,22 @@
         <v>53</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M66" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="13" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O66" s="12" t="s">
         <v>34</v>
@@ -8490,27 +8565,27 @@
         <v>86</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>23</v>
@@ -8525,22 +8600,22 @@
         <v>53</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M67" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N67" s="15" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O67" s="14" t="s">
         <v>34</v>
@@ -8549,25 +8624,25 @@
         <v>89</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="15" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>23</v>
@@ -8582,22 +8657,22 @@
         <v>53</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N68" s="13" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>34</v>
@@ -8606,25 +8681,25 @@
         <v>89</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>23</v>
@@ -8639,22 +8714,22 @@
         <v>53</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O69" s="14" t="s">
         <v>34</v>
@@ -8663,25 +8738,25 @@
         <v>89</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="15" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>23</v>
@@ -8696,22 +8771,22 @@
         <v>55</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="13" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>36</v>
@@ -8720,27 +8795,27 @@
         <v>86</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R70" s="12" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>23</v>
@@ -8755,22 +8830,22 @@
         <v>55</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>36</v>
@@ -8779,27 +8854,27 @@
         <v>86</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R71" s="14" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>23</v>
@@ -8814,22 +8889,22 @@
         <v>55</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>36</v>
@@ -8838,27 +8913,27 @@
         <v>86</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R72" s="12" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>23</v>
@@ -8873,22 +8948,22 @@
         <v>55</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M73" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="15" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>36</v>
@@ -8897,27 +8972,27 @@
         <v>86</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R73" s="14" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>23</v>
@@ -8932,22 +9007,22 @@
         <v>55</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O74" s="12" t="s">
         <v>36</v>
@@ -8956,27 +9031,27 @@
         <v>86</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R74" s="12" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>23</v>
@@ -8991,22 +9066,22 @@
         <v>55</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M75" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="15" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>36</v>
@@ -9015,27 +9090,27 @@
         <v>86</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R75" s="14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>26</v>
@@ -9050,22 +9125,22 @@
         <v>55</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>36</v>
@@ -9074,27 +9149,27 @@
         <v>86</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R76" s="12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="S76" s="13" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>24</v>
@@ -9109,22 +9184,22 @@
         <v>55</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="15" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>34</v>
@@ -9133,25 +9208,25 @@
         <v>86</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="15" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>23</v>
@@ -9166,22 +9241,22 @@
         <v>55</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M78" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N78" s="13" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O78" s="12" t="s">
         <v>36</v>
@@ -9190,27 +9265,27 @@
         <v>89</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R78" s="12" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="S78" s="13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>24</v>
@@ -9225,22 +9300,22 @@
         <v>55</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M79" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="15" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>36</v>
@@ -9249,27 +9324,27 @@
         <v>86</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>24</v>
@@ -9284,22 +9359,22 @@
         <v>55</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M80" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O80" s="12" t="s">
         <v>36</v>
@@ -9308,27 +9383,27 @@
         <v>86</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R80" s="12" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="S80" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>25</v>
@@ -9343,22 +9418,22 @@
         <v>53</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M81" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>34</v>
@@ -9367,25 +9442,25 @@
         <v>89</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="15" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>25</v>
@@ -9400,22 +9475,22 @@
         <v>53</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N82" s="13" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O82" s="12" t="s">
         <v>34</v>
@@ -9424,25 +9499,25 @@
         <v>89</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R82" s="12"/>
       <c r="S82" s="13" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>25</v>
@@ -9457,22 +9532,22 @@
         <v>55</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M83" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="15" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>36</v>
@@ -9481,27 +9556,27 @@
         <v>89</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S83" s="15" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>24</v>
@@ -9516,22 +9591,22 @@
         <v>55</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M84" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N84" s="13" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O84" s="12" t="s">
         <v>36</v>
@@ -9540,18 +9615,77 @@
         <v>89</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R84" s="12" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="S84" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="L85" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="M85" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N85" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="O85" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="P85" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q85" s="14" t="s">
+        <v>667</v>
+      </c>
+      <c r="R85" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="S85" s="15" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S84"/>
-  <conditionalFormatting sqref="O2:O84">
+  <autoFilter ref="A1:S85"/>
+  <conditionalFormatting sqref="O2:O85">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$O2="Pass"</formula>
     </cfRule>
@@ -9562,33 +9696,33 @@
       <formula>$O2="Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G84">
+  <conditionalFormatting sqref="G2:G85">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$G2="P1"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E85" type="list">
       <formula1>"Functional,Security,API,Usability,Performance"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F85" type="list">
       <formula1>"Positive,Negative,Edge,Boundary"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G85" type="list">
       <formula1>"P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H85" type="list">
       <formula1>"Challenge brief,Observed behaviour,Assumed (common practice)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O85" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M85" type="list">
       <formula1>"Automated,Automated (known defect),Backlog,Manual"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9609,7 +9743,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -9626,920 +9760,952 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>777</v>
+        <v>787</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>803</v>
+        <v>813</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
-        <v>814</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
+        <v>823</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>824</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>825</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>826</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>827</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>828</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J29"/>
   <mergeCells count="1">
-    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
   </mergeCells>
-  <conditionalFormatting sqref="I2:I28">
+  <conditionalFormatting sqref="I2:I29">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$I2="Reproduced"</formula>
     </cfRule>
@@ -10548,11 +10714,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I28" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I29" type="list">
       <formula1>"Reproduced,To reproduce,Intermittent,Not reproducible"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C28" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C29" type="list">
       <formula1>"Defect,Potential defect – requirement to confirm,Security observation,UX / improvement suggestion"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10583,175 +10749,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>815</v>
+        <v>831</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>822</v>
+        <v>838</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>823</v>
+        <v>839</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>825</v>
+        <v>841</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>827</v>
+        <v>843</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>828</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>830</v>
+        <v>846</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>828</v>
+        <v>844</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>836</v>
+        <v>852</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>837</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>838</v>
+        <v>854</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>851</v>
+        <v>867</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>853</v>
+        <v>869</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>854</v>
+        <v>870</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>855</v>
+        <v>871</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>58</v>
@@ -10759,182 +10925,182 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>858</v>
+        <v>874</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>360</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>820</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>861</v>
+        <v>877</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>650</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>862</v>
+        <v>878</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>800</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>320</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>700</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>866</v>
+        <v>882</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>874</v>
+        <v>890</v>
       </c>
       <c r="B34" s="20" t="n">
         <f aca="false">B21+B22</f>
         <v>1180</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>876</v>
+        <v>892</v>
       </c>
       <c r="B35" s="20" t="n">
         <f aca="false">B21*2</f>
         <v>720</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>877</v>
+        <v>893</v>
       </c>
       <c r="B36" s="20" t="n">
         <f aca="false">B21*2+B22</f>
         <v>1540</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="B37" s="20" t="n">
         <f aca="false">B23*3</f>
         <v>1950</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="B38" s="20" t="n">
         <f aca="false">SUM(B21:B29)+B21</f>
         <v>6380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -337,7 +337,7 @@
     <t xml:space="preserve">1.7</t>
   </si>
   <si>
-    <t xml:space="preserve">Root causes of the latest run's 5 failures: new defect PD-28 (bought items stay in the cart when OK is pressed quickly), covered by CRT-050; LGN-005 starts on Home to avoid the shared guest cart; the performance check runs on its own and uses the median of 3 cold loads.</t>
+    <t xml:space="preserve">Root causes of the latest run's 5 failures: new defect PD-28 (bought items stay in the cart when OK is pressed quickly), covered by CRT-050; LGN-005 starts on Home to avoid the shared guest cart; the performance check runs on its own and uses the median of 3 cold loads. Confirmed by the next full run: 167 passed, 0 failed, 0 flaky.</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -4685,7 +4685,7 @@
       <c r="G68" s="11"/>
       <c r="H68" s="11"/>
     </row>
-    <row r="69" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
         <v>101</v>
       </c>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="899">
   <si>
     <t xml:space="preserve">DemoBlaze – Test Case Suite (Login &amp; Cart)</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7 (20-Oct-2026)</t>
+    <t xml:space="preserve">1.8 (20-Oct-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Execution environment</t>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t xml:space="preserve">Root causes of the latest run's 5 failures: new defect PD-28 (bought items stay in the cart when OK is pressed quickly), covered by CRT-050; LGN-005 starts on Home to avoid the shared guest cart; the performance check runs on its own and uses the median of 3 cold loads. Confirmed by the next full run: 167 passed, 0 failed, 0 flaky.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT-011 executed manually (Pass), so every case has now been run. CRT-010 and CRT-011 automated: they keep watch for the intermittent lost-items defect PD-14 and capture a trace if it returns. Now 63 automated, 10 backlog, 11 manual.</t>
   </si>
   <si>
     <t xml:space="preserve">TC ID</t>
@@ -1437,7 +1443,10 @@
     <t xml:space="preserve">Cart has 3 'Nexus 6' rows; Total is 1950. No error alerts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Result depends on the intermittent lost-items defect (PD-14), so an automated test would pass or fail at random</t>
+    <t xml:space="preserve">Clicked 'Add to cart' on Nexus 6 3 times quickly: all 3 items were in the cart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Chrome – desktop (manual)</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-012</t>
@@ -3753,7 +3762,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3925,11 +3934,11 @@
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$M$2:$M$85,"Automated*")</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$85,$A12,'Test Cases'!$O$2:$O$85,"&lt;&gt;Not Run")</f>
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3958,11 +3967,11 @@
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">SUM(G11:G12)</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" s="8" t="n">
         <f aca="false">SUM(H11:H12)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4108,7 +4117,7 @@
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$85,$A23)</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A23,'Test Cases'!$G$2:$G$85,"P1")</f>
@@ -4120,7 +4129,7 @@
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A23,'Test Cases'!$G$2:$G$85,"P3")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>35</v>
@@ -4148,7 +4157,7 @@
       </c>
       <c r="G24" s="10" t="n">
         <f aca="false">IFERROR(B23/(B23+B24),0)</f>
-        <v>0.614457831325301</v>
+        <v>0.619047619047619</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4178,7 +4187,7 @@
       </c>
       <c r="B26" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$O$2:$O$85,$A26)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A26,'Test Cases'!$G$2:$G$85,"P1")</f>
@@ -4190,7 +4199,7 @@
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">COUNTIFS('Test Cases'!$O$2:$O$85,$A26,'Test Cases'!$G$2:$G$85,"P3")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4236,7 +4245,7 @@
       </c>
       <c r="B31" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A31)</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>42</v>
@@ -4270,7 +4279,7 @@
       </c>
       <c r="B33" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A33)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>46</v>
@@ -4287,7 +4296,7 @@
       </c>
       <c r="B34" s="7" t="n">
         <f aca="false">COUNTIF('Test Cases'!$M$2:$M$85,$A34)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>48</v>
@@ -4701,8 +4710,24 @@
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
     </row>
+    <row r="70" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -4730,6 +4755,7 @@
     <mergeCell ref="C67:H67"/>
     <mergeCell ref="C68:H68"/>
     <mergeCell ref="C69:H69"/>
+    <mergeCell ref="C70:H70"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4772,19 +4798,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>78</v>
@@ -4793,54 +4819,54 @@
         <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>23</v>
@@ -4855,22 +4881,22 @@
         <v>53</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O2" s="12" t="s">
         <v>34</v>
@@ -4879,25 +4905,25 @@
         <v>89</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>23</v>
@@ -4912,22 +4938,22 @@
         <v>53</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O3" s="14" t="s">
         <v>34</v>
@@ -4936,16 +4962,16 @@
         <v>89</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -4954,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>23</v>
@@ -4969,22 +4995,22 @@
         <v>53</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>34</v>
@@ -4993,16 +5019,16 @@
         <v>89</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R4" s="12"/>
       <c r="S4" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>20</v>
@@ -5011,7 +5037,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>23</v>
@@ -5026,22 +5052,22 @@
         <v>51</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>34</v>
@@ -5050,16 +5076,16 @@
         <v>89</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R5" s="14"/>
       <c r="S5" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
@@ -5068,7 +5094,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>23</v>
@@ -5083,22 +5109,22 @@
         <v>53</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>34</v>
@@ -5107,16 +5133,16 @@
         <v>89</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>20</v>
@@ -5125,7 +5151,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>23</v>
@@ -5140,22 +5166,22 @@
         <v>53</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O7" s="14" t="s">
         <v>34</v>
@@ -5164,16 +5190,16 @@
         <v>89</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>20</v>
@@ -5182,7 +5208,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>23</v>
@@ -5197,22 +5223,22 @@
         <v>53</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>34</v>
@@ -5221,16 +5247,16 @@
         <v>89</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>20</v>
@@ -5239,7 +5265,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>23</v>
@@ -5254,22 +5280,22 @@
         <v>53</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O9" s="14" t="s">
         <v>34</v>
@@ -5278,16 +5304,16 @@
         <v>89</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>20</v>
@@ -5296,7 +5322,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>23</v>
@@ -5311,22 +5337,22 @@
         <v>53</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>34</v>
@@ -5335,16 +5361,16 @@
         <v>89</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>20</v>
@@ -5353,7 +5379,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>23</v>
@@ -5368,22 +5394,22 @@
         <v>53</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M11" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O11" s="14" t="s">
         <v>34</v>
@@ -5392,16 +5418,16 @@
         <v>89</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R11" s="14"/>
       <c r="S11" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>20</v>
@@ -5410,7 +5436,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
@@ -5425,22 +5451,22 @@
         <v>55</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>36</v>
@@ -5449,18 +5475,18 @@
         <v>89</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>20</v>
@@ -5469,7 +5495,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>23</v>
@@ -5484,22 +5510,22 @@
         <v>55</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O13" s="14" t="s">
         <v>36</v>
@@ -5508,18 +5534,18 @@
         <v>89</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="S13" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>20</v>
@@ -5528,7 +5554,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>23</v>
@@ -5543,22 +5569,22 @@
         <v>55</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>36</v>
@@ -5567,18 +5593,18 @@
         <v>89</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>20</v>
@@ -5587,7 +5613,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>24</v>
@@ -5602,22 +5628,22 @@
         <v>55</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O15" s="14" t="s">
         <v>34</v>
@@ -5626,16 +5652,16 @@
         <v>89</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R15" s="14"/>
       <c r="S15" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>20</v>
@@ -5644,7 +5670,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>23</v>
@@ -5659,22 +5685,22 @@
         <v>55</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>34</v>
@@ -5683,16 +5709,16 @@
         <v>89</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -5701,7 +5727,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>23</v>
@@ -5716,22 +5742,22 @@
         <v>55</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O17" s="14" t="s">
         <v>34</v>
@@ -5740,16 +5766,16 @@
         <v>89</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R17" s="14"/>
       <c r="S17" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>20</v>
@@ -5758,7 +5784,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>24</v>
@@ -5773,22 +5799,22 @@
         <v>55</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>34</v>
@@ -5797,16 +5823,16 @@
         <v>89</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>20</v>
@@ -5815,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>24</v>
@@ -5830,22 +5856,22 @@
         <v>55</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O19" s="14" t="s">
         <v>36</v>
@@ -5854,18 +5880,18 @@
         <v>89</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R19" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="S19" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>20</v>
@@ -5874,7 +5900,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>23</v>
@@ -5889,22 +5915,22 @@
         <v>55</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>36</v>
@@ -5913,18 +5939,18 @@
         <v>89</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
@@ -5933,7 +5959,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -5948,22 +5974,22 @@
         <v>55</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O21" s="14" t="s">
         <v>36</v>
@@ -5972,18 +5998,18 @@
         <v>89</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R21" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="S21" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>20</v>
@@ -5992,7 +6018,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>26</v>
@@ -6007,22 +6033,22 @@
         <v>55</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O22" s="12" t="s">
         <v>36</v>
@@ -6031,18 +6057,18 @@
         <v>89</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>20</v>
@@ -6051,7 +6077,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -6066,22 +6092,22 @@
         <v>51</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M23" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>34</v>
@@ -6090,25 +6116,25 @@
         <v>89</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R23" s="14"/>
       <c r="S23" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>23</v>
@@ -6123,22 +6149,22 @@
         <v>53</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>34</v>
@@ -6147,25 +6173,25 @@
         <v>89</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R24" s="12"/>
       <c r="S24" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>23</v>
@@ -6180,22 +6206,22 @@
         <v>53</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>34</v>
@@ -6204,25 +6230,25 @@
         <v>86</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>24</v>
@@ -6237,22 +6263,22 @@
         <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>34</v>
@@ -6261,25 +6287,25 @@
         <v>89</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>24</v>
@@ -6294,22 +6320,22 @@
         <v>55</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O27" s="14" t="s">
         <v>36</v>
@@ -6318,27 +6344,27 @@
         <v>89</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>24</v>
@@ -6353,22 +6379,22 @@
         <v>55</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>36</v>
@@ -6377,27 +6403,27 @@
         <v>89</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>24</v>
@@ -6412,22 +6438,22 @@
         <v>55</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M29" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O29" s="14" t="s">
         <v>34</v>
@@ -6436,25 +6462,25 @@
         <v>89</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R29" s="14"/>
       <c r="S29" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>24</v>
@@ -6469,22 +6495,22 @@
         <v>55</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O30" s="12" t="s">
         <v>36</v>
@@ -6493,27 +6519,27 @@
         <v>89</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>23</v>
@@ -6528,22 +6554,22 @@
         <v>53</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O31" s="14" t="s">
         <v>34</v>
@@ -6552,25 +6578,25 @@
         <v>89</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R31" s="14"/>
       <c r="S31" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>24</v>
@@ -6585,22 +6611,22 @@
         <v>55</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M32" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O32" s="12" t="s">
         <v>34</v>
@@ -6609,16 +6635,16 @@
         <v>89</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R32" s="12"/>
       <c r="S32" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>20</v>
@@ -6627,7 +6653,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>25</v>
@@ -6642,22 +6668,22 @@
         <v>53</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O33" s="14" t="s">
         <v>34</v>
@@ -6666,16 +6692,16 @@
         <v>89</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R33" s="14"/>
       <c r="S33" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>20</v>
@@ -6684,7 +6710,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>25</v>
@@ -6699,22 +6725,22 @@
         <v>53</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O34" s="12" t="s">
         <v>34</v>
@@ -6723,25 +6749,25 @@
         <v>89</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>25</v>
@@ -6756,22 +6782,22 @@
         <v>55</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M35" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>36</v>
@@ -6780,27 +6806,27 @@
         <v>89</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S35" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>23</v>
@@ -6815,22 +6841,22 @@
         <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>34</v>
@@ -6839,25 +6865,25 @@
         <v>86</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R36" s="12"/>
       <c r="S36" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>23</v>
@@ -6872,22 +6898,22 @@
         <v>55</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O37" s="14" t="s">
         <v>34</v>
@@ -6896,25 +6922,25 @@
         <v>86</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R37" s="14"/>
       <c r="S37" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>23</v>
@@ -6929,22 +6955,22 @@
         <v>55</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>36</v>
@@ -6953,27 +6979,27 @@
         <v>86</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>23</v>
@@ -6988,22 +7014,22 @@
         <v>55</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>36</v>
@@ -7012,27 +7038,27 @@
         <v>86</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>23</v>
@@ -7047,22 +7073,22 @@
         <v>53</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M40" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O40" s="12" t="s">
         <v>34</v>
@@ -7071,25 +7097,25 @@
         <v>89</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R40" s="12"/>
       <c r="S40" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>23</v>
@@ -7104,22 +7130,22 @@
         <v>51</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M41" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>34</v>
@@ -7128,27 +7154,27 @@
         <v>89</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>23</v>
@@ -7163,22 +7189,22 @@
         <v>53</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M42" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>34</v>
@@ -7187,27 +7213,27 @@
         <v>89</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R42" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>23</v>
@@ -7222,22 +7248,22 @@
         <v>53</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M43" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>34</v>
@@ -7246,25 +7272,25 @@
         <v>89</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R43" s="14"/>
       <c r="S43" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>23</v>
@@ -7279,22 +7305,22 @@
         <v>53</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M44" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O44" s="12" t="s">
         <v>34</v>
@@ -7303,25 +7329,25 @@
         <v>86</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>23</v>
@@ -7336,22 +7362,22 @@
         <v>55</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M45" s="15" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>36</v>
@@ -7360,27 +7386,27 @@
         <v>86</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R45" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>274</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>23</v>
@@ -7395,43 +7421,49 @@
         <v>55</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N46" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="N46" s="13" t="s">
+        <v>413</v>
+      </c>
       <c r="O46" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="P46" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q46" s="12" t="s">
+        <v>414</v>
+      </c>
       <c r="R46" s="12"/>
       <c r="S46" s="13" t="s">
-        <v>411</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -7446,22 +7478,22 @@
         <v>55</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>36</v>
@@ -7470,27 +7502,27 @@
         <v>86</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>23</v>
@@ -7505,22 +7537,22 @@
         <v>53</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O48" s="12" t="s">
         <v>34</v>
@@ -7529,25 +7561,25 @@
         <v>89</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="13" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>23</v>
@@ -7562,22 +7594,22 @@
         <v>53</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M49" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>34</v>
@@ -7586,25 +7618,25 @@
         <v>89</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>23</v>
@@ -7619,22 +7651,22 @@
         <v>53</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M50" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>34</v>
@@ -7643,25 +7675,25 @@
         <v>86</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R50" s="12"/>
       <c r="S50" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>23</v>
@@ -7676,22 +7708,22 @@
         <v>53</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M51" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N51" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O51" s="14" t="s">
         <v>34</v>
@@ -7700,25 +7732,25 @@
         <v>89</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>23</v>
@@ -7733,22 +7765,22 @@
         <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M52" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O52" s="12" t="s">
         <v>34</v>
@@ -7757,25 +7789,25 @@
         <v>86</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>26</v>
@@ -7790,22 +7822,22 @@
         <v>51</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M53" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N53" s="15" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O53" s="14" t="s">
         <v>34</v>
@@ -7814,25 +7846,25 @@
         <v>89</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R53" s="14"/>
       <c r="S53" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>27</v>
@@ -7847,22 +7879,22 @@
         <v>55</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M54" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>34</v>
@@ -7871,25 +7903,25 @@
         <v>89</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="13" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>23</v>
@@ -7904,22 +7936,22 @@
         <v>53</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M55" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N55" s="15" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O55" s="14" t="s">
         <v>34</v>
@@ -7928,25 +7960,25 @@
         <v>89</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R55" s="14"/>
       <c r="S55" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>24</v>
@@ -7961,22 +7993,22 @@
         <v>53</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M56" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N56" s="13" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="O56" s="12" t="s">
         <v>34</v>
@@ -7985,25 +8017,25 @@
         <v>89</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R56" s="12"/>
       <c r="S56" s="13" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>24</v>
@@ -8018,22 +8050,22 @@
         <v>55</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M57" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N57" s="15" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="O57" s="14" t="s">
         <v>34</v>
@@ -8042,25 +8074,25 @@
         <v>89</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>23</v>
@@ -8075,22 +8107,22 @@
         <v>55</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M58" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N58" s="13" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="O58" s="12" t="s">
         <v>36</v>
@@ -8099,27 +8131,27 @@
         <v>89</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R58" s="12" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="S58" s="13" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>23</v>
@@ -8134,22 +8166,22 @@
         <v>53</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M59" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O59" s="14" t="s">
         <v>34</v>
@@ -8158,25 +8190,25 @@
         <v>89</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="165.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>23</v>
@@ -8191,22 +8223,22 @@
         <v>51</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N60" s="13" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>34</v>
@@ -8215,27 +8247,27 @@
         <v>89</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>23</v>
@@ -8250,22 +8282,22 @@
         <v>53</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="O61" s="14" t="s">
         <v>34</v>
@@ -8274,25 +8306,25 @@
         <v>89</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>23</v>
@@ -8307,22 +8339,22 @@
         <v>55</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M62" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="13" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>36</v>
@@ -8331,27 +8363,27 @@
         <v>89</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="S62" s="13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>23</v>
@@ -8366,22 +8398,22 @@
         <v>53</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M63" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N63" s="15" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="O63" s="14" t="s">
         <v>34</v>
@@ -8390,25 +8422,25 @@
         <v>89</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="15" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>23</v>
@@ -8423,22 +8455,22 @@
         <v>55</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="M64" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="O64" s="12" t="s">
         <v>36</v>
@@ -8447,27 +8479,27 @@
         <v>89</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>23</v>
@@ -8482,22 +8514,22 @@
         <v>55</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="O65" s="14" t="s">
         <v>36</v>
@@ -8506,27 +8538,27 @@
         <v>86</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="S65" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>23</v>
@@ -8541,22 +8573,22 @@
         <v>53</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M66" s="13" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="13" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="O66" s="12" t="s">
         <v>34</v>
@@ -8565,27 +8597,27 @@
         <v>86</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>23</v>
@@ -8600,22 +8632,22 @@
         <v>53</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M67" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N67" s="15" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="O67" s="14" t="s">
         <v>34</v>
@@ -8624,25 +8656,25 @@
         <v>89</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="15" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>23</v>
@@ -8657,22 +8689,22 @@
         <v>53</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N68" s="13" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>34</v>
@@ -8681,25 +8713,25 @@
         <v>89</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="13" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>23</v>
@@ -8714,22 +8746,22 @@
         <v>53</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="O69" s="14" t="s">
         <v>34</v>
@@ -8738,25 +8770,25 @@
         <v>89</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="15" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>23</v>
@@ -8771,22 +8803,22 @@
         <v>55</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="13" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>36</v>
@@ -8795,27 +8827,27 @@
         <v>86</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R70" s="12" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>23</v>
@@ -8830,22 +8862,22 @@
         <v>55</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>36</v>
@@ -8854,27 +8886,27 @@
         <v>86</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R71" s="14" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>23</v>
@@ -8889,22 +8921,22 @@
         <v>55</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="13" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>36</v>
@@ -8913,27 +8945,27 @@
         <v>86</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R72" s="12" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>23</v>
@@ -8948,22 +8980,22 @@
         <v>55</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M73" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="15" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>36</v>
@@ -8972,27 +9004,27 @@
         <v>86</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R73" s="14" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>23</v>
@@ -9007,22 +9039,22 @@
         <v>55</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="O74" s="12" t="s">
         <v>36</v>
@@ -9031,27 +9063,27 @@
         <v>86</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R74" s="12" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>23</v>
@@ -9066,22 +9098,22 @@
         <v>55</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M75" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="15" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>36</v>
@@ -9090,27 +9122,27 @@
         <v>86</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R75" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>26</v>
@@ -9125,22 +9157,22 @@
         <v>55</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L76" s="13" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="13" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>36</v>
@@ -9149,27 +9181,27 @@
         <v>86</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R76" s="12" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="S76" s="13" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>24</v>
@@ -9184,22 +9216,22 @@
         <v>55</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="15" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>34</v>
@@ -9208,25 +9240,25 @@
         <v>86</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="15" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>23</v>
@@ -9241,22 +9273,22 @@
         <v>55</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L78" s="13" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M78" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N78" s="13" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="O78" s="12" t="s">
         <v>36</v>
@@ -9265,27 +9297,27 @@
         <v>89</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R78" s="12" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="S78" s="13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>24</v>
@@ -9300,22 +9332,22 @@
         <v>55</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="M79" s="15" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="15" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>36</v>
@@ -9324,27 +9356,27 @@
         <v>86</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>24</v>
@@ -9359,22 +9391,22 @@
         <v>55</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M80" s="13" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="O80" s="12" t="s">
         <v>36</v>
@@ -9383,27 +9415,27 @@
         <v>86</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R80" s="12" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="S80" s="13" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E81" s="14" t="s">
         <v>25</v>
@@ -9418,22 +9450,22 @@
         <v>53</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M81" s="15" t="s">
         <v>18</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>34</v>
@@ -9442,25 +9474,25 @@
         <v>89</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="15" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>25</v>
@@ -9475,22 +9507,22 @@
         <v>53</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>18</v>
       </c>
       <c r="N82" s="13" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="O82" s="12" t="s">
         <v>34</v>
@@ -9499,25 +9531,25 @@
         <v>89</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R82" s="12"/>
       <c r="S82" s="13" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>25</v>
@@ -9532,22 +9564,22 @@
         <v>55</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M83" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="15" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>36</v>
@@ -9556,27 +9588,27 @@
         <v>89</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S83" s="15" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>24</v>
@@ -9591,22 +9623,22 @@
         <v>55</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="M84" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N84" s="13" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="O84" s="12" t="s">
         <v>36</v>
@@ -9615,27 +9647,27 @@
         <v>89</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R84" s="12" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="S84" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E85" s="14" t="s">
         <v>23</v>
@@ -9650,22 +9682,22 @@
         <v>53</v>
       </c>
       <c r="I85" s="15" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L85" s="15" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="M85" s="15" t="s">
         <v>43</v>
       </c>
       <c r="N85" s="15" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="O85" s="14" t="s">
         <v>36</v>
@@ -9674,13 +9706,13 @@
         <v>89</v>
       </c>
       <c r="Q85" s="14" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="R85" s="14" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="S85" s="15" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -9760,935 +9792,935 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>60</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="I29" s="14" t="s">
         <v>60</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -10749,175 +10781,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>58</v>
@@ -10925,182 +10957,182 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>360</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>820</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>650</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>800</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>320</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>700</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>790</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B34" s="20" t="n">
         <f aca="false">B21+B22</f>
         <v>1180</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B35" s="20" t="n">
         <f aca="false">B21*2</f>
         <v>720</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B36" s="20" t="n">
         <f aca="false">B21*2+B22</f>
         <v>1540</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B37" s="20" t="n">
         <f aca="false">B23*3</f>
         <v>1950</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B38" s="20" t="n">
         <f aca="false">SUM(B21:B29)+B21</f>
         <v>6380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DemoBlaze_Test_Cases.xlsx
+++ b/docs/DemoBlaze_Test_Cases.xlsx
@@ -450,7 +450,7 @@
     <t xml:space="preserve">Page reloads on cart.html, shows 'Welcome {VALID_USER}' and lists {VALID_USER}'s cart item.</t>
   </si>
   <si>
-    <t xml:space="preserve">Page reloaded on cart.html with 'Welcome &lt;user&gt;' and the user's cart item listed. (The journey starts on Home: opening cart.html directly as a guest loads the shared guest cart (PD-22), hundreds of items, which once slowed the API enough to time the test out.)</t>
+    <t xml:space="preserve">Page reloaded on cart.html with 'Welcome &lt;user&gt;' and the user's cart item listed. (The journey starts on Home: opening cart.html directly as a guest loads the shared guest cart (PD-21), hundreds of items, which once slowed the API enough to time the test out.)</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-006</t>
@@ -598,10 +598,10 @@
     <t xml:space="preserve">Login succeeds and the navbar shows 'Welcome {VALID_USER}' (no spaces).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-26): ' &lt;username&gt; ' with spaces gave 'User does not exist.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-26</t>
+    <t xml:space="preserve">Fails as expected (PD-25): ' &lt;username&gt; ' with spaces gave 'User does not exist.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-25</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-013</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">Login succeeds and the navbar shows 'Welcome {VALID_USER}'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-27): username in upper case gave 'User does not exist.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-27</t>
+    <t xml:space="preserve">Fails as expected (PD-26): username in upper case gave 'User does not exist.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-26</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-014</t>
@@ -778,10 +778,10 @@
     <t xml:space="preserve">After the configured threshold (e.g. 5 attempts, to confirm with PO), further attempts are blocked with a lockout, CAPTCHA or rate-limit message.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-25): the 10th consecutive wrong password still returned 'Wrong password.' – no lockout or rate limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-25</t>
+    <t xml:space="preserve">Fails as expected (PD-24): the 10th consecutive wrong password still returned 'Wrong password.' – no lockout or rate limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-24</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-019</t>
@@ -798,10 +798,10 @@
     <t xml:space="preserve">User is logged in ('Welcome {VALID_USER}'). Only one POST /login request is sent; no error alert.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-23): double-click sent two POST /login requests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-23</t>
+    <t xml:space="preserve">Fails as expected (PD-22): double-click sent two POST /login requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-22</t>
   </si>
   <si>
     <t xml:space="preserve">LGN-020</t>
@@ -957,10 +957,10 @@
     <t xml:space="preserve">The token is random and opaque; decoding it does not reveal the username or any predictable value.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-18): token decodes to username + number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-18</t>
+    <t xml:space="preserve">Fails as expected (PD-17): token decodes to username + number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-17</t>
   </si>
   <si>
     <t xml:space="preserve">tests/security/session-security.spec.ts</t>
@@ -1119,10 +1119,10 @@
     <t xml:space="preserve">HTTP 401 Unauthorized.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-19): HTTP 200 + errorMessage instead of 401.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-19</t>
+    <t xml:space="preserve">Fails as expected (PD-18): HTTP 200 + errorMessage instead of 401.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-18</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-001</t>
@@ -1194,7 +1194,7 @@
     <t xml:space="preserve">Page showed 'undefined $undefined' with an active 'Add to cart'; clicking it gave alert 'Bad parameter, token malformed.'</t>
   </si>
   <si>
-    <t xml:space="preserve">PD-15</t>
+    <t xml:space="preserve">PD-14</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-004</t>
@@ -1213,7 +1213,7 @@
     <t xml:space="preserve">Blank product area; Console: Uncaught TypeError: Cannot read properties of undefined (reading 'split') at prod.js:39.</t>
   </si>
   <si>
-    <t xml:space="preserve">PD-16</t>
+    <t xml:space="preserve">PD-15</t>
   </si>
   <si>
     <t xml:space="preserve">Console-error judgement – manual (automatable later)</t>
@@ -1738,7 +1738,7 @@
     <t xml:space="preserve">The cart table has no rows, and the server-side cart (/viewcart) is empty.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart empty on the server and in the UI after purchase. One run failed on Chromium and Firefox because the script pressed OK before the site's cart-clear call had finished: logged as PD-28 (CRT-050). The script now waits for that call, as a user reading the receipt would.</t>
+    <t xml:space="preserve">Cart empty on the server and in the UI after purchase. One run failed on Chromium and Firefox because the script pressed OK before the site's cart-clear call had finished: logged as PD-27 (CRT-050). The script now waits for that call, as a user reading the receipt would.</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-027</t>
@@ -1840,7 +1840,7 @@
     <t xml:space="preserve">Item was purchased and removed from the cart, but confirmation showed 'Amount: 0 USD'.</t>
   </si>
   <si>
-    <t xml:space="preserve">PD-20</t>
+    <t xml:space="preserve">PD-19</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-031</t>
@@ -2085,7 +2085,7 @@
     <t xml:space="preserve">Order placed; the 500-character Name overflowed the dialog horizontally.</t>
   </si>
   <si>
-    <t xml:space="preserve">PD-21</t>
+    <t xml:space="preserve">PD-20</t>
   </si>
   <si>
     <t xml:space="preserve">Visual layout check – manual or visual-regression tool</t>
@@ -2137,10 +2137,10 @@
     <t xml:space="preserve">Exactly one confirmation (one order Id) is shown.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-24): double-click sent two order submissions (POST /deletecart twice).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-24</t>
+    <t xml:space="preserve">Fails as expected (PD-23): double-click sent two order submissions (POST /deletecart twice).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-23</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-044</t>
@@ -2164,7 +2164,7 @@
     <t xml:space="preserve">Credit card is a plain text input; full number visible while typing.</t>
   </si>
   <si>
-    <t xml:space="preserve">PD-17</t>
+    <t xml:space="preserve">PD-16</t>
   </si>
   <si>
     <t xml:space="preserve">Security UX, assumed requirement – manual</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">HTTP 404 Not Found.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-19): HTTP 200 + 'Not found.' instead of 404.</t>
+    <t xml:space="preserve">Fails as expected (PD-18): HTTP 200 + 'Not found.' instead of 404.</t>
   </si>
   <si>
     <t xml:space="preserve">tests/api/product.api.spec.ts</t>
@@ -2272,10 +2272,10 @@
     <t xml:space="preserve">The cart contains only the one 'Nokia lumia 1520' just added (the guest has a private cart keyed by a unique guest id).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-22): /addtocart sent with an empty guest id; the shared cart held 121-134 items from other guests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD-22</t>
+    <t xml:space="preserve">Fails as expected (PD-21): /addtocart sent with an empty guest id; the shared cart held 121-134 items from other guests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD-21</t>
   </si>
   <si>
     <t xml:space="preserve">CRT-050</t>
@@ -2298,13 +2298,13 @@
     <t xml:space="preserve">The cart is empty, however quickly 'OK' is clicked.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fails as expected (PD-28). First seen in the 20-Oct full run (CRT-026, Chromium and Firefox): OK was pressed about 1 s after Purchase, the move to Home cancelled POST /deletecart (no response), and the server cart still held the item 20 s later. The test reproduces it on demand by slowing that one request down.</t>
+    <t xml:space="preserve">Fails as expected (PD-27). First seen in the 20-Oct full run (CRT-026, Chromium and Firefox): OK was pressed about 1 s after Purchase, the move to Home cancelled POST /deletecart (no response), and the server cart still held the item 20 s later. The test reproduces it on demand by slowing that one request down.</t>
   </si>
   <si>
     <t xml:space="preserve">Automated: Chromium</t>
   </si>
   <si>
-    <t xml:space="preserve">PD-28</t>
+    <t xml:space="preserve">PD-27</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -2659,7 +2659,7 @@
     <t xml:space="preserve">'cWFfc3lfMDExNzkzMDEx' decodes to 'qa_sy_011793011' (username + number). A token for another user could potentially be built without their password (not attempted).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-18_LGN-026_&lt;browser&gt;.txt (API log)
+    <t xml:space="preserve">reports/evidence/PD-17_LGN-026_&lt;browser&gt;.txt (API log)
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2683,8 +2683,8 @@
     <t xml:space="preserve">HTTP 200 with {"errorMessage": ...} in the body.</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-19_LGN-034_api.txt (API log)
-reports/evidence/PD-19_CRT-048_api.txt (API log)</t>
+    <t xml:space="preserve">reports/evidence/PD-18_LGN-034_api.txt (API log)
+reports/evidence/PD-18_CRT-048_api.txt (API log)</t>
   </si>
   <si>
     <t xml:space="preserve">Order amount uses a stale client-side total</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">Only the Home page creates the guest id cookie ('user'). A guest who lands on a product page first (search result, shared link) sends an empty id, so all such guests read and write the same cart: our test saw 121-134 items from other people. Privacy issue: one guest can see, and buy, another guest's items. Reproduced 20-Oct-2026 by the automated run on Chromium, Firefox and WebKit.</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-22_CRT-049_&lt;browser&gt;.png + .webm
+    <t xml:space="preserve">reports/evidence/PD-21_CRT-049_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2751,7 +2751,7 @@
     <t xml:space="preserve">A double-click calls logIn() twice and sends two POST /login requests. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-23_LGN-019_&lt;browser&gt;.png + .webm
+    <t xml:space="preserve">reports/evidence/PD-22_LGN-019_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">A double-click runs purchaseOrder() twice: two order submissions (POST /deletecart twice) and the confirmation is regenerated. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-24_CRT-043_&lt;browser&gt;.png + .webm
+    <t xml:space="preserve">reports/evidence/PD-23_CRT-043_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">10 consecutive wrong passwords all returned 'Wrong password.'; nothing slows down or blocks guessing, so passwords can be brute-forced. Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-25_LGN-018_&lt;browser&gt;.png + .webm
+    <t xml:space="preserve">reports/evidence/PD-24_LGN-018_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">' &lt;username&gt; ' with surrounding spaces returns 'User does not exist.' Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-26_LGN-012_&lt;browser&gt;.png + .webm
+    <t xml:space="preserve">reports/evidence/PD-25_LGN-012_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">The username in upper case returns 'User does not exist.' Reproduced 20-Oct-2026 by the automated run (Chromium, Firefox, WebKit).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-27_LGN-013_&lt;browser&gt;.png + .webm
+    <t xml:space="preserve">reports/evidence/PD-26_LGN-013_&lt;browser&gt;.png + .webm
 (&lt;browser&gt; = chromium, firefox, webkit)</t>
   </si>
   <si>
@@ -2851,7 +2851,7 @@
     <t xml:space="preserve">purchaseOrder() sends POST /deletecart without waiting for it, and OK goes to Home straight away. If OK is pressed before that request finishes, the browser cancels it and the server cart keeps the purchased items (automated run: the item was still there 20 s later). The customer can then pay for the same items again. Found by the automated run on 20-Oct-2026 (Chromium, Firefox).</t>
   </si>
   <si>
-    <t xml:space="preserve">reports/evidence/PD-28_CRT-050_chromium.png + .webm</t>
+    <t xml:space="preserve">reports/evidence/PD-27_CRT-050_chromium.png + .webm</t>
   </si>
   <si>
     <t xml:space="preserve">Note: DemoBlaze has no published requirements. 'Expected' follows common e-commerce practice, so 'Potential defect – requirement to confirm' items should be agreed with the product owner before being raised as bugs. 'Reproduced?' = observed when the related test was run on 19-Oct-2026.</t>
